--- a/dados/2026-08-13.xlsx
+++ b/dados/2026-08-13.xlsx
@@ -3549,72 +3549,72 @@
       </c>
       <c r="C8" s="64"/>
       <c r="D8" s="83">
-        <v>29755728.719999999</v>
+        <v>29714466.289999995</v>
       </c>
       <c r="E8" s="120">
-        <v>4.0553040568091481</v>
+        <v>4.0496805447336284</v>
       </c>
       <c r="F8" s="64"/>
       <c r="G8" s="84">
         <v>7337484.021706827</v>
       </c>
       <c r="H8" s="84">
-        <v>3301867.8097680719</v>
+        <v>3668742.0108534135</v>
       </c>
       <c r="I8" s="85">
-        <v>3928440.3800000115</v>
+        <v>4241594.9000000153</v>
       </c>
       <c r="J8" s="70">
-        <v>1.189763069368895</v>
+        <v>1.1561442280356329</v>
       </c>
       <c r="K8" s="86"/>
       <c r="L8" s="87">
         <v>2.95</v>
       </c>
       <c r="M8" s="88">
-        <v>-5.1427038864716437</v>
+        <v>-4.9417690619153385</v>
       </c>
       <c r="N8" s="70">
-        <v>-1.7432894530412351</v>
+        <v>-1.6751759531916401</v>
       </c>
       <c r="O8" s="86"/>
       <c r="P8" s="84">
-        <v>97405.100388158127</v>
+        <v>108227.8893201757</v>
       </c>
       <c r="Q8" s="84">
-        <v>-202028.056099982</v>
+        <v>-209609.82449997959</v>
       </c>
       <c r="R8" s="83">
         <v>0</v>
       </c>
       <c r="S8" s="85">
-        <v>-202028.056099982</v>
+        <v>-209609.82449997959</v>
       </c>
       <c r="T8" s="70">
-        <v>-2.0741014104487618</v>
+        <v>-1.9367450092266041</v>
       </c>
       <c r="U8" s="69"/>
       <c r="V8" s="83">
         <v>366874.20108534134</v>
       </c>
       <c r="W8" s="89">
-        <v>1011451.4700000001</v>
+        <v>311807.2300000001</v>
       </c>
       <c r="X8" s="90">
-        <v>-12.788764467364969</v>
+        <v>-2.5074493622228458</v>
       </c>
       <c r="Y8" s="70">
-        <v>-4.3351743957169386</v>
+        <v>-0.84998283465181212</v>
       </c>
       <c r="Z8" s="91"/>
       <c r="AA8" s="85">
         <v>10822.788932017569</v>
       </c>
       <c r="AB8" s="85">
-        <v>-129352.14620000066</v>
+        <v>-7818.4083999997238</v>
       </c>
       <c r="AC8" s="70">
-        <v>-11.951831178868515</v>
+        <v>-0.72240237235618221</v>
       </c>
     </row>
     <row r="9" spans="1:29" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3626,72 +3626,72 @@
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="83">
-        <v>1395937.47</v>
+        <v>1372960.35</v>
       </c>
       <c r="E9" s="120">
-        <v>0.85385706968564601</v>
+        <v>0.83980258889789594</v>
       </c>
       <c r="F9" s="28"/>
       <c r="G9" s="84">
         <v>1634860.8210434155</v>
       </c>
       <c r="H9" s="84">
-        <v>735687.36946953693</v>
+        <v>817430.41052170773</v>
       </c>
       <c r="I9" s="85">
-        <v>608230.62000000034</v>
+        <v>681457.39000000083</v>
       </c>
       <c r="J9" s="70">
-        <v>0.82675147792541481</v>
+        <v>0.83365798632947241</v>
       </c>
       <c r="K9" s="86"/>
       <c r="L9" s="87">
         <v>3.55</v>
       </c>
       <c r="M9" s="88">
-        <v>-1.782301390876843</v>
+        <v>-1.924045874680379</v>
       </c>
       <c r="N9" s="70">
-        <v>-0.50205672982446281</v>
+        <v>-0.54198475343109276</v>
       </c>
       <c r="O9" s="86"/>
       <c r="P9" s="84">
-        <v>26116.901616168558</v>
+        <v>29018.779573520624</v>
       </c>
       <c r="Q9" s="84">
-        <v>-10840.502799998852</v>
+        <v>-13111.552799999597</v>
       </c>
       <c r="R9" s="83">
         <v>0</v>
       </c>
       <c r="S9" s="85">
-        <v>-10840.502799998852</v>
+        <v>-13111.552799999597</v>
       </c>
       <c r="T9" s="70">
-        <v>-0.41507614338477539</v>
+        <v>-0.45182991816664031</v>
       </c>
       <c r="U9" s="69"/>
       <c r="V9" s="83">
         <v>81743.041052170767</v>
       </c>
       <c r="W9" s="89">
-        <v>124256.45</v>
+        <v>73311.009999999995</v>
       </c>
       <c r="X9" s="90">
-        <v>-9.3243449334018873</v>
+        <v>-3.0384658457167806</v>
       </c>
       <c r="Y9" s="70">
-        <v>-2.6265760375779967</v>
+        <v>-0.85590587203289603</v>
       </c>
       <c r="Z9" s="91"/>
       <c r="AA9" s="85">
         <v>2901.8779573520624</v>
       </c>
       <c r="AB9" s="85">
-        <v>-11586.100000000049</v>
+        <v>-2227.5300000000134</v>
       </c>
       <c r="AC9" s="70">
-        <v>-3.9926213887272715</v>
+        <v>-0.76761670640091784</v>
       </c>
     </row>
     <row r="10" spans="1:29" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3703,72 +3703,72 @@
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="83">
-        <v>10965825.989999996</v>
+        <v>11615212.340000002</v>
       </c>
       <c r="E10" s="120">
-        <v>0.61834975758050048</v>
+        <v>0.65496787394170941</v>
       </c>
       <c r="F10" s="28"/>
       <c r="G10" s="84">
         <v>17734018.418487694</v>
       </c>
       <c r="H10" s="84">
-        <v>7980308.2883194629</v>
+        <v>8867009.2092438471</v>
       </c>
       <c r="I10" s="85">
-        <v>7915284.4800001495</v>
+        <v>8533590.4500001837</v>
       </c>
       <c r="J10" s="70">
-        <v>0.99185196787265895</v>
+        <v>0.96239783320670569</v>
       </c>
       <c r="K10" s="86"/>
       <c r="L10" s="87">
         <v>3.7</v>
       </c>
       <c r="M10" s="88">
-        <v>0.56169375818253786</v>
+        <v>0.57818548635761668</v>
       </c>
       <c r="N10" s="70">
-        <v>0.15180912383311834</v>
+        <v>0.15626634766422071</v>
       </c>
       <c r="O10" s="86"/>
       <c r="P10" s="84">
-        <v>295271.40666782012</v>
+        <v>328079.34074202238</v>
       </c>
       <c r="Q10" s="84">
-        <v>44459.658866551996</v>
+        <v>49339.981447100698</v>
       </c>
       <c r="R10" s="83">
         <v>0</v>
       </c>
       <c r="S10" s="85">
-        <v>44459.658866551996</v>
+        <v>49339.981447100698</v>
       </c>
       <c r="T10" s="70">
-        <v>0.15057217821490262</v>
+        <v>0.15039039439517179</v>
       </c>
       <c r="U10" s="69"/>
       <c r="V10" s="83">
         <v>886700.92092438473</v>
       </c>
       <c r="W10" s="89">
-        <v>1228459.5999999959</v>
+        <v>697396.39000000106</v>
       </c>
       <c r="X10" s="90">
-        <v>-2.9243520096229414</v>
+        <v>-3.3414958457127186</v>
       </c>
       <c r="Y10" s="70">
-        <v>-0.79036540800620037</v>
+        <v>-0.90310698532776179</v>
       </c>
       <c r="Z10" s="91"/>
       <c r="AA10" s="85">
         <v>32807.934074202232</v>
       </c>
       <c r="AB10" s="85">
-        <v>-35924.483000005828</v>
+        <v>-23303.471400000504</v>
       </c>
       <c r="AC10" s="70">
-        <v>-1.0949937572647777</v>
+        <v>-0.71029987280804296</v>
       </c>
     </row>
     <row r="11" spans="1:29" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3780,72 +3780,72 @@
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="83">
-        <v>5801376.5699999994</v>
+        <v>5954180.6500000013</v>
       </c>
       <c r="E11" s="120">
-        <v>0.66836406214676791</v>
+        <v>0.68596829010699512</v>
       </c>
       <c r="F11" s="28"/>
       <c r="G11" s="84">
         <v>8679964.8553306852</v>
       </c>
       <c r="H11" s="84">
-        <v>3905984.1848988086</v>
+        <v>4339982.4276653426</v>
       </c>
       <c r="I11" s="85">
-        <v>3611734.4699999406</v>
+        <v>3872352.4399999469</v>
       </c>
       <c r="J11" s="70">
-        <v>0.92466694667211224</v>
+        <v>0.89225071864704453</v>
       </c>
       <c r="K11" s="86"/>
       <c r="L11" s="87">
         <v>3.7</v>
       </c>
       <c r="M11" s="88">
-        <v>-1.0115108268210404</v>
+        <v>-0.98399838833018194</v>
       </c>
       <c r="N11" s="70">
-        <v>-0.27338130454622711</v>
+        <v>-0.26594551035950864</v>
       </c>
       <c r="O11" s="86"/>
       <c r="P11" s="84">
-        <v>144521.41484125593</v>
+        <v>160579.34982361767</v>
       </c>
       <c r="Q11" s="84">
-        <v>-36533.085200076923</v>
+        <v>-38103.885600063957</v>
       </c>
       <c r="R11" s="83">
         <v>0</v>
       </c>
       <c r="S11" s="85">
-        <v>-36533.085200076923</v>
+        <v>-38103.885600063957</v>
       </c>
       <c r="T11" s="70">
-        <v>-0.25278665615199869</v>
+        <v>-0.23729007273922664</v>
       </c>
       <c r="U11" s="69"/>
       <c r="V11" s="83">
         <v>433998.24276653427</v>
       </c>
       <c r="W11" s="89">
-        <v>425581.51999999984</v>
+        <v>257508.3699999993</v>
       </c>
       <c r="X11" s="90">
-        <v>-0.6018519789109309</v>
+        <v>-0.65916319535575196</v>
       </c>
       <c r="Y11" s="70">
-        <v>-0.1626626970029543</v>
+        <v>-0.17815221496101405</v>
       </c>
       <c r="Z11" s="91"/>
       <c r="AA11" s="85">
         <v>16057.934982361769</v>
       </c>
       <c r="AB11" s="85">
-        <v>-2561.370799999218</v>
+        <v>-1697.4004000005079</v>
       </c>
       <c r="AC11" s="70">
-        <v>-0.15950810629216389</v>
+        <v>-0.10570477473379691</v>
       </c>
     </row>
     <row r="12" spans="1:29" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3857,72 +3857,72 @@
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="83">
-        <v>38470330.080000006</v>
+        <v>38867035.659999989</v>
       </c>
       <c r="E12" s="120">
-        <v>1.4626306186781348</v>
+        <v>1.4777132479849755</v>
       </c>
       <c r="F12" s="28"/>
       <c r="G12" s="84">
         <v>26302150.104561534</v>
       </c>
       <c r="H12" s="84">
-        <v>11835967.547052689</v>
+        <v>13151075.052280765</v>
       </c>
       <c r="I12" s="85">
-        <v>12352396.450000048</v>
+        <v>13665756.440000055</v>
       </c>
       <c r="J12" s="70">
-        <v>1.0436321661828107</v>
+        <v>1.0391360695360057</v>
       </c>
       <c r="K12" s="86"/>
       <c r="L12" s="87">
         <v>2.95</v>
       </c>
       <c r="M12" s="88">
-        <v>-5.2134775628897225</v>
+        <v>-5.2025894133373631</v>
       </c>
       <c r="N12" s="70">
-        <v>-1.7672805297931262</v>
+        <v>-1.7635896316397841</v>
       </c>
       <c r="O12" s="86"/>
       <c r="P12" s="84">
-        <v>349161.04263805435</v>
+        <v>387956.71404228261</v>
       </c>
       <c r="Q12" s="84">
-        <v>-643989.41739993903</v>
+        <v>-710973.19779991184</v>
       </c>
       <c r="R12" s="83">
         <v>2078.3200000000002</v>
       </c>
       <c r="S12" s="85">
-        <v>-641911.09739993908</v>
+        <v>-708894.87779991189</v>
       </c>
       <c r="T12" s="70">
-        <v>-1.8384384825696432</v>
+        <v>-1.8272525056046611</v>
       </c>
       <c r="U12" s="69"/>
       <c r="V12" s="83">
         <v>1315107.5052280766</v>
       </c>
       <c r="W12" s="89">
-        <v>1540524.4300000004</v>
+        <v>1309777.9699999993</v>
       </c>
       <c r="X12" s="90">
-        <v>-5.6410075431261433</v>
+        <v>-5.0765077687174394</v>
       </c>
       <c r="Y12" s="70">
-        <v>-1.9122059468224213</v>
+        <v>-1.7208500910906572</v>
       </c>
       <c r="Z12" s="91"/>
       <c r="AA12" s="85">
         <v>38795.671404228262</v>
       </c>
       <c r="AB12" s="85">
-        <v>-86901.099300001035</v>
+        <v>-66490.980399999535</v>
       </c>
       <c r="AC12" s="70">
-        <v>-2.2399689489722263</v>
+        <v>-1.7138762648853867</v>
       </c>
     </row>
     <row r="13" spans="1:29" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3934,72 +3934,72 @@
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="83">
-        <v>2667544.4899999998</v>
+        <v>2672751.3500000006</v>
       </c>
       <c r="E13" s="120">
-        <v>1.0575876686500489</v>
+        <v>1.0596520057019823</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" s="84">
         <v>2522291.597258287</v>
       </c>
       <c r="H13" s="84">
-        <v>1135031.2187662292</v>
+        <v>1261145.7986291435</v>
       </c>
       <c r="I13" s="85">
-        <v>1413008.9699999979</v>
+        <v>1518181.8399999964</v>
       </c>
       <c r="J13" s="70">
-        <v>1.2449075819570219</v>
+        <v>1.2038115193740877</v>
       </c>
       <c r="K13" s="86"/>
       <c r="L13" s="87">
         <v>4.05</v>
       </c>
       <c r="M13" s="88">
-        <v>-4.2964847420608203</v>
+        <v>-4.4085774204756021</v>
       </c>
       <c r="N13" s="70">
-        <v>-1.0608604301384743</v>
+        <v>-1.0885376346853339</v>
       </c>
       <c r="O13" s="86"/>
       <c r="P13" s="84">
-        <v>45968.764360032277</v>
+        <v>51076.404844480305</v>
       </c>
       <c r="Q13" s="84">
-        <v>-60709.714800000664</v>
+        <v>-66930.221800000872</v>
       </c>
       <c r="R13" s="83">
-        <v>214.4</v>
+        <v>858.75</v>
       </c>
       <c r="S13" s="85">
-        <v>-60495.314800000662</v>
+        <v>-66071.471800000872</v>
       </c>
       <c r="T13" s="70">
-        <v>-1.3160091562652172</v>
+        <v>-1.2935810968132586</v>
       </c>
       <c r="U13" s="69"/>
       <c r="V13" s="83">
         <v>126114.57986291435</v>
       </c>
       <c r="W13" s="89">
-        <v>220313.87999999998</v>
+        <v>104697.77</v>
       </c>
       <c r="X13" s="90">
-        <v>-6.5620959060772837</v>
+        <v>-5.9521200881355441</v>
       </c>
       <c r="Y13" s="70">
-        <v>-1.6202705940931565</v>
+        <v>-1.469659281021122</v>
       </c>
       <c r="Z13" s="92"/>
       <c r="AA13" s="85">
         <v>5107.6404844480312</v>
       </c>
       <c r="AB13" s="85">
-        <v>-14457.208100000016</v>
+        <v>-6231.7369999999491</v>
       </c>
       <c r="AC13" s="70">
-        <v>-2.8305062081052808</v>
+        <v>-1.2200813700523003</v>
       </c>
     </row>
     <row r="14" spans="1:29" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4011,72 +4011,72 @@
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="83">
-        <v>2283255.41</v>
+        <v>2243161.67</v>
       </c>
       <c r="E14" s="120">
-        <v>1.1646335342876586</v>
+        <v>1.1441826841924383</v>
       </c>
       <c r="F14" s="28"/>
       <c r="G14" s="84">
         <v>1960492.5865341325</v>
       </c>
       <c r="H14" s="84">
-        <v>882221.66394035961</v>
+        <v>980246.29326706624</v>
       </c>
       <c r="I14" s="85">
-        <v>885769.91000000329</v>
+        <v>942217.17000000412</v>
       </c>
       <c r="J14" s="70">
-        <v>1.004021943922569</v>
+        <v>0.96120452224275721</v>
       </c>
       <c r="K14" s="86"/>
       <c r="L14" s="87">
         <v>4.05</v>
       </c>
       <c r="M14" s="88">
-        <v>-2.556329532575409</v>
+        <v>-2.4195002305037931</v>
       </c>
       <c r="N14" s="70">
-        <v>-0.63119247717911331</v>
+        <v>-0.59740746432192426</v>
       </c>
       <c r="O14" s="86"/>
       <c r="P14" s="84">
-        <v>35729.977389584557</v>
+        <v>39699.974877316177</v>
       </c>
       <c r="Q14" s="84">
-        <v>-22643.197799996706</v>
+        <v>-22796.946599996416</v>
       </c>
       <c r="R14" s="83">
         <v>0</v>
       </c>
       <c r="S14" s="85">
-        <v>-22643.197799996706</v>
+        <v>-22796.946599996416</v>
       </c>
       <c r="T14" s="70">
-        <v>-0.63373109792667526</v>
+        <v>-0.57423075632781229</v>
       </c>
       <c r="U14" s="69"/>
       <c r="V14" s="83">
         <v>98024.629326706621</v>
       </c>
       <c r="W14" s="89">
-        <v>119729.38000000003</v>
+        <v>56218.880000000005</v>
       </c>
       <c r="X14" s="90">
-        <v>-0.13749123231058921</v>
+        <v>-0.30761694292023645</v>
       </c>
       <c r="Y14" s="70">
-        <v>-3.3948452422367707E-2</v>
+        <v>-7.5954800721046045E-2</v>
       </c>
       <c r="Z14" s="91"/>
       <c r="AA14" s="85">
         <v>3969.9974877316181</v>
       </c>
       <c r="AB14" s="85">
-        <v>-164.61739999982819</v>
+        <v>-172.93879999999623</v>
       </c>
       <c r="AC14" s="70">
-        <v>-4.1465366290165458E-2</v>
+        <v>-4.3561438145596966E-2</v>
       </c>
     </row>
     <row r="15" spans="1:29" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4088,72 +4088,72 @@
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="83">
-        <v>9627462.540000001</v>
+        <v>10202868.999999996</v>
       </c>
       <c r="E15" s="120">
-        <v>0.61124505559774178</v>
+        <v>0.64777745987069535</v>
       </c>
       <c r="F15" s="28"/>
       <c r="G15" s="84">
         <v>15750577.36963651</v>
       </c>
       <c r="H15" s="84">
-        <v>7087759.8163364287</v>
+        <v>7875288.6848182548</v>
       </c>
       <c r="I15" s="85">
-        <v>5879688.9700000267</v>
+        <v>6341324.0400000252</v>
       </c>
       <c r="J15" s="70">
-        <v>0.82955533516359503</v>
+        <v>0.80521797914845195</v>
       </c>
       <c r="K15" s="86"/>
       <c r="L15" s="87">
         <v>3</v>
       </c>
       <c r="M15" s="88">
-        <v>-7.4631290250027806</v>
+        <v>-7.4640664270480261</v>
       </c>
       <c r="N15" s="70">
-        <v>-2.4877096750009269</v>
+        <v>-2.488022142349342</v>
       </c>
       <c r="O15" s="86"/>
       <c r="P15" s="84">
-        <v>212632.79449009284</v>
+        <v>236258.66054454766</v>
       </c>
       <c r="Q15" s="84">
-        <v>-438808.77409995906</v>
+        <v>-473320.63869996741</v>
       </c>
       <c r="R15" s="83">
         <v>0</v>
       </c>
       <c r="S15" s="85">
-        <v>-438808.77409995906</v>
+        <v>-473320.63869996741</v>
       </c>
       <c r="T15" s="70">
-        <v>-2.0636928332351121</v>
+        <v>-2.003400161539139</v>
       </c>
       <c r="U15" s="69"/>
       <c r="V15" s="83">
         <v>787528.86848182546</v>
       </c>
       <c r="W15" s="89">
-        <v>1189909.6700000002</v>
+        <v>459051.4300000004</v>
       </c>
       <c r="X15" s="90">
-        <v>-15.569759543175966</v>
+        <v>-7.5288415069307089</v>
       </c>
       <c r="Y15" s="70">
-        <v>-5.1899198477253217</v>
+        <v>-2.5096138356435698</v>
       </c>
       <c r="Z15" s="91"/>
       <c r="AA15" s="85">
         <v>23625.866054454764</v>
       </c>
       <c r="AB15" s="85">
-        <v>-185266.07439999867</v>
+        <v>-34561.254599998996</v>
       </c>
       <c r="AC15" s="70">
-        <v>-7.8416627764240587</v>
+        <v>-1.462856621651011</v>
       </c>
     </row>
     <row r="16" spans="1:29" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -4165,72 +4165,72 @@
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="83">
-        <v>13316491.969999999</v>
+        <v>13267350.659999998</v>
       </c>
       <c r="E16" s="120">
-        <v>0.74605706295375718</v>
+        <v>0.74330391884561708</v>
       </c>
       <c r="F16" s="28"/>
       <c r="G16" s="84">
         <v>17849160.112871144</v>
       </c>
       <c r="H16" s="84">
-        <v>8032122.0507920142</v>
+        <v>8924580.056435572</v>
       </c>
       <c r="I16" s="85">
-        <v>8017121.3800000036</v>
+        <v>8649861.6200000178</v>
       </c>
       <c r="J16" s="70">
-        <v>0.99813241498359306</v>
+        <v>0.96921777442766588</v>
       </c>
       <c r="K16" s="86"/>
       <c r="L16" s="87">
         <v>2.6</v>
       </c>
       <c r="M16" s="88">
-        <v>-5.2443152831499829</v>
+        <v>-5.1280256411775156</v>
       </c>
       <c r="N16" s="70">
-        <v>-2.0170443396730704</v>
+        <v>-1.9723175542990443</v>
       </c>
       <c r="O16" s="86"/>
       <c r="P16" s="84">
-        <v>208835.17332059238</v>
+        <v>232039.08146732487</v>
       </c>
       <c r="Q16" s="84">
-        <v>-420443.12180002505</v>
+        <v>-443567.12179997377</v>
       </c>
       <c r="R16" s="83">
         <v>864.47</v>
       </c>
       <c r="S16" s="85">
-        <v>-419578.65180002508</v>
+        <v>-442702.6517999738</v>
       </c>
       <c r="T16" s="70">
-        <v>-2.0091378532097695</v>
+        <v>-1.9078796942329477</v>
       </c>
       <c r="U16" s="69"/>
       <c r="V16" s="83">
         <v>892458.00564355718</v>
       </c>
       <c r="W16" s="89">
-        <v>854327.71999999881</v>
+        <v>643026.2699999999</v>
       </c>
       <c r="X16" s="90">
-        <v>-3.3551430123325288</v>
+        <v>-3.4906785379080341</v>
       </c>
       <c r="Y16" s="70">
-        <v>-1.2904396201278956</v>
+        <v>-1.3425686684261668</v>
       </c>
       <c r="Z16" s="91"/>
       <c r="AA16" s="85">
         <v>23203.908146732487</v>
       </c>
       <c r="AB16" s="85">
-        <v>-28663.916799999774</v>
+        <v>-22445.980000000563</v>
       </c>
       <c r="AC16" s="70">
-        <v>-1.2353055622673697</v>
+        <v>-0.96733618570031044</v>
       </c>
     </row>
     <row r="17" spans="1:29" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="83">
-        <v>3977.08</v>
+        <v>3915.46</v>
       </c>
       <c r="E18" s="120"/>
       <c r="F18" s="28"/>
       <c r="G18" s="84"/>
       <c r="H18" s="84"/>
       <c r="I18" s="85">
-        <v>1529.6900000000003</v>
+        <v>1620.8900000000003</v>
       </c>
       <c r="J18" s="70" t="s">
         <v>69</v>
@@ -4326,7 +4326,7 @@
       <c r="K18" s="86"/>
       <c r="L18" s="87"/>
       <c r="M18" s="88">
-        <v>8.6226621080088321</v>
+        <v>7.9943734614933994</v>
       </c>
       <c r="N18" s="70" t="s">
         <v>69</v>
@@ -4336,13 +4336,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="84">
-        <v>131.90000000000032</v>
+        <v>129.58000000000038</v>
       </c>
       <c r="R18" s="83">
         <v>0</v>
       </c>
       <c r="S18" s="85">
-        <v>131.90000000000032</v>
+        <v>129.58000000000038</v>
       </c>
       <c r="T18" s="70" t="s">
         <v>69</v>
@@ -4352,10 +4352,10 @@
         <v>0</v>
       </c>
       <c r="W18" s="89">
-        <v>114.91</v>
+        <v>91.2</v>
       </c>
       <c r="X18" s="90">
-        <v>8.4500913758593637</v>
+        <v>-2.5438596491227994</v>
       </c>
       <c r="Y18" s="70">
         <v>0</v>
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="85">
-        <v>9.7099999999999937</v>
+        <v>-2.3199999999999932</v>
       </c>
       <c r="AC18" s="70" t="s">
         <v>69</v>
@@ -4471,72 +4471,72 @@
       </c>
       <c r="C22" s="28"/>
       <c r="D22" s="68">
-        <v>114347557.48999999</v>
+        <v>115973530.59999998</v>
       </c>
       <c r="E22" s="122">
-        <v>1.146100145523411</v>
+        <v>1.1623971968893845</v>
       </c>
       <c r="F22" s="28"/>
       <c r="G22" s="41">
         <v>99770999.887430221</v>
       </c>
       <c r="H22" s="41">
-        <v>44896949.949343599</v>
+        <v>49885499.94371511</v>
       </c>
       <c r="I22" s="41">
-        <v>44613205.320000179</v>
+        <v>48447957.180000246</v>
       </c>
       <c r="J22" s="44">
-        <v>0.99368009119408862</v>
+        <v>0.97118315411618972</v>
       </c>
       <c r="K22" s="45"/>
       <c r="L22" s="43">
         <v>3.153092976937192</v>
       </c>
       <c r="M22" s="43">
-        <v>-4.0154126973932911</v>
+        <v>-3.9814760836790826</v>
       </c>
       <c r="N22" s="44">
-        <v>-1.2734837592051369</v>
+        <v>-1.2627207991648106</v>
       </c>
       <c r="O22" s="45"/>
       <c r="P22" s="41">
-        <v>1415642.575711759</v>
+        <v>1572936.1952352882</v>
       </c>
       <c r="Q22" s="41">
-        <v>-1791404.3111334264</v>
+        <v>-1928943.8281527925</v>
       </c>
       <c r="R22" s="40">
-        <v>3157.1900000000005</v>
+        <v>3801.54</v>
       </c>
       <c r="S22" s="41">
-        <v>-1788247.1211334264</v>
+        <v>-1925142.2881527927</v>
       </c>
       <c r="T22" s="44">
-        <v>-1.2632052410788286</v>
+        <v>-1.2239163253947625</v>
       </c>
       <c r="U22" s="42"/>
       <c r="V22" s="40">
         <v>4988549.994371511</v>
       </c>
       <c r="W22" s="40">
-        <v>6714669.0299999947</v>
+        <v>3912886.52</v>
       </c>
       <c r="X22" s="46">
-        <v>-7.3699433849832729</v>
+        <v>-4.2156096313265889</v>
       </c>
       <c r="Y22" s="44">
-        <v>-2.3373695095227376</v>
+        <v>-1.336975998538898</v>
       </c>
       <c r="Z22" s="45"/>
       <c r="AA22" s="41">
         <v>157293.61952352879</v>
       </c>
       <c r="AB22" s="41">
-        <v>-494867.30600000505</v>
+        <v>-164952.02099999978</v>
       </c>
       <c r="AC22" s="44">
-        <v>-3.1461371891564887</v>
+        <v>-1.0486885704561297</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="14.5" x14ac:dyDescent="0.35">
@@ -5351,51 +5351,51 @@
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="33">
-        <v>27019.549999999992</v>
+        <v>25004.949999999997</v>
       </c>
       <c r="F8" s="123">
-        <v>0.34640448717948708</v>
+        <v>0.32057628205128202</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="35">
         <v>78000</v>
       </c>
       <c r="I8" s="35">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="J8" s="35">
-        <v>29024.470000000012</v>
+        <v>31685.560000000019</v>
       </c>
       <c r="K8" s="70">
-        <v>0.96748233333333378</v>
+        <v>0.96016848484848549</v>
       </c>
       <c r="L8" s="36"/>
       <c r="M8" s="35">
         <v>15522</v>
       </c>
       <c r="N8" s="35">
-        <v>5970</v>
+        <v>6567</v>
       </c>
       <c r="O8" s="37">
         <v>0</v>
       </c>
       <c r="P8" s="35">
-        <v>6792.0299999999943</v>
+        <v>7380.2399999999934</v>
       </c>
       <c r="Q8" s="115">
-        <v>1.1376934673366825</v>
+        <v>1.1238373686614882</v>
       </c>
       <c r="R8" s="36"/>
       <c r="S8" s="127">
         <v>0.19900000000000001</v>
       </c>
       <c r="T8" s="127">
-        <v>0.23401047460987201</v>
+        <v>0.23292124235771716</v>
       </c>
       <c r="U8" s="36"/>
       <c r="V8" s="35"/>
       <c r="W8" s="38">
-        <v>6.677641314380554</v>
+        <v>6.4883814583046542</v>
       </c>
       <c r="X8" s="69" t="s">
         <v>69</v>
@@ -5406,38 +5406,38 @@
         <v>3000</v>
       </c>
       <c r="AB8" s="33">
-        <v>2932.08</v>
+        <v>2661.09</v>
       </c>
       <c r="AC8" s="36"/>
       <c r="AD8" s="35">
         <v>597</v>
       </c>
       <c r="AE8" s="35">
-        <v>762.29</v>
+        <v>588.21</v>
       </c>
       <c r="AF8" s="115">
-        <v>1.2768676716917922</v>
+        <v>0.9852763819095478</v>
       </c>
       <c r="AG8" s="36"/>
       <c r="AH8" s="35">
-        <v>679.20299999999941</v>
+        <v>670.93090909090847</v>
       </c>
       <c r="AI8" s="35">
-        <v>17659.277999999984</v>
+        <v>17444.203636363622</v>
       </c>
       <c r="AJ8" s="115">
-        <v>1.1376934673366823</v>
+        <v>1.1238373686614884</v>
       </c>
       <c r="AK8" s="36"/>
       <c r="AL8" s="108">
         <v>0.19900000000000001</v>
       </c>
       <c r="AM8" s="108">
-        <v>0.25998267441543205</v>
+        <v>0.22104100199542293</v>
       </c>
       <c r="AN8" s="36"/>
       <c r="AO8" s="38">
-        <v>8.9990723309050278</v>
+        <v>4.4241269554956633</v>
       </c>
       <c r="AP8" s="70">
         <v>0</v>
@@ -5453,51 +5453,51 @@
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="33">
-        <v>96036.549999999974</v>
+        <v>96634.83</v>
       </c>
       <c r="F9" s="123">
-        <v>0.83510043478260843</v>
+        <v>0.84030286956521738</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="35">
         <v>115000</v>
       </c>
       <c r="I9" s="35">
-        <v>44516.129032258061</v>
+        <v>48225.806451612902</v>
       </c>
       <c r="J9" s="35">
-        <v>42609.940000000242</v>
+        <v>46467.060000000296</v>
       </c>
       <c r="K9" s="70">
-        <v>0.9571798115942084</v>
+        <v>0.96353101003345099</v>
       </c>
       <c r="L9" s="36"/>
       <c r="M9" s="35">
         <v>23000</v>
       </c>
       <c r="N9" s="35">
-        <v>8903.2258064516118</v>
+        <v>9645.1612903225796</v>
       </c>
       <c r="O9" s="37">
         <v>0</v>
       </c>
       <c r="P9" s="35">
-        <v>10161.739999999985</v>
+        <v>11143.619999999983</v>
       </c>
       <c r="Q9" s="115">
-        <v>1.1413548550724621</v>
+        <v>1.1553585953177241</v>
       </c>
       <c r="R9" s="36"/>
       <c r="S9" s="127">
         <v>0.2</v>
       </c>
       <c r="T9" s="127">
-        <v>0.23848285165386121</v>
+        <v>0.23981762564706938</v>
       </c>
       <c r="U9" s="36"/>
       <c r="V9" s="35"/>
       <c r="W9" s="38">
-        <v>8.7201014598944706</v>
+        <v>8.8343656775363009</v>
       </c>
       <c r="X9" s="69" t="s">
         <v>69</v>
@@ -5508,38 +5508,38 @@
         <v>3709.6774193548385</v>
       </c>
       <c r="AB9" s="33">
-        <v>2112.8500000000004</v>
+        <v>3857.1200000000008</v>
       </c>
       <c r="AC9" s="36"/>
       <c r="AD9" s="35">
         <v>741.93548387096769</v>
       </c>
       <c r="AE9" s="35">
-        <v>510.95999999999987</v>
+        <v>981.88</v>
       </c>
       <c r="AF9" s="115">
-        <v>0.68868521739130417</v>
+        <v>1.3234034782608697</v>
       </c>
       <c r="AG9" s="36"/>
       <c r="AH9" s="35">
-        <v>846.81166666666547</v>
+        <v>857.2015384615371</v>
       </c>
       <c r="AI9" s="35">
-        <v>26251.16166666663</v>
+        <v>26573.24769230765</v>
       </c>
       <c r="AJ9" s="115">
-        <v>1.1413548550724621</v>
+        <v>1.1553585953177239</v>
       </c>
       <c r="AK9" s="36"/>
       <c r="AL9" s="108">
         <v>0.2</v>
       </c>
       <c r="AM9" s="108">
-        <v>0.24183448896040882</v>
+        <v>0.25456299000290367</v>
       </c>
       <c r="AN9" s="36"/>
       <c r="AO9" s="38">
-        <v>9.7205196772132574</v>
+        <v>10.096652424606983</v>
       </c>
       <c r="AP9" s="70">
         <v>0</v>
@@ -5555,51 +5555,51 @@
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="33">
-        <v>143419.64999999997</v>
+        <v>148932.17999999996</v>
       </c>
       <c r="F10" s="123">
-        <v>0.75484026315789454</v>
+        <v>0.78385357894736818</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="35">
         <v>190000</v>
       </c>
       <c r="I10" s="35">
-        <v>73548.387096774197</v>
+        <v>79677.419354838712</v>
       </c>
       <c r="J10" s="35">
-        <v>81347.540000000183</v>
+        <v>86051.430000000037</v>
       </c>
       <c r="K10" s="70">
-        <v>1.1060411140350901</v>
+        <v>1.0799977044534417</v>
       </c>
       <c r="L10" s="36"/>
       <c r="M10" s="35">
         <v>36480</v>
       </c>
       <c r="N10" s="35">
-        <v>14121.290322580644</v>
+        <v>15298.064516129032</v>
       </c>
       <c r="O10" s="37">
         <v>0</v>
       </c>
       <c r="P10" s="35">
-        <v>15487.230000000014</v>
+        <v>16561.200000000023</v>
       </c>
       <c r="Q10" s="115">
-        <v>1.0967290981359661</v>
+        <v>1.0825683198380582</v>
       </c>
       <c r="R10" s="36"/>
       <c r="S10" s="127">
         <v>0.192</v>
       </c>
       <c r="T10" s="127">
-        <v>0.19038350760207351</v>
+        <v>0.19245699926195317</v>
       </c>
       <c r="U10" s="36"/>
       <c r="V10" s="35"/>
       <c r="W10" s="38">
-        <v>4.2307855898286988</v>
+        <v>4.3586841032159205</v>
       </c>
       <c r="X10" s="69" t="s">
         <v>69</v>
@@ -5610,38 +5610,38 @@
         <v>6129.0322580645161</v>
       </c>
       <c r="AB10" s="33">
-        <v>6073.8200000000015</v>
+        <v>4703.8900000000012</v>
       </c>
       <c r="AC10" s="36"/>
       <c r="AD10" s="35">
         <v>1176.7741935483871</v>
       </c>
       <c r="AE10" s="35">
-        <v>1253.3500000000001</v>
+        <v>1073.97</v>
       </c>
       <c r="AF10" s="115">
-        <v>1.0650726425438597</v>
+        <v>0.91263898026315793</v>
       </c>
       <c r="AG10" s="36"/>
       <c r="AH10" s="35">
-        <v>1290.6025000000011</v>
+        <v>1273.9384615384633</v>
       </c>
       <c r="AI10" s="35">
-        <v>40008.677500000034</v>
+        <v>39492.092307692365</v>
       </c>
       <c r="AJ10" s="115">
-        <v>1.0967290981359659</v>
+        <v>1.0825683198380582</v>
       </c>
       <c r="AK10" s="36"/>
       <c r="AL10" s="108">
         <v>0.192</v>
       </c>
       <c r="AM10" s="108">
-        <v>0.20635283890533468</v>
+        <v>0.22831528798505063</v>
       </c>
       <c r="AN10" s="36"/>
       <c r="AO10" s="38">
-        <v>5.3291009611743556</v>
+        <v>6.5705192936059227</v>
       </c>
       <c r="AP10" s="70">
         <v>0</v>
@@ -5657,30 +5657,30 @@
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="33">
-        <v>23530.61</v>
+        <v>23515.64</v>
       </c>
       <c r="F11" s="123">
-        <v>0.49022104166666669</v>
+        <v>0.48990916666666667</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="35">
         <v>48000</v>
       </c>
       <c r="I11" s="35">
-        <v>18461.538461538461</v>
+        <v>20307.692307692309</v>
       </c>
       <c r="J11" s="35">
         <v>11605.849999999993</v>
       </c>
       <c r="K11" s="70">
-        <v>0.62865020833333296</v>
+        <v>0.57150018939393898</v>
       </c>
       <c r="L11" s="36"/>
       <c r="M11" s="35">
         <v>5760</v>
       </c>
       <c r="N11" s="35">
-        <v>2215.3846153846152</v>
+        <v>2436.9230769230771</v>
       </c>
       <c r="O11" s="37">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>5296.34</v>
       </c>
       <c r="Q11" s="115">
-        <v>2.3907090277777781</v>
+        <v>2.1733718434343432</v>
       </c>
       <c r="R11" s="36"/>
       <c r="S11" s="127">
@@ -5712,38 +5712,38 @@
         <v>1846.1538461538462</v>
       </c>
       <c r="AB11" s="33">
-        <v>66.88</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="36"/>
       <c r="AD11" s="35">
         <v>221.53846153846155</v>
       </c>
       <c r="AE11" s="35">
-        <v>19.069999999999993</v>
+        <v>0</v>
       </c>
       <c r="AF11" s="115">
-        <v>8.6079861111111072E-2</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="36"/>
       <c r="AH11" s="35">
-        <v>529.63400000000001</v>
+        <v>481.48545454545456</v>
       </c>
       <c r="AI11" s="35">
-        <v>13770.484</v>
+        <v>12518.621818181819</v>
       </c>
       <c r="AJ11" s="115">
-        <v>2.3907090277777781</v>
+        <v>2.1733718434343436</v>
       </c>
       <c r="AK11" s="36"/>
       <c r="AL11" s="108">
         <v>0.12</v>
       </c>
-      <c r="AM11" s="108">
-        <v>0.28513755980861238</v>
+      <c r="AM11" s="108" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="AN11" s="36"/>
       <c r="AO11" s="38">
-        <v>12.799043062200941</v>
+        <v>0</v>
       </c>
       <c r="AP11" s="70">
         <v>0</v>
@@ -5757,51 +5757,51 @@
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="27">
-        <v>290006.35999999993</v>
+        <v>294087.59999999998</v>
       </c>
       <c r="F12" s="124">
-        <v>0.6728685846867748</v>
+        <v>0.68233781902552204</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="29">
         <v>431000</v>
       </c>
       <c r="I12" s="29">
-        <v>166526.05459057071</v>
+        <v>181210.91811414395</v>
       </c>
       <c r="J12" s="29">
-        <v>164587.80000000042</v>
+        <v>175809.90000000034</v>
       </c>
       <c r="K12" s="31">
-        <v>0.98836065265981488</v>
+        <v>0.97019485265925576</v>
       </c>
       <c r="L12" s="39"/>
       <c r="M12" s="29">
         <v>80762</v>
       </c>
       <c r="N12" s="29">
-        <v>31209.900744416875</v>
+        <v>33947.148883374692</v>
       </c>
       <c r="O12" s="27">
         <v>0</v>
       </c>
       <c r="P12" s="29">
-        <v>37737.339999999997</v>
+        <v>40381.399999999994</v>
       </c>
       <c r="Q12" s="31">
-        <v>1.2091464278927837</v>
+        <v>1.1895373051424776</v>
       </c>
       <c r="R12" s="39"/>
       <c r="S12" s="128">
         <v>0.18738283062645011</v>
       </c>
       <c r="T12" s="128">
-        <v>0.22928394449649306</v>
+        <v>0.22968786171882194</v>
       </c>
       <c r="U12" s="39"/>
       <c r="V12" s="29"/>
       <c r="W12" s="32">
-        <v>7.8703099500693696</v>
+        <v>7.8322153644363421</v>
       </c>
       <c r="X12" s="30" t="s">
         <v>69</v>
@@ -5812,34 +5812,34 @@
         <v>14684.863523573202</v>
       </c>
       <c r="AB12" s="27">
-        <v>11185.630000000001</v>
+        <v>11222.100000000002</v>
       </c>
       <c r="AC12" s="39"/>
       <c r="AD12" s="29">
         <v>2737.2481389578165</v>
       </c>
       <c r="AE12" s="29">
-        <v>2545.67</v>
+        <v>2644.0600000000004</v>
       </c>
       <c r="AF12" s="31">
-        <v>0.93001067888906919</v>
+        <v>0.96595553847255633</v>
       </c>
       <c r="AG12" s="39"/>
       <c r="AH12" s="29">
-        <v>3346.251166666666</v>
+        <v>3283.5563636363636</v>
       </c>
       <c r="AI12" s="29">
-        <v>97689.601166666645</v>
+        <v>96028.165454545466</v>
       </c>
       <c r="AJ12" s="31">
-        <v>1.2095985880323252</v>
+        <v>1.189026589912898</v>
       </c>
       <c r="AK12" s="39"/>
       <c r="AL12" s="80">
         <v>0.18738283062645011</v>
       </c>
       <c r="AM12" s="80">
-        <v>0.22758396263777719</v>
+        <v>0.23561187300059702</v>
       </c>
       <c r="AN12" s="39"/>
       <c r="AO12" s="32">
@@ -5904,51 +5904,51 @@
       </c>
       <c r="D14" s="34"/>
       <c r="E14" s="33">
-        <v>888013.17000000109</v>
+        <v>908498.32000000135</v>
       </c>
       <c r="F14" s="131">
-        <v>1.7584419207920814</v>
+        <v>1.7990065742574284</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="35">
         <v>505000</v>
       </c>
       <c r="I14" s="35">
-        <v>194230.76923076922</v>
+        <v>213653.84615384613</v>
       </c>
       <c r="J14" s="35">
-        <v>170471.8500000005</v>
+        <v>190452.03000000046</v>
       </c>
       <c r="K14" s="70">
-        <v>0.87767685148515118</v>
+        <v>0.89140464086408866</v>
       </c>
       <c r="L14" s="36"/>
       <c r="M14" s="35">
         <v>51510</v>
       </c>
       <c r="N14" s="35">
-        <v>19811.538461538461</v>
+        <v>21792.692307692309</v>
       </c>
       <c r="O14" s="37">
         <v>0</v>
       </c>
       <c r="P14" s="35">
-        <v>20655.836900000068</v>
+        <v>22855.925700000105</v>
       </c>
       <c r="Q14" s="115">
-        <v>1.042616500485346</v>
+        <v>1.0487885286175724</v>
       </c>
       <c r="R14" s="36"/>
       <c r="S14" s="127">
         <v>0.10199999999999999</v>
       </c>
       <c r="T14" s="127">
-        <v>0.12116860877617042</v>
+        <v>0.12000883214529165</v>
       </c>
       <c r="U14" s="36"/>
       <c r="V14" s="35"/>
       <c r="W14" s="38">
-        <v>1.578012381516753</v>
+        <v>1.4533295864587359</v>
       </c>
       <c r="X14" s="69" t="s">
         <v>69</v>
@@ -5959,38 +5959,38 @@
         <v>19423.076923076922</v>
       </c>
       <c r="AB14" s="33">
-        <v>19472.429999999982</v>
+        <v>19980.179999999993</v>
       </c>
       <c r="AC14" s="36"/>
       <c r="AD14" s="35">
         <v>1981.1538461538462</v>
       </c>
       <c r="AE14" s="35">
-        <v>1987.8344499999996</v>
+        <v>2200.0888000000004</v>
       </c>
       <c r="AF14" s="115">
-        <v>1.00337207726655</v>
+        <v>1.1105088099398177</v>
       </c>
       <c r="AG14" s="36"/>
       <c r="AH14" s="35">
-        <v>2065.5836900000068</v>
+        <v>2077.8114272727366</v>
       </c>
       <c r="AI14" s="35">
-        <v>53705.175940000176</v>
+        <v>54023.097109091155</v>
       </c>
       <c r="AJ14" s="115">
-        <v>1.042616500485346</v>
+        <v>1.0487885286175724</v>
       </c>
       <c r="AK14" s="36"/>
       <c r="AL14" s="108">
         <v>0.10199999999999999</v>
       </c>
       <c r="AM14" s="108">
-        <v>0.10208456006774715</v>
+        <v>0.11011356254047767</v>
       </c>
       <c r="AN14" s="36"/>
       <c r="AO14" s="38">
-        <v>0.18669703781182292</v>
+        <v>0.3895300242540507</v>
       </c>
       <c r="AP14" s="70">
         <v>0</v>
@@ -6006,51 +6006,51 @@
       </c>
       <c r="D15" s="34"/>
       <c r="E15" s="33">
-        <v>1232376.2599999991</v>
+        <v>1227720.6499999999</v>
       </c>
       <c r="F15" s="131">
-        <v>1.4413757426900573</v>
+        <v>1.4359305847953214</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="35">
         <v>855000</v>
       </c>
       <c r="I15" s="35">
-        <v>330967.74193548388</v>
+        <v>358548.38709677418</v>
       </c>
       <c r="J15" s="35">
-        <v>357644.74999998912</v>
+        <v>384155.28999998589</v>
       </c>
       <c r="K15" s="70">
-        <v>1.080603045808934</v>
+        <v>1.0714182627080129</v>
       </c>
       <c r="L15" s="36"/>
       <c r="M15" s="35">
         <v>106020</v>
       </c>
       <c r="N15" s="35">
-        <v>41040</v>
+        <v>44460</v>
       </c>
       <c r="O15" s="37">
         <v>0</v>
       </c>
       <c r="P15" s="35">
-        <v>49563.357249999979</v>
+        <v>53421.885249999999</v>
       </c>
       <c r="Q15" s="115">
-        <v>1.2076841435185179</v>
+        <v>1.20157186797121</v>
       </c>
       <c r="R15" s="36"/>
       <c r="S15" s="127">
         <v>0.124</v>
       </c>
       <c r="T15" s="127">
-        <v>0.13858265010181609</v>
+        <v>0.13906325551315971</v>
       </c>
       <c r="U15" s="36"/>
       <c r="V15" s="35"/>
       <c r="W15" s="38">
-        <v>3.8463299824725938</v>
+        <v>3.8852478772287271</v>
       </c>
       <c r="X15" s="69" t="s">
         <v>69</v>
@@ -6061,38 +6061,38 @@
         <v>27580.645161290322</v>
       </c>
       <c r="AB15" s="33">
-        <v>23814.179999999989</v>
+        <v>26510.540000000052</v>
       </c>
       <c r="AC15" s="36"/>
       <c r="AD15" s="35">
         <v>3420</v>
       </c>
       <c r="AE15" s="35">
-        <v>3362.8294999999985</v>
+        <v>3858.5279999999993</v>
       </c>
       <c r="AF15" s="115">
-        <v>0.98328347953216333</v>
+        <v>1.1282245614035087</v>
       </c>
       <c r="AG15" s="36"/>
       <c r="AH15" s="35">
-        <v>4130.2797708333319</v>
+        <v>4109.3757884615388</v>
       </c>
       <c r="AI15" s="35">
-        <v>128038.67289583328</v>
+        <v>127390.64944230771</v>
       </c>
       <c r="AJ15" s="115">
-        <v>1.2076841435185179</v>
+        <v>1.2015718679712102</v>
       </c>
       <c r="AK15" s="36"/>
       <c r="AL15" s="108">
         <v>0.124</v>
       </c>
       <c r="AM15" s="108">
-        <v>0.14121122373308675</v>
+        <v>0.14554694095254159</v>
       </c>
       <c r="AN15" s="36"/>
       <c r="AO15" s="38">
-        <v>4.3070536125954639</v>
+        <v>4.4102760637845364</v>
       </c>
       <c r="AP15" s="70">
         <v>0</v>
@@ -6108,51 +6108,51 @@
       </c>
       <c r="D16" s="34"/>
       <c r="E16" s="33">
-        <v>1790297.2400000007</v>
+        <v>1754287.7199999995</v>
       </c>
       <c r="F16" s="131">
-        <v>1.4555262113821144</v>
+        <v>1.4262501788617883</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="35">
         <v>1230000</v>
       </c>
       <c r="I16" s="35">
-        <v>476129.03225806454</v>
+        <v>515806.45161290327</v>
       </c>
       <c r="J16" s="35">
-        <v>491716.7299999785</v>
+        <v>535460.69999997644</v>
       </c>
       <c r="K16" s="70">
-        <v>1.0327383895663504</v>
+        <v>1.0381039212007046</v>
       </c>
       <c r="L16" s="36"/>
       <c r="M16" s="35">
         <v>170891.33832238274</v>
       </c>
       <c r="N16" s="35">
-        <v>66151.485802212672</v>
+        <v>71664.109619063733</v>
       </c>
       <c r="O16" s="37">
         <v>5000</v>
       </c>
       <c r="P16" s="35">
-        <v>70174.317899999907</v>
+        <v>75529.258849999824</v>
       </c>
       <c r="Q16" s="115">
-        <v>1.060812422412025</v>
+        <v>1.0539342392095792</v>
       </c>
       <c r="R16" s="36"/>
       <c r="S16" s="127">
         <v>0.13893604741657134</v>
       </c>
       <c r="T16" s="127">
-        <v>0.14271289467820827</v>
+        <v>0.14105471951536899</v>
       </c>
       <c r="U16" s="36"/>
       <c r="V16" s="35"/>
       <c r="W16" s="38">
-        <v>3.4647830469339973</v>
+        <v>3.3356937026333591</v>
       </c>
       <c r="X16" s="69" t="s">
         <v>69</v>
@@ -6163,38 +6163,38 @@
         <v>39677.419354838712</v>
       </c>
       <c r="AB16" s="33">
-        <v>38269.54000000003</v>
+        <v>43743.970000000118</v>
       </c>
       <c r="AC16" s="36"/>
       <c r="AD16" s="35">
         <v>5512.6238168510563</v>
       </c>
       <c r="AE16" s="35">
-        <v>4493.1337500000018</v>
+        <v>5354.9409500000002</v>
       </c>
       <c r="AF16" s="115">
-        <v>0.81506264517185723</v>
+        <v>0.97139604078024533</v>
       </c>
       <c r="AG16" s="36"/>
       <c r="AH16" s="35">
-        <v>5847.8598249999923</v>
+        <v>5809.9429884615247</v>
       </c>
       <c r="AI16" s="35">
-        <v>181283.65457499976</v>
+        <v>180108.23264230727</v>
       </c>
       <c r="AJ16" s="115">
-        <v>1.060812422412025</v>
+        <v>1.0539342392095792</v>
       </c>
       <c r="AK16" s="36"/>
       <c r="AL16" s="108">
         <v>0.13893604741657134</v>
       </c>
       <c r="AM16" s="108">
-        <v>0.11740757140012653</v>
+        <v>0.12241552264232043</v>
       </c>
       <c r="AN16" s="36"/>
       <c r="AO16" s="38">
-        <v>1.858877190580309</v>
+        <v>1.8846276412499099</v>
       </c>
       <c r="AP16" s="70">
         <v>0</v>
@@ -6210,51 +6210,51 @@
       </c>
       <c r="D17" s="34"/>
       <c r="E17" s="33">
-        <v>51603.859999999993</v>
+        <v>51333.299999999974</v>
       </c>
       <c r="F17" s="131">
-        <v>1.1218230434782608</v>
+        <v>1.1159413043478255</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="35">
         <v>46000</v>
       </c>
       <c r="I17" s="35">
-        <v>17692.307692307691</v>
+        <v>19461.538461538461</v>
       </c>
       <c r="J17" s="35">
-        <v>13805.999999999956</v>
+        <v>14657.859999999962</v>
       </c>
       <c r="K17" s="70">
-        <v>0.7803391304347802</v>
+        <v>0.75317067193675702</v>
       </c>
       <c r="L17" s="36"/>
       <c r="M17" s="35">
         <v>6566.3465285347293</v>
       </c>
       <c r="N17" s="35">
-        <v>2525.5178955902802</v>
+        <v>2778.0696851493085</v>
       </c>
       <c r="O17" s="37">
         <v>0</v>
       </c>
       <c r="P17" s="35">
-        <v>1851.4799999999989</v>
+        <v>1955.8699999999988</v>
       </c>
       <c r="Q17" s="115">
-        <v>0.73310904002414889</v>
+        <v>0.70403921487479881</v>
       </c>
       <c r="R17" s="36"/>
       <c r="S17" s="127">
         <v>0.14274666366379846</v>
       </c>
       <c r="T17" s="127">
-        <v>0.13410691003911376</v>
+        <v>0.13343489431608732</v>
       </c>
       <c r="U17" s="36"/>
       <c r="V17" s="35"/>
       <c r="W17" s="38">
-        <v>2.616833260900715</v>
+        <v>2.5587636940177951</v>
       </c>
       <c r="X17" s="69" t="s">
         <v>69</v>
@@ -6265,38 +6265,38 @@
         <v>1769.2307692307693</v>
       </c>
       <c r="AB17" s="33">
-        <v>1081.01</v>
+        <v>851.86000000000024</v>
       </c>
       <c r="AC17" s="36"/>
       <c r="AD17" s="35">
         <v>252.55178955902804</v>
       </c>
       <c r="AE17" s="35">
-        <v>171.75000000000003</v>
+        <v>104.39</v>
       </c>
       <c r="AF17" s="115">
-        <v>0.68005853492421009</v>
+        <v>0.41334096338130005</v>
       </c>
       <c r="AG17" s="36"/>
       <c r="AH17" s="35">
-        <v>185.14799999999988</v>
+        <v>177.80636363636353</v>
       </c>
       <c r="AI17" s="35">
-        <v>4813.8479999999972</v>
+        <v>4622.9654545454514</v>
       </c>
       <c r="AJ17" s="115">
-        <v>0.73310904002414878</v>
+        <v>0.70403921487479881</v>
       </c>
       <c r="AK17" s="36"/>
       <c r="AL17" s="108">
         <v>0.14274666366379846</v>
       </c>
       <c r="AM17" s="108">
-        <v>0.15887919630715722</v>
+        <v>0.12254361045242172</v>
       </c>
       <c r="AN17" s="36"/>
       <c r="AO17" s="38">
-        <v>5.2968982710613108</v>
+        <v>1.6176367008663626</v>
       </c>
       <c r="AP17" s="70">
         <v>0</v>
@@ -6310,51 +6310,51 @@
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="27">
-        <v>3962290.5300000007</v>
+        <v>3941839.99</v>
       </c>
       <c r="F18" s="124">
-        <v>1.5031451176024282</v>
+        <v>1.4953869461305009</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="29">
         <v>2636000</v>
       </c>
       <c r="I18" s="29">
-        <v>1019019.8511166254</v>
+        <v>1107470.2233250621</v>
       </c>
       <c r="J18" s="29">
-        <v>1033639.3299999682</v>
+        <v>1124725.8799999626</v>
       </c>
       <c r="K18" s="31">
-        <v>1.0143466085251656</v>
+        <v>1.0155811472954028</v>
       </c>
       <c r="L18" s="39"/>
       <c r="M18" s="29">
         <v>334987.68485091749</v>
       </c>
       <c r="N18" s="29">
-        <v>129528.54215934142</v>
+        <v>140694.87161190534</v>
       </c>
       <c r="O18" s="27">
         <v>5000</v>
       </c>
       <c r="P18" s="29">
-        <v>142244.99204999997</v>
+        <v>153762.93979999993</v>
       </c>
       <c r="Q18" s="31">
-        <v>1.0981748862348442</v>
+        <v>1.0928823349307411</v>
       </c>
       <c r="R18" s="39"/>
       <c r="S18" s="128">
         <v>0.12708182278107644</v>
       </c>
       <c r="T18" s="128">
-        <v>0.13761569236147811</v>
+        <v>0.13671148013416837</v>
       </c>
       <c r="U18" s="39"/>
       <c r="V18" s="29"/>
       <c r="W18" s="32">
-        <v>3.2743009159653278</v>
+        <v>3.1945268121655075</v>
       </c>
       <c r="X18" s="30" t="s">
         <v>69</v>
@@ -6365,34 +6365,34 @@
         <v>88450.372208436718</v>
       </c>
       <c r="AB18" s="27">
-        <v>82637.159999999989</v>
+        <v>91086.550000000163</v>
       </c>
       <c r="AC18" s="39"/>
       <c r="AD18" s="29">
         <v>11166.329452563928</v>
       </c>
       <c r="AE18" s="29">
-        <v>10015.547699999999</v>
+        <v>11517.947749999999</v>
       </c>
       <c r="AF18" s="31">
-        <v>0.89694180550084923</v>
+        <v>1.031489156658846</v>
       </c>
       <c r="AG18" s="39"/>
       <c r="AH18" s="29">
-        <v>12228.871285833329</v>
+        <v>12174.936567832165</v>
       </c>
       <c r="AI18" s="29">
-        <v>367841.35141083319</v>
+        <v>366144.94464825158</v>
       </c>
       <c r="AJ18" s="31">
-        <v>1.0980742518177551</v>
+        <v>1.093010164869793</v>
       </c>
       <c r="AK18" s="39"/>
       <c r="AL18" s="80">
         <v>0.12708182278107644</v>
       </c>
       <c r="AM18" s="80">
-        <v>0.12119907920359316</v>
+        <v>0.12645058738090287</v>
       </c>
       <c r="AN18" s="39"/>
       <c r="AO18" s="32">
@@ -6457,51 +6457,51 @@
       </c>
       <c r="D20" s="34"/>
       <c r="E20" s="33">
-        <v>73481.359999999986</v>
+        <v>72135.28</v>
       </c>
       <c r="F20" s="123">
-        <v>0.42721720930232548</v>
+        <v>0.41939116279069766</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="35">
         <v>172000</v>
       </c>
       <c r="I20" s="35">
-        <v>66153.846153846156</v>
+        <v>72769.230769230766</v>
       </c>
       <c r="J20" s="35">
-        <v>69643.890000000261</v>
+        <v>74020.200000000303</v>
       </c>
       <c r="K20" s="70">
-        <v>1.0527564767441899</v>
+        <v>1.0171909090909133</v>
       </c>
       <c r="L20" s="36"/>
       <c r="M20" s="35">
         <v>31045.208551705378</v>
       </c>
       <c r="N20" s="35">
-        <v>11940.464827578991</v>
+        <v>13134.511310336891</v>
       </c>
       <c r="O20" s="37">
         <v>0</v>
       </c>
       <c r="P20" s="35">
-        <v>11872.604519999988</v>
+        <v>12718.230789999987</v>
       </c>
       <c r="Q20" s="115">
-        <v>0.99431677840361243</v>
+        <v>0.96830635639947327</v>
       </c>
       <c r="R20" s="36"/>
       <c r="S20" s="127">
         <v>0.18049539855642663</v>
       </c>
       <c r="T20" s="127">
-        <v>0.17047589558825538</v>
+        <v>0.17182108113731029</v>
       </c>
       <c r="U20" s="36"/>
       <c r="V20" s="35"/>
       <c r="W20" s="38">
-        <v>0.90864327078818907</v>
+        <v>1.0466207737890441</v>
       </c>
       <c r="X20" s="69" t="s">
         <v>69</v>
@@ -6512,38 +6512,38 @@
         <v>6615.3846153846152</v>
       </c>
       <c r="AB20" s="33">
-        <v>7508.5499999999975</v>
+        <v>4376.3099999999986</v>
       </c>
       <c r="AC20" s="36"/>
       <c r="AD20" s="35">
         <v>1194.0464827578992</v>
       </c>
       <c r="AE20" s="35">
-        <v>1099.2981299999997</v>
+        <v>845.62626999999998</v>
       </c>
       <c r="AF20" s="115">
-        <v>0.9206493598649037</v>
+        <v>0.70820213635808371</v>
       </c>
       <c r="AG20" s="36"/>
       <c r="AH20" s="35">
-        <v>1187.2604519999988</v>
+        <v>1156.202799090908</v>
       </c>
       <c r="AI20" s="35">
-        <v>30868.771751999971</v>
+        <v>30061.272776363607</v>
       </c>
       <c r="AJ20" s="115">
-        <v>0.99431677840361243</v>
+        <v>0.96830635639947338</v>
       </c>
       <c r="AK20" s="36"/>
       <c r="AL20" s="108">
         <v>0.18049539855642663</v>
       </c>
       <c r="AM20" s="108">
-        <v>0.14640618095371277</v>
+        <v>0.19322814654354931</v>
       </c>
       <c r="AN20" s="36"/>
       <c r="AO20" s="38">
-        <v>-2.1042927063148631</v>
+        <v>3.2423724553333795</v>
       </c>
       <c r="AP20" s="70">
         <v>0</v>
@@ -6559,51 +6559,51 @@
       </c>
       <c r="D21" s="34"/>
       <c r="E21" s="33">
-        <v>83496.420000000071</v>
+        <v>81559.58</v>
       </c>
       <c r="F21" s="123">
-        <v>0.49115541176470628</v>
+        <v>0.47976223529411766</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="35">
         <v>170000</v>
       </c>
       <c r="I21" s="35">
-        <v>65806.451612903227</v>
+        <v>71290.322580645166</v>
       </c>
       <c r="J21" s="35">
-        <v>79165.600000000297</v>
+        <v>85849.110000000393</v>
       </c>
       <c r="K21" s="70">
-        <v>1.2030066666666712</v>
+        <v>1.2042182850678786</v>
       </c>
       <c r="L21" s="36"/>
       <c r="M21" s="35">
         <v>40800</v>
       </c>
       <c r="N21" s="35">
-        <v>15793.548387096776</v>
+        <v>17109.677419354841</v>
       </c>
       <c r="O21" s="37">
         <v>0</v>
       </c>
       <c r="P21" s="35">
-        <v>18901.989220000007</v>
+        <v>20685.761180000005</v>
       </c>
       <c r="Q21" s="115">
-        <v>1.196817127900327</v>
+        <v>1.2090094203996984</v>
       </c>
       <c r="R21" s="36"/>
       <c r="S21" s="127">
         <v>0.24</v>
       </c>
       <c r="T21" s="127">
-        <v>0.23876518614145456</v>
+        <v>0.24095487046982678</v>
       </c>
       <c r="U21" s="36"/>
       <c r="V21" s="35"/>
       <c r="W21" s="38">
-        <v>8.0736320068315948</v>
+        <v>8.2997729155262157</v>
       </c>
       <c r="X21" s="69" t="s">
         <v>69</v>
@@ -6614,38 +6614,38 @@
         <v>5483.8709677419356</v>
       </c>
       <c r="AB21" s="33">
-        <v>4298.779999999997</v>
+        <v>6683.5099999999893</v>
       </c>
       <c r="AC21" s="36"/>
       <c r="AD21" s="35">
         <v>1316.1290322580646</v>
       </c>
       <c r="AE21" s="35">
-        <v>1063.0205500000002</v>
+        <v>1783.7719599999989</v>
       </c>
       <c r="AF21" s="115">
-        <v>0.80768718259803929</v>
+        <v>1.3553169303921559</v>
       </c>
       <c r="AG21" s="36"/>
       <c r="AH21" s="35">
-        <v>1575.165768333334</v>
+        <v>1591.2123984615389</v>
       </c>
       <c r="AI21" s="35">
-        <v>48830.138818333355</v>
+        <v>49327.584352307706</v>
       </c>
       <c r="AJ21" s="115">
-        <v>1.1968171279003272</v>
+        <v>1.2090094203996986</v>
       </c>
       <c r="AK21" s="36"/>
       <c r="AL21" s="108">
         <v>0.24</v>
       </c>
       <c r="AM21" s="108">
-        <v>0.2472842411102687</v>
+        <v>0.2668914926438356</v>
       </c>
       <c r="AN21" s="36"/>
       <c r="AO21" s="38">
-        <v>9.1721500053503338</v>
+        <v>10.978392491370451</v>
       </c>
       <c r="AP21" s="70">
         <v>0</v>
@@ -6661,51 +6661,51 @@
       </c>
       <c r="D22" s="34"/>
       <c r="E22" s="33">
-        <v>183290.41999999995</v>
+        <v>182052.22999999986</v>
       </c>
       <c r="F22" s="123">
-        <v>0.61096806666666648</v>
+        <v>0.6068407666666662</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="35">
         <v>300000</v>
       </c>
       <c r="I22" s="35">
-        <v>116129.03225806452</v>
+        <v>125806.45161290323</v>
       </c>
       <c r="J22" s="35">
-        <v>112853.49000000075</v>
+        <v>119814.61000000087</v>
       </c>
       <c r="K22" s="70">
-        <v>0.9717939416666731</v>
+        <v>0.95237254102564795</v>
       </c>
       <c r="L22" s="36"/>
       <c r="M22" s="35">
         <v>73642.908202804829</v>
       </c>
       <c r="N22" s="35">
-        <v>28506.932207537349</v>
+        <v>30882.509891498798</v>
       </c>
       <c r="O22" s="37">
         <v>1357.86</v>
       </c>
       <c r="P22" s="35">
-        <v>30872.932819999907</v>
+        <v>32828.27788999991</v>
       </c>
       <c r="Q22" s="115">
-        <v>1.082997377453228</v>
+        <v>1.0630055006972323</v>
       </c>
       <c r="R22" s="36"/>
       <c r="S22" s="127">
         <v>0.24547636067601611</v>
       </c>
       <c r="T22" s="127">
-        <v>0.27356648713300497</v>
+        <v>0.27399227765294792</v>
       </c>
       <c r="U22" s="36"/>
       <c r="V22" s="35"/>
       <c r="W22" s="38">
-        <v>10.224365077234564</v>
+        <v>10.349095064450417</v>
       </c>
       <c r="X22" s="69" t="s">
         <v>69</v>
@@ -6716,38 +6716,38 @@
         <v>9677.4193548387102</v>
       </c>
       <c r="AB22" s="33">
-        <v>10903.659999999989</v>
+        <v>6961.1199999999844</v>
       </c>
       <c r="AC22" s="36"/>
       <c r="AD22" s="35">
         <v>2375.5776839614459</v>
       </c>
       <c r="AE22" s="35">
-        <v>2661.5594900000006</v>
+        <v>1955.3450699999999</v>
       </c>
       <c r="AF22" s="115">
-        <v>1.120384110344756</v>
+        <v>0.823102979625285</v>
       </c>
       <c r="AG22" s="36"/>
       <c r="AH22" s="35">
-        <v>2572.7444016666591</v>
+        <v>2525.2521453846084</v>
       </c>
       <c r="AI22" s="35">
-        <v>79755.076451666435</v>
+        <v>78282.816506922856</v>
       </c>
       <c r="AJ22" s="115">
-        <v>1.082997377453228</v>
+        <v>1.0630055006972323</v>
       </c>
       <c r="AK22" s="36"/>
       <c r="AL22" s="108">
         <v>0.24547636067601611</v>
       </c>
       <c r="AM22" s="108">
-        <v>0.24409780660805669</v>
+        <v>0.28089518209713438</v>
       </c>
       <c r="AN22" s="36"/>
       <c r="AO22" s="38">
-        <v>8.7182605657182481</v>
+        <v>12.371214258624896</v>
       </c>
       <c r="AP22" s="70">
         <v>0</v>
@@ -6763,51 +6763,51 @@
       </c>
       <c r="D23" s="34"/>
       <c r="E23" s="33">
-        <v>21579.190000000002</v>
+        <v>-29733.140000000018</v>
       </c>
       <c r="F23" s="123">
-        <v>2.4246280898876406E-2</v>
+        <v>-3.3408022471910132E-2</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="35">
         <v>890000</v>
       </c>
       <c r="I23" s="35">
-        <v>342307.69230769237</v>
+        <v>376538.46153846156</v>
       </c>
       <c r="J23" s="35">
-        <v>366101.67999999988</v>
+        <v>440071.84999999986</v>
       </c>
       <c r="K23" s="70">
-        <v>1.069510525842696</v>
+        <v>1.1687301430030639</v>
       </c>
       <c r="L23" s="36"/>
       <c r="M23" s="35">
         <v>228323.22150295851</v>
       </c>
       <c r="N23" s="35">
-        <v>87816.623654984025</v>
+        <v>96598.286020482439</v>
       </c>
       <c r="O23" s="37">
         <v>10134.549999999999</v>
       </c>
       <c r="P23" s="35">
-        <v>60453.860000000044</v>
+        <v>69590.900000000038</v>
       </c>
       <c r="Q23" s="115">
-        <v>0.68841020622146165</v>
+        <v>0.72041547388578064</v>
       </c>
       <c r="R23" s="36"/>
       <c r="S23" s="127">
         <v>0.25654294550894213</v>
       </c>
       <c r="T23" s="127">
-        <v>0.16512860580153596</v>
+        <v>0.15813531358572483</v>
       </c>
       <c r="U23" s="36"/>
       <c r="V23" s="35"/>
       <c r="W23" s="38">
-        <v>-2.6691710346699966</v>
+        <v>-2.8451513088147706</v>
       </c>
       <c r="X23" s="69" t="s">
         <v>69</v>
@@ -6818,38 +6818,38 @@
         <v>34230.769230769234</v>
       </c>
       <c r="AB23" s="33">
-        <v>6472.8399999999992</v>
+        <v>73970.17</v>
       </c>
       <c r="AC23" s="36"/>
       <c r="AD23" s="35">
         <v>8781.6623654984032</v>
       </c>
       <c r="AE23" s="35">
-        <v>1151.2199999999998</v>
+        <v>9137.0400000000063</v>
       </c>
       <c r="AF23" s="115">
-        <v>0.13109363034986854</v>
+        <v>1.0404681505289726</v>
       </c>
       <c r="AG23" s="36"/>
       <c r="AH23" s="35">
-        <v>6045.3860000000041</v>
+        <v>6326.4454545454582</v>
       </c>
       <c r="AI23" s="35">
-        <v>157180.03600000011</v>
+        <v>164487.5818181819</v>
       </c>
       <c r="AJ23" s="115">
-        <v>0.68841020622146154</v>
+        <v>0.72041547388578064</v>
       </c>
       <c r="AK23" s="36"/>
       <c r="AL23" s="108">
         <v>0.25654294550894213</v>
       </c>
       <c r="AM23" s="108">
-        <v>0.17785392501591263</v>
+        <v>0.12352330676000889</v>
       </c>
       <c r="AN23" s="36"/>
       <c r="AO23" s="38">
-        <v>1.2855253644458866</v>
+        <v>-3.7161331385340897</v>
       </c>
       <c r="AP23" s="70">
         <v>0</v>
@@ -6863,51 +6863,51 @@
       </c>
       <c r="D24" s="28"/>
       <c r="E24" s="27">
-        <v>361847.39</v>
+        <v>306013.94999999984</v>
       </c>
       <c r="F24" s="124">
-        <v>0.2361928133159269</v>
+        <v>0.19974800913838109</v>
       </c>
       <c r="G24" s="26"/>
       <c r="H24" s="29">
         <v>1532000</v>
       </c>
       <c r="I24" s="29">
-        <v>590397.02233250625</v>
+        <v>646404.46650124073</v>
       </c>
       <c r="J24" s="29">
-        <v>627764.6600000012</v>
+        <v>719755.77000000142</v>
       </c>
       <c r="K24" s="31">
-        <v>1.0632923884335748</v>
+        <v>1.1134758611675217</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="29">
         <v>373811.33825746871</v>
       </c>
       <c r="N24" s="29">
-        <v>144057.56907719714</v>
+        <v>157724.98464167299</v>
       </c>
       <c r="O24" s="27">
         <v>11492.41</v>
       </c>
       <c r="P24" s="29">
-        <v>122101.38655999996</v>
+        <v>135823.16985999994</v>
       </c>
       <c r="Q24" s="31">
-        <v>0.84758744259087582</v>
+        <v>0.86113921753468148</v>
       </c>
       <c r="R24" s="39"/>
       <c r="S24" s="128">
         <v>0.24400217901923546</v>
       </c>
       <c r="T24" s="128">
-        <v>0.19450184812888277</v>
+        <v>0.18870730256181159</v>
       </c>
       <c r="U24" s="39"/>
       <c r="V24" s="29"/>
       <c r="W24" s="32">
-        <v>1.4003697755143869</v>
+        <v>1.0807846472701097</v>
       </c>
       <c r="X24" s="30" t="s">
         <v>69</v>
@@ -6918,34 +6918,34 @@
         <v>56007.444168734495</v>
       </c>
       <c r="AB24" s="27">
-        <v>29183.829999999984</v>
+        <v>91991.109999999971</v>
       </c>
       <c r="AC24" s="39"/>
       <c r="AD24" s="29">
         <v>13667.415564475814</v>
       </c>
       <c r="AE24" s="29">
-        <v>5975.0981699999993</v>
+        <v>13721.783300000005</v>
       </c>
       <c r="AF24" s="31">
-        <v>0.43717834888480339</v>
+        <v>1.003977909010501</v>
       </c>
       <c r="AG24" s="39"/>
       <c r="AH24" s="29">
-        <v>11380.556621999996</v>
+        <v>11599.112797482514</v>
       </c>
       <c r="AI24" s="29">
-        <v>316634.02302199986</v>
+        <v>322159.2554537761</v>
       </c>
       <c r="AJ24" s="31">
-        <v>0.8470423195240615</v>
+        <v>0.86182312434804642</v>
       </c>
       <c r="AK24" s="39"/>
       <c r="AL24" s="80">
         <v>0.24400217901923546</v>
       </c>
       <c r="AM24" s="80">
-        <v>0.20474002795383617</v>
+        <v>0.14916423228288048</v>
       </c>
       <c r="AN24" s="39"/>
       <c r="AO24" s="32">
@@ -7010,51 +7010,51 @@
       </c>
       <c r="D26" s="34"/>
       <c r="E26" s="33">
-        <v>176861.66</v>
+        <v>165484.02000000005</v>
       </c>
       <c r="F26" s="123">
-        <v>0.53594442424242428</v>
+        <v>0.50146672727272745</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="35">
         <v>330000</v>
       </c>
       <c r="I26" s="35">
-        <v>126923.07692307691</v>
+        <v>139615.3846153846</v>
       </c>
       <c r="J26" s="35">
-        <v>147827.84999999951</v>
+        <v>165894.34999999913</v>
       </c>
       <c r="K26" s="70">
-        <v>1.164704272727269</v>
+        <v>1.1882239944903521</v>
       </c>
       <c r="L26" s="36"/>
       <c r="M26" s="35">
         <v>45867.685825971581</v>
       </c>
       <c r="N26" s="35">
-        <v>17641.417625373684</v>
+        <v>19405.559387911053</v>
       </c>
       <c r="O26" s="37">
         <v>0</v>
       </c>
       <c r="P26" s="35">
-        <v>14559.772849999988</v>
+        <v>15515.437899999977</v>
       </c>
       <c r="Q26" s="115">
-        <v>0.82531762238079098</v>
+        <v>0.79953572014345142</v>
       </c>
       <c r="R26" s="36"/>
       <c r="S26" s="127">
         <v>0.13899298735142904</v>
       </c>
       <c r="T26" s="127">
-        <v>9.8491406389256395E-2</v>
+        <v>9.3526017613017307E-2</v>
       </c>
       <c r="U26" s="36"/>
       <c r="V26" s="35"/>
       <c r="W26" s="38">
-        <v>-4.6080607612165316</v>
+        <v>-4.9892790803307578</v>
       </c>
       <c r="X26" s="69" t="s">
         <v>69</v>
@@ -7065,38 +7065,38 @@
         <v>12692.307692307691</v>
       </c>
       <c r="AB26" s="33">
-        <v>8286.9899999999925</v>
+        <v>18066.500000000011</v>
       </c>
       <c r="AC26" s="36"/>
       <c r="AD26" s="35">
         <v>1764.1417625373685</v>
       </c>
       <c r="AE26" s="35">
-        <v>1091.7222999999999</v>
+        <v>955.66505000000041</v>
       </c>
       <c r="AF26" s="115">
-        <v>0.61884046009418969</v>
+        <v>0.54171669777006215</v>
       </c>
       <c r="AG26" s="36"/>
       <c r="AH26" s="35">
-        <v>1455.9772849999988</v>
+        <v>1410.4943545454526</v>
       </c>
       <c r="AI26" s="35">
-        <v>37855.409409999971</v>
+        <v>36672.853218181765</v>
       </c>
       <c r="AJ26" s="115">
-        <v>0.82531762238079098</v>
+        <v>0.79953572014345131</v>
       </c>
       <c r="AK26" s="36"/>
       <c r="AL26" s="108">
         <v>0.13899298735142904</v>
       </c>
       <c r="AM26" s="108">
-        <v>0.13173930462085762</v>
+        <v>5.2897077463814231E-2</v>
       </c>
       <c r="AN26" s="36"/>
       <c r="AO26" s="38">
-        <v>-0.75295975981646102</v>
+        <v>-8.1085708355241817</v>
       </c>
       <c r="AP26" s="70">
         <v>0</v>
@@ -7112,51 +7112,51 @@
       </c>
       <c r="D27" s="34"/>
       <c r="E27" s="33">
-        <v>162727.05000000002</v>
+        <v>157876.69999999995</v>
       </c>
       <c r="F27" s="123">
-        <v>0.54242350000000006</v>
+        <v>0.52625566666666657</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="35">
         <v>300000</v>
       </c>
       <c r="I27" s="35">
-        <v>116129.03225806452</v>
+        <v>125806.45161290323</v>
       </c>
       <c r="J27" s="35">
-        <v>103682.03000000173</v>
+        <v>112777.49000000185</v>
       </c>
       <c r="K27" s="70">
-        <v>0.89281748055557042</v>
+        <v>0.89643645897437374</v>
       </c>
       <c r="L27" s="36"/>
       <c r="M27" s="35">
         <v>50700</v>
       </c>
       <c r="N27" s="35">
-        <v>19625.806451612902</v>
+        <v>21261.290322580644</v>
       </c>
       <c r="O27" s="37">
         <v>0</v>
       </c>
       <c r="P27" s="35">
-        <v>19274.38009999994</v>
+        <v>21030.927499999925</v>
       </c>
       <c r="Q27" s="115">
-        <v>0.98209366058513836</v>
+        <v>0.98916515323926224</v>
       </c>
       <c r="R27" s="36"/>
       <c r="S27" s="127">
         <v>0.16900000000000001</v>
       </c>
       <c r="T27" s="127">
-        <v>0.18589894603722187</v>
+        <v>0.18648160639148451</v>
       </c>
       <c r="U27" s="36"/>
       <c r="V27" s="35"/>
       <c r="W27" s="38">
-        <v>4.8204786306768908</v>
+        <v>4.905285177034937</v>
       </c>
       <c r="X27" s="69" t="s">
         <v>69</v>
@@ -7167,38 +7167,38 @@
         <v>9677.4193548387102</v>
       </c>
       <c r="AB27" s="33">
-        <v>7871.9999999999682</v>
+        <v>9095.4599999999791</v>
       </c>
       <c r="AC27" s="36"/>
       <c r="AD27" s="35">
         <v>1635.483870967742</v>
       </c>
       <c r="AE27" s="35">
-        <v>1367.57115</v>
+        <v>1756.5473999999992</v>
       </c>
       <c r="AF27" s="115">
-        <v>0.83618748816568045</v>
+        <v>1.074023065088757</v>
       </c>
       <c r="AG27" s="36"/>
       <c r="AH27" s="35">
-        <v>1606.1983416666617</v>
+        <v>1617.7636538461481</v>
       </c>
       <c r="AI27" s="35">
-        <v>49792.148591666511</v>
+        <v>50150.673269230596</v>
       </c>
       <c r="AJ27" s="115">
-        <v>0.98209366058513825</v>
+        <v>0.98916515323926224</v>
       </c>
       <c r="AK27" s="36"/>
       <c r="AL27" s="108">
         <v>0.16900000000000001</v>
       </c>
       <c r="AM27" s="108">
-        <v>0.17372600990853729</v>
+        <v>0.19312353635769969</v>
       </c>
       <c r="AN27" s="36"/>
       <c r="AO27" s="38">
-        <v>3.7013611534548714</v>
+        <v>5.8720218658537107</v>
       </c>
       <c r="AP27" s="70">
         <v>0</v>
@@ -7214,51 +7214,51 @@
       </c>
       <c r="D28" s="34"/>
       <c r="E28" s="33">
-        <v>318384.21000000014</v>
+        <v>315590.71000000008</v>
       </c>
       <c r="F28" s="123">
-        <v>0.69974551648351679</v>
+        <v>0.69360595604395625</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="35">
         <v>455000</v>
       </c>
       <c r="I28" s="35">
-        <v>176129.03225806452</v>
+        <v>190806.45161290324</v>
       </c>
       <c r="J28" s="35">
-        <v>154795.91000000061</v>
+        <v>168480.09999999992</v>
       </c>
       <c r="K28" s="70">
-        <v>0.87887787728938083</v>
+        <v>0.88298953508030376</v>
       </c>
       <c r="L28" s="36"/>
       <c r="M28" s="35">
         <v>85995</v>
       </c>
       <c r="N28" s="35">
-        <v>33288.387096774197</v>
+        <v>36062.419354838712</v>
       </c>
       <c r="O28" s="37">
         <v>0</v>
       </c>
       <c r="P28" s="35">
-        <v>29544.798839999967</v>
+        <v>31803.660139999974</v>
       </c>
       <c r="Q28" s="115">
-        <v>0.88754071364614118</v>
+        <v>0.88190589286496901</v>
       </c>
       <c r="R28" s="36"/>
       <c r="S28" s="127">
         <v>0.189</v>
       </c>
       <c r="T28" s="127">
-        <v>0.19086291646852846</v>
+        <v>0.18876805118230575</v>
       </c>
       <c r="U28" s="36"/>
       <c r="V28" s="35"/>
       <c r="W28" s="38">
-        <v>5.266714630897626</v>
+        <v>5.0510357840484916</v>
       </c>
       <c r="X28" s="69" t="s">
         <v>69</v>
@@ -7269,38 +7269,38 @@
         <v>14677.41935483871</v>
       </c>
       <c r="AB28" s="33">
-        <v>13384.479999999965</v>
+        <v>13684.189999999964</v>
       </c>
       <c r="AC28" s="36"/>
       <c r="AD28" s="35">
         <v>2774.0322580645161</v>
       </c>
       <c r="AE28" s="35">
-        <v>1776.9437499999983</v>
+        <v>2258.8612999999987</v>
       </c>
       <c r="AF28" s="115">
-        <v>0.64056347752776266</v>
+        <v>0.81428804349090012</v>
       </c>
       <c r="AG28" s="36"/>
       <c r="AH28" s="35">
-        <v>2462.0665699999972</v>
+        <v>2446.4353953846135</v>
       </c>
       <c r="AI28" s="35">
-        <v>76324.063669999916</v>
+        <v>75839.497256923016</v>
       </c>
       <c r="AJ28" s="115">
-        <v>0.88754071364614129</v>
+        <v>0.88190589286496912</v>
       </c>
       <c r="AK28" s="36"/>
       <c r="AL28" s="108">
         <v>0.189</v>
       </c>
       <c r="AM28" s="108">
-        <v>0.13276150810490978</v>
+        <v>0.16507088106786039</v>
       </c>
       <c r="AN28" s="36"/>
       <c r="AO28" s="38">
-        <v>-0.22179606529375692</v>
+        <v>2.6112711092141225</v>
       </c>
       <c r="AP28" s="70">
         <v>0</v>
@@ -7316,51 +7316,51 @@
       </c>
       <c r="D29" s="34"/>
       <c r="E29" s="33">
-        <v>36161.690000000024</v>
+        <v>20544.399999999991</v>
       </c>
       <c r="F29" s="123">
-        <v>7.0905274509803967E-2</v>
+        <v>4.0283137254901943E-2</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="35">
         <v>510000</v>
       </c>
       <c r="I29" s="35">
-        <v>196153.84615384619</v>
+        <v>215769.23076923078</v>
       </c>
       <c r="J29" s="35">
-        <v>277775.57999999973</v>
+        <v>299079.80999999947</v>
       </c>
       <c r="K29" s="70">
-        <v>1.4161107999999984</v>
+        <v>1.3861096363636338</v>
       </c>
       <c r="L29" s="36"/>
       <c r="M29" s="35">
         <v>112200</v>
       </c>
       <c r="N29" s="35">
-        <v>43153.846153846156</v>
+        <v>47469.230769230766</v>
       </c>
       <c r="O29" s="37">
         <v>0</v>
       </c>
       <c r="P29" s="35">
-        <v>30835.040000000001</v>
+        <v>36119.140000000007</v>
       </c>
       <c r="Q29" s="115">
-        <v>0.71453746880570412</v>
+        <v>0.76089583535893712</v>
       </c>
       <c r="R29" s="36"/>
       <c r="S29" s="127">
         <v>0.22</v>
       </c>
       <c r="T29" s="127">
-        <v>0.11100702228756046</v>
+        <v>0.12076756368141357</v>
       </c>
       <c r="U29" s="36"/>
       <c r="V29" s="35"/>
       <c r="W29" s="38">
-        <v>-3.0285131615962531</v>
+        <v>-2.0441700828954863</v>
       </c>
       <c r="X29" s="69" t="s">
         <v>69</v>
@@ -7371,38 +7371,38 @@
         <v>19615.384615384617</v>
       </c>
       <c r="AB29" s="33">
-        <v>7442.58</v>
+        <v>21304.23</v>
       </c>
       <c r="AC29" s="36"/>
       <c r="AD29" s="35">
         <v>4315.3846153846152</v>
       </c>
       <c r="AE29" s="35">
-        <v>-1025.1199999999999</v>
+        <v>5284.1</v>
       </c>
       <c r="AF29" s="115">
-        <v>-0.2375500891265597</v>
+        <v>1.2244795008912657</v>
       </c>
       <c r="AG29" s="36"/>
       <c r="AH29" s="35">
-        <v>3083.5039999999999</v>
+        <v>3283.5581818181822</v>
       </c>
       <c r="AI29" s="35">
-        <v>80171.103999999992</v>
+        <v>85372.51272727274</v>
       </c>
       <c r="AJ29" s="115">
-        <v>0.71453746880570401</v>
+        <v>0.76089583535893712</v>
       </c>
       <c r="AK29" s="36"/>
       <c r="AL29" s="108">
         <v>0.22</v>
       </c>
       <c r="AM29" s="108">
-        <v>-0.13773718253616352</v>
+        <v>0.24803055543429639</v>
       </c>
       <c r="AN29" s="36"/>
       <c r="AO29" s="38">
-        <v>-27.757713051119389</v>
+        <v>10.790204574396713</v>
       </c>
       <c r="AP29" s="70">
         <v>0</v>
@@ -7416,51 +7416,51 @@
       </c>
       <c r="D30" s="28"/>
       <c r="E30" s="27">
-        <v>694134.61000000022</v>
+        <v>659495.83000000007</v>
       </c>
       <c r="F30" s="124">
-        <v>0.43519411285266474</v>
+        <v>0.41347700940438875</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="29">
         <v>1595000</v>
       </c>
       <c r="I30" s="29">
-        <v>615334.98759305221</v>
+        <v>671997.5186104218</v>
       </c>
       <c r="J30" s="29">
-        <v>684081.37000000151</v>
+        <v>746231.75000000047</v>
       </c>
       <c r="K30" s="31">
-        <v>1.1117218812404248</v>
+        <v>1.1104680141424965</v>
       </c>
       <c r="L30" s="39"/>
       <c r="M30" s="29">
         <v>294762.6858259716</v>
       </c>
       <c r="N30" s="29">
-        <v>113709.45732760694</v>
+        <v>124198.49983456118</v>
       </c>
       <c r="O30" s="27">
         <v>0</v>
       </c>
       <c r="P30" s="29">
-        <v>94213.991789999898</v>
+        <v>104469.16553999987</v>
       </c>
       <c r="Q30" s="31">
-        <v>0.82855018398831248</v>
+        <v>0.84114675844843689</v>
       </c>
       <c r="R30" s="39"/>
       <c r="S30" s="128">
         <v>0.18480419174042106</v>
       </c>
       <c r="T30" s="128">
-        <v>0.13772337023298806</v>
+        <v>0.13999560530626015</v>
       </c>
       <c r="U30" s="39"/>
       <c r="V30" s="29"/>
       <c r="W30" s="32">
-        <v>-0.30315665664116642</v>
+        <v>-4.671262781280347E-2</v>
       </c>
       <c r="X30" s="30" t="s">
         <v>69</v>
@@ -7471,34 +7471,34 @@
         <v>56662.531017369729</v>
       </c>
       <c r="AB30" s="27">
-        <v>36986.04999999993</v>
+        <v>62150.379999999961</v>
       </c>
       <c r="AC30" s="39"/>
       <c r="AD30" s="29">
         <v>10489.042506954242</v>
       </c>
       <c r="AE30" s="29">
-        <v>3211.1171999999988</v>
+        <v>10255.173749999998</v>
       </c>
       <c r="AF30" s="31">
-        <v>0.30614016464048327</v>
+        <v>0.97770351709422587</v>
       </c>
       <c r="AG30" s="39"/>
       <c r="AH30" s="29">
-        <v>8607.7461966666579</v>
+        <v>8758.2515855943966</v>
       </c>
       <c r="AI30" s="29">
-        <v>244142.72567166638</v>
+        <v>248035.53647160815</v>
       </c>
       <c r="AJ30" s="31">
-        <v>0.82826876470995614</v>
+        <v>0.84147535763074421</v>
       </c>
       <c r="AK30" s="39"/>
       <c r="AL30" s="80">
         <v>0.18480419174042106</v>
       </c>
       <c r="AM30" s="80">
-        <v>8.6819684718968504E-2</v>
+        <v>0.1650058092967413</v>
       </c>
       <c r="AN30" s="39"/>
       <c r="AO30" s="32">
@@ -7563,51 +7563,51 @@
       </c>
       <c r="D32" s="34"/>
       <c r="E32" s="33">
-        <v>337176.71999999991</v>
+        <v>333133.04999999993</v>
       </c>
       <c r="F32" s="123">
-        <v>0.22478447999999995</v>
+        <v>0.22208869999999994</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="35">
         <v>1500000</v>
       </c>
       <c r="I32" s="35">
-        <v>576923.07692307699</v>
+        <v>634615.38461538462</v>
       </c>
       <c r="J32" s="35">
-        <v>960984.73999999953</v>
+        <v>1031286.8299999996</v>
       </c>
       <c r="K32" s="70">
-        <v>1.6657068826666657</v>
+        <v>1.6250580351515145</v>
       </c>
       <c r="L32" s="36"/>
       <c r="M32" s="35">
         <v>105000.00000000001</v>
       </c>
       <c r="N32" s="35">
-        <v>40384.61538461539</v>
+        <v>44423.076923076929</v>
       </c>
       <c r="O32" s="37">
         <v>0</v>
       </c>
       <c r="P32" s="35">
-        <v>79876.246800000037</v>
+        <v>89221.206800000087</v>
       </c>
       <c r="Q32" s="115">
-        <v>1.9778880160000007</v>
+        <v>2.0084427504761924</v>
       </c>
       <c r="R32" s="36"/>
       <c r="S32" s="127">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="T32" s="127">
-        <v>8.3119162537378138E-2</v>
+        <v>8.6514444095053669E-2</v>
       </c>
       <c r="U32" s="36"/>
       <c r="V32" s="35"/>
       <c r="W32" s="38">
-        <v>-3.97045151830411</v>
+        <v>-3.4827539880443834</v>
       </c>
       <c r="X32" s="69" t="s">
         <v>69</v>
@@ -7618,38 +7618,38 @@
         <v>57692.307692307695</v>
       </c>
       <c r="AB32" s="33">
-        <v>111830.12</v>
+        <v>70302.089999999982</v>
       </c>
       <c r="AC32" s="36"/>
       <c r="AD32" s="35">
         <v>4038.461538461539</v>
       </c>
       <c r="AE32" s="35">
-        <v>12907.378399999996</v>
+        <v>9344.9599999999973</v>
       </c>
       <c r="AF32" s="115">
-        <v>3.1961127466666652</v>
+        <v>2.3139900952380943</v>
       </c>
       <c r="AG32" s="36"/>
       <c r="AH32" s="35">
-        <v>7987.6246800000035</v>
+        <v>8111.018800000008</v>
       </c>
       <c r="AI32" s="35">
-        <v>207678.24168000009</v>
+        <v>210886.4888000002</v>
       </c>
       <c r="AJ32" s="115">
-        <v>1.9778880160000005</v>
+        <v>2.0084427504761919</v>
       </c>
       <c r="AK32" s="36"/>
       <c r="AL32" s="108">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AM32" s="108">
-        <v>0.11541951667404092</v>
+        <v>0.13292577788227916</v>
       </c>
       <c r="AN32" s="36"/>
       <c r="AO32" s="38">
-        <v>2.3616342359285549</v>
+        <v>3.1837602552071869</v>
       </c>
       <c r="AP32" s="70">
         <v>0</v>
@@ -7665,51 +7665,51 @@
       </c>
       <c r="D33" s="34"/>
       <c r="E33" s="33">
-        <v>260932.39999999979</v>
+        <v>305909.33</v>
       </c>
       <c r="F33" s="123">
-        <v>0.42085870967741901</v>
+        <v>0.49340214516129033</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="35">
         <v>620000</v>
       </c>
       <c r="I33" s="35">
-        <v>240000</v>
+        <v>260000</v>
       </c>
       <c r="J33" s="35">
-        <v>254972.22999999957</v>
+        <v>286454.67999999912</v>
       </c>
       <c r="K33" s="70">
-        <v>1.0623842916666648</v>
+        <v>1.1017487692307659</v>
       </c>
       <c r="L33" s="36"/>
       <c r="M33" s="35">
         <v>92380</v>
       </c>
       <c r="N33" s="35">
-        <v>35760</v>
+        <v>38740</v>
       </c>
       <c r="O33" s="37">
         <v>0</v>
       </c>
       <c r="P33" s="35">
-        <v>33367.895199999941</v>
+        <v>36759.564399999945</v>
       </c>
       <c r="Q33" s="115">
-        <v>0.93310668903802962</v>
+        <v>0.94887879194630731</v>
       </c>
       <c r="R33" s="36"/>
       <c r="S33" s="127">
         <v>0.14899999999999999</v>
       </c>
       <c r="T33" s="127">
-        <v>0.13086874284309313</v>
+        <v>0.12832593414078644</v>
       </c>
       <c r="U33" s="36"/>
       <c r="V33" s="35"/>
       <c r="W33" s="38">
-        <v>-0.6372320624880573</v>
+        <v>-0.85141063151814667</v>
       </c>
       <c r="X33" s="69" t="s">
         <v>69</v>
@@ -7720,38 +7720,38 @@
         <v>20000</v>
       </c>
       <c r="AB33" s="33">
-        <v>18690.239999999991</v>
+        <v>31482.449999999997</v>
       </c>
       <c r="AC33" s="36"/>
       <c r="AD33" s="35">
         <v>2980</v>
       </c>
       <c r="AE33" s="35">
-        <v>2305.39</v>
+        <v>3391.6692000000003</v>
       </c>
       <c r="AF33" s="115">
-        <v>0.77362080536912747</v>
+        <v>1.1381440268456378</v>
       </c>
       <c r="AG33" s="36"/>
       <c r="AH33" s="35">
-        <v>2780.6579333333284</v>
+        <v>2827.6587999999956</v>
       </c>
       <c r="AI33" s="35">
-        <v>86200.395933333173</v>
+        <v>87657.422799999869</v>
       </c>
       <c r="AJ33" s="115">
-        <v>0.93310668903802962</v>
+        <v>0.94887879194630731</v>
       </c>
       <c r="AK33" s="36"/>
       <c r="AL33" s="108">
         <v>0.14899999999999999</v>
       </c>
       <c r="AM33" s="108">
-        <v>0.12334726573869575</v>
+        <v>0.10773206024308783</v>
       </c>
       <c r="AN33" s="36"/>
       <c r="AO33" s="38">
-        <v>1.4825384799766779</v>
+        <v>-2.5860147478992181</v>
       </c>
       <c r="AP33" s="70">
         <v>0</v>
@@ -7767,51 +7767,51 @@
       </c>
       <c r="D34" s="34"/>
       <c r="E34" s="33">
-        <v>941915.78000000014</v>
+        <v>1017351.3599999994</v>
       </c>
       <c r="F34" s="123">
-        <v>0.554068105882353</v>
+        <v>0.59844197647058783</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="35">
         <v>1700000</v>
       </c>
       <c r="I34" s="35">
-        <v>658064.51612903224</v>
+        <v>712903.22580645164</v>
       </c>
       <c r="J34" s="35">
-        <v>704770.92999999644</v>
+        <v>786158.80999999493</v>
       </c>
       <c r="K34" s="70">
-        <v>1.0709754328431318</v>
+        <v>1.1027567018099476</v>
       </c>
       <c r="L34" s="36"/>
       <c r="M34" s="35">
         <v>229500.00000000003</v>
       </c>
       <c r="N34" s="35">
-        <v>88838.709677419363</v>
+        <v>96241.93548387097</v>
       </c>
       <c r="O34" s="37">
         <v>0</v>
       </c>
       <c r="P34" s="35">
-        <v>87671.755600000135</v>
+        <v>97128.247200000143</v>
       </c>
       <c r="Q34" s="115">
-        <v>0.98686435134350181</v>
+        <v>1.0092092050276535</v>
       </c>
       <c r="R34" s="36"/>
       <c r="S34" s="127">
         <v>0.13500000000000001</v>
       </c>
       <c r="T34" s="127">
-        <v>0.12439751963095382</v>
+        <v>0.1235478709448041</v>
       </c>
       <c r="U34" s="36"/>
       <c r="V34" s="35"/>
       <c r="W34" s="38">
-        <v>-2.3075943838944437</v>
+        <v>-2.5091231630415973</v>
       </c>
       <c r="X34" s="69" t="s">
         <v>69</v>
@@ -7822,38 +7822,38 @@
         <v>54838.709677419356</v>
       </c>
       <c r="AB34" s="33">
-        <v>46788.86</v>
+        <v>81387.87999999999</v>
       </c>
       <c r="AC34" s="36"/>
       <c r="AD34" s="35">
         <v>7403.2258064516136</v>
       </c>
       <c r="AE34" s="35">
-        <v>6220.5120000000006</v>
+        <v>9456.4915999999994</v>
       </c>
       <c r="AF34" s="115">
-        <v>0.84024345098039221</v>
+        <v>1.2773474492374726</v>
       </c>
       <c r="AG34" s="36"/>
       <c r="AH34" s="35">
-        <v>7305.9796333333443</v>
+        <v>7471.4036307692422</v>
       </c>
       <c r="AI34" s="35">
-        <v>226485.36863333368</v>
+        <v>231613.51255384652</v>
       </c>
       <c r="AJ34" s="115">
-        <v>0.9868643513435017</v>
+        <v>1.0092092050276535</v>
       </c>
       <c r="AK34" s="36"/>
       <c r="AL34" s="108">
         <v>0.13500000000000001</v>
       </c>
       <c r="AM34" s="108">
-        <v>0.13294856938168617</v>
+        <v>0.11619041557539035</v>
       </c>
       <c r="AN34" s="36"/>
       <c r="AO34" s="38">
-        <v>0.94283553820285004</v>
+        <v>-4.2542432607902168</v>
       </c>
       <c r="AP34" s="70">
         <v>0</v>
@@ -7869,51 +7869,51 @@
       </c>
       <c r="D35" s="34"/>
       <c r="E35" s="33">
-        <v>112889.75</v>
+        <v>94070.43</v>
       </c>
       <c r="F35" s="123">
-        <v>0.21709567307692307</v>
+        <v>0.18090467307692307</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="35">
         <v>520000</v>
       </c>
       <c r="I35" s="35">
-        <v>200000</v>
+        <v>220000</v>
       </c>
       <c r="J35" s="35">
-        <v>377963.4</v>
+        <v>400758.24000000005</v>
       </c>
       <c r="K35" s="70">
-        <v>1.8898170000000001</v>
+        <v>1.8216283636363639</v>
       </c>
       <c r="L35" s="36"/>
       <c r="M35" s="35">
         <v>31200</v>
       </c>
       <c r="N35" s="35">
-        <v>12000</v>
+        <v>13200</v>
       </c>
       <c r="O35" s="37">
         <v>0</v>
       </c>
       <c r="P35" s="35">
-        <v>16737.620000000003</v>
+        <v>19387.150000000001</v>
       </c>
       <c r="Q35" s="115">
-        <v>1.3948016666666669</v>
+        <v>1.4687234848484849</v>
       </c>
       <c r="R35" s="36"/>
       <c r="S35" s="127">
         <v>0.06</v>
       </c>
       <c r="T35" s="127">
-        <v>4.4283705776802733E-2</v>
+        <v>4.837617312622193E-2</v>
       </c>
       <c r="U35" s="36"/>
       <c r="V35" s="35"/>
       <c r="W35" s="38">
-        <v>-8.4946955181374921</v>
+        <v>-8.0522860864944441</v>
       </c>
       <c r="X35" s="69" t="s">
         <v>69</v>
@@ -7924,38 +7924,38 @@
         <v>20000</v>
       </c>
       <c r="AB35" s="33">
-        <v>2220.1600000000003</v>
+        <v>22794.84</v>
       </c>
       <c r="AC35" s="36"/>
       <c r="AD35" s="35">
         <v>1200</v>
       </c>
       <c r="AE35" s="35">
-        <v>356.6400000000001</v>
+        <v>2649.5299999999993</v>
       </c>
       <c r="AF35" s="115">
-        <v>0.29720000000000008</v>
+        <v>2.2079416666666662</v>
       </c>
       <c r="AG35" s="36"/>
       <c r="AH35" s="35">
-        <v>1673.7620000000002</v>
+        <v>1762.4681818181818</v>
       </c>
       <c r="AI35" s="35">
-        <v>43517.812000000005</v>
+        <v>45824.172727272729</v>
       </c>
       <c r="AJ35" s="115">
-        <v>1.3948016666666669</v>
+        <v>1.4687234848484849</v>
       </c>
       <c r="AK35" s="36"/>
       <c r="AL35" s="108">
         <v>0.06</v>
       </c>
       <c r="AM35" s="108">
-        <v>0.16063707120207554</v>
+        <v>0.11623376167588802</v>
       </c>
       <c r="AN35" s="36"/>
       <c r="AO35" s="38">
-        <v>1.2273890170078037</v>
+        <v>-0.71665341805426397</v>
       </c>
       <c r="AP35" s="70">
         <v>0</v>
@@ -7969,51 +7969,51 @@
       </c>
       <c r="D36" s="28"/>
       <c r="E36" s="27">
-        <v>1652914.65</v>
+        <v>1750464.1699999992</v>
       </c>
       <c r="F36" s="124">
-        <v>0.38085591013824882</v>
+        <v>0.40333275806451596</v>
       </c>
       <c r="G36" s="26"/>
       <c r="H36" s="29">
         <v>4340000</v>
       </c>
       <c r="I36" s="29">
-        <v>1674987.5930521092</v>
+        <v>1827518.6104218364</v>
       </c>
       <c r="J36" s="29">
-        <v>2298691.2999999956</v>
+        <v>2504658.559999994</v>
       </c>
       <c r="K36" s="31">
-        <v>1.3723631802020655</v>
+        <v>1.3705242429360853</v>
       </c>
       <c r="L36" s="39"/>
       <c r="M36" s="29">
         <v>458080</v>
       </c>
       <c r="N36" s="29">
-        <v>176983.32506203477</v>
+        <v>192605.01240694791</v>
       </c>
       <c r="O36" s="27">
         <v>0</v>
       </c>
       <c r="P36" s="29">
-        <v>217653.51760000011</v>
+        <v>242496.16840000017</v>
       </c>
       <c r="Q36" s="31">
-        <v>1.2297967479349252</v>
+        <v>1.2590335286167897</v>
       </c>
       <c r="R36" s="39"/>
       <c r="S36" s="128">
         <v>0.10554838709677419</v>
       </c>
       <c r="T36" s="128">
-        <v>9.4685840417110603E-2</v>
+        <v>9.6818054274032769E-2</v>
       </c>
       <c r="U36" s="39"/>
       <c r="V36" s="29"/>
       <c r="W36" s="32">
-        <v>-3.8348034118370911</v>
+        <v>-3.6073572279650383</v>
       </c>
       <c r="X36" s="30" t="s">
         <v>69</v>
@@ -8024,34 +8024,34 @@
         <v>152531.01736972705</v>
       </c>
       <c r="AB36" s="27">
-        <v>179529.37999999998</v>
+        <v>205967.25999999998</v>
       </c>
       <c r="AC36" s="39"/>
       <c r="AD36" s="29">
         <v>15621.687344913153</v>
       </c>
       <c r="AE36" s="29">
-        <v>21789.920399999995</v>
+        <v>24842.650799999996</v>
       </c>
       <c r="AF36" s="31">
-        <v>1.3948506277777597</v>
+        <v>1.5902668035466374</v>
       </c>
       <c r="AG36" s="39"/>
       <c r="AH36" s="29">
-        <v>19748.024246666675</v>
+        <v>20172.549412587428</v>
       </c>
       <c r="AI36" s="29">
-        <v>563881.81824666704</v>
+        <v>575981.5968811193</v>
       </c>
       <c r="AJ36" s="31">
-        <v>1.2309679930288751</v>
+        <v>1.2573821098522513</v>
       </c>
       <c r="AK36" s="39"/>
       <c r="AL36" s="80">
         <v>0.10554838709677419</v>
       </c>
       <c r="AM36" s="80">
-        <v>0.12137244834243843</v>
+        <v>0.12061456175122201</v>
       </c>
       <c r="AN36" s="39"/>
       <c r="AO36" s="32">
@@ -8116,51 +8116,51 @@
       </c>
       <c r="D38" s="34"/>
       <c r="E38" s="33">
-        <v>108057.31000000006</v>
+        <v>121015.35000000003</v>
       </c>
       <c r="F38" s="123">
-        <v>0.49116959090909118</v>
+        <v>0.55006977272727287</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="35">
         <v>220000</v>
       </c>
       <c r="I38" s="35">
-        <v>84615.38461538461</v>
+        <v>93076.923076923063</v>
       </c>
       <c r="J38" s="35">
-        <v>80662.180000000357</v>
+        <v>88317.070000000662</v>
       </c>
       <c r="K38" s="70">
-        <v>0.95328030909091332</v>
+        <v>0.94886108264463531</v>
       </c>
       <c r="L38" s="36"/>
       <c r="M38" s="35">
         <v>23100</v>
       </c>
       <c r="N38" s="35">
-        <v>8884.6153846153848</v>
+        <v>9773.0769230769238</v>
       </c>
       <c r="O38" s="37">
         <v>0</v>
       </c>
       <c r="P38" s="35">
-        <v>10096.347599999988</v>
+        <v>11410.036399999995</v>
       </c>
       <c r="Q38" s="115">
-        <v>1.1363854441558427</v>
+        <v>1.1674968374655641</v>
       </c>
       <c r="R38" s="36"/>
       <c r="S38" s="127">
         <v>0.105</v>
       </c>
       <c r="T38" s="127">
-        <v>0.12516829572421603</v>
+        <v>0.12919400971975079</v>
       </c>
       <c r="U38" s="36"/>
       <c r="V38" s="35"/>
       <c r="W38" s="38">
-        <v>-0.50586582212321707</v>
+        <v>-0.12779364170384902</v>
       </c>
       <c r="X38" s="69" t="s">
         <v>69</v>
@@ -8171,38 +8171,38 @@
         <v>8461.538461538461</v>
       </c>
       <c r="AB38" s="33">
-        <v>6239.9599999999891</v>
+        <v>7654.8899999999821</v>
       </c>
       <c r="AC38" s="36"/>
       <c r="AD38" s="35">
         <v>888.46153846153845</v>
       </c>
       <c r="AE38" s="35">
-        <v>1138.2411999999999</v>
+        <v>1313.6888000000006</v>
       </c>
       <c r="AF38" s="115">
-        <v>1.2811372813852813</v>
+        <v>1.4786107705627711</v>
       </c>
       <c r="AG38" s="36"/>
       <c r="AH38" s="35">
-        <v>1009.6347599999988</v>
+        <v>1037.276036363636</v>
       </c>
       <c r="AI38" s="35">
-        <v>26250.503759999967</v>
+        <v>26969.176945454536</v>
       </c>
       <c r="AJ38" s="115">
-        <v>1.1363854441558427</v>
+        <v>1.1674968374655643</v>
       </c>
       <c r="AK38" s="36"/>
       <c r="AL38" s="108">
         <v>0.105</v>
       </c>
       <c r="AM38" s="108">
-        <v>0.18241161802319275</v>
+        <v>0.17161432757361683</v>
       </c>
       <c r="AN38" s="36"/>
       <c r="AO38" s="38">
-        <v>5.7220110385321457</v>
+        <v>3.8560815374222757</v>
       </c>
       <c r="AP38" s="70">
         <v>0</v>
@@ -8218,51 +8218,51 @@
       </c>
       <c r="D39" s="34"/>
       <c r="E39" s="33">
-        <v>203179.24999999974</v>
+        <v>208731.03999999975</v>
       </c>
       <c r="F39" s="123">
-        <v>0.34731495726495681</v>
+        <v>0.35680519658119614</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="35">
         <v>585000</v>
       </c>
       <c r="I39" s="35">
-        <v>226451.61290322582</v>
+        <v>245322.5806451613</v>
       </c>
       <c r="J39" s="35">
-        <v>218620.83999999583</v>
+        <v>234817.58999999485</v>
       </c>
       <c r="K39" s="70">
-        <v>0.96541966381764532</v>
+        <v>0.95717886785007755</v>
       </c>
       <c r="L39" s="36"/>
       <c r="M39" s="35">
         <v>93541.499999999985</v>
       </c>
       <c r="N39" s="35">
-        <v>36209.612903225803</v>
+        <v>39227.080645161288</v>
       </c>
       <c r="O39" s="37">
         <v>367.36</v>
       </c>
       <c r="P39" s="35">
-        <v>35525.723600000107</v>
+        <v>38006.077600000273</v>
       </c>
       <c r="Q39" s="115">
-        <v>0.98111304572480607</v>
+        <v>0.96887346636355853</v>
       </c>
       <c r="R39" s="36"/>
       <c r="S39" s="127">
         <v>0.15989999999999999</v>
       </c>
       <c r="T39" s="127">
-        <v>0.16249925487433303</v>
+        <v>0.16185362263534478</v>
       </c>
       <c r="U39" s="36"/>
       <c r="V39" s="35"/>
       <c r="W39" s="38">
-        <v>5.7601890103416222</v>
+        <v>5.7037837753105514</v>
       </c>
       <c r="X39" s="69" t="s">
         <v>69</v>
@@ -8273,38 +8273,38 @@
         <v>18870.967741935485</v>
       </c>
       <c r="AB39" s="33">
-        <v>15622.259999999938</v>
+        <v>16196.749999999905</v>
       </c>
       <c r="AC39" s="36"/>
       <c r="AD39" s="35">
         <v>3017.4677419354834</v>
       </c>
       <c r="AE39" s="35">
-        <v>2781.0959999999995</v>
+        <v>2480.3540000000016</v>
       </c>
       <c r="AF39" s="115">
-        <v>0.92166552813457125</v>
+        <v>0.82199851402853341</v>
       </c>
       <c r="AG39" s="36"/>
       <c r="AH39" s="35">
-        <v>2960.4769666666757</v>
+        <v>2923.5444307692519</v>
       </c>
       <c r="AI39" s="35">
-        <v>91774.785966666954</v>
+        <v>90629.877353846809</v>
       </c>
       <c r="AJ39" s="115">
-        <v>0.98111304572480629</v>
+        <v>0.96887346636355864</v>
       </c>
       <c r="AK39" s="36"/>
       <c r="AL39" s="108">
         <v>0.15989999999999999</v>
       </c>
       <c r="AM39" s="108">
-        <v>0.17802136182601047</v>
+        <v>0.15313899393396924</v>
       </c>
       <c r="AN39" s="36"/>
       <c r="AO39" s="38">
-        <v>7.2427164827619368</v>
+        <v>4.9424359825268658</v>
       </c>
       <c r="AP39" s="70">
         <v>0</v>
@@ -8320,51 +8320,51 @@
       </c>
       <c r="D40" s="34"/>
       <c r="E40" s="33">
-        <v>356762.58000000019</v>
+        <v>368113.59999999986</v>
       </c>
       <c r="F40" s="123">
-        <v>0.38778541304347847</v>
+        <v>0.40012347826086941</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="35">
         <v>920000</v>
       </c>
       <c r="I40" s="35">
-        <v>356129.03225806449</v>
+        <v>385806.45161290321</v>
       </c>
       <c r="J40" s="35">
-        <v>372378.46999997913</v>
+        <v>403076.33999997395</v>
       </c>
       <c r="K40" s="70">
-        <v>1.045627950181101</v>
+        <v>1.0447630886286952</v>
       </c>
       <c r="L40" s="36"/>
       <c r="M40" s="35">
         <v>158240</v>
       </c>
       <c r="N40" s="35">
-        <v>61254.193548387106</v>
+        <v>66358.709677419363</v>
       </c>
       <c r="O40" s="37">
-        <v>431.9</v>
+        <v>694.9</v>
       </c>
       <c r="P40" s="35">
-        <v>64761.603450000024</v>
+        <v>70640.889449999988</v>
       </c>
       <c r="Q40" s="115">
-        <v>1.0572599147655461</v>
+        <v>1.0645307871927741</v>
       </c>
       <c r="R40" s="36"/>
       <c r="S40" s="127">
         <v>0.17199999999999999</v>
       </c>
       <c r="T40" s="127">
-        <v>0.17391339367714695</v>
+        <v>0.17525436856453683</v>
       </c>
       <c r="U40" s="36"/>
       <c r="V40" s="35"/>
       <c r="W40" s="38">
-        <v>6.6875465302763448</v>
+        <v>6.763830258550291</v>
       </c>
       <c r="X40" s="69" t="s">
         <v>69</v>
@@ -8375,38 +8375,38 @@
         <v>29677.419354838708</v>
       </c>
       <c r="AB40" s="33">
-        <v>30247.680000000084</v>
+        <v>30697.870000000228</v>
       </c>
       <c r="AC40" s="36"/>
       <c r="AD40" s="35">
         <v>5104.5161290322585</v>
       </c>
       <c r="AE40" s="35">
-        <v>5243.6492000000007</v>
+        <v>5616.2860000000001</v>
       </c>
       <c r="AF40" s="115">
-        <v>1.0272568579373105</v>
+        <v>1.1002582532861476</v>
       </c>
       <c r="AG40" s="36"/>
       <c r="AH40" s="35">
-        <v>5396.800287500002</v>
+        <v>5433.9145730769224</v>
       </c>
       <c r="AI40" s="35">
-        <v>167300.80891250007</v>
+        <v>168451.35176538461</v>
       </c>
       <c r="AJ40" s="115">
-        <v>1.0572599147655464</v>
+        <v>1.0645307871927743</v>
       </c>
       <c r="AK40" s="36"/>
       <c r="AL40" s="108">
         <v>0.17199999999999999</v>
       </c>
       <c r="AM40" s="108">
-        <v>0.17335707069104098</v>
+        <v>0.18295360557589038</v>
       </c>
       <c r="AN40" s="36"/>
       <c r="AO40" s="38">
-        <v>6.7443823790786919</v>
+        <v>7.6891849499662168</v>
       </c>
       <c r="AP40" s="70">
         <v>0</v>
@@ -8422,51 +8422,51 @@
       </c>
       <c r="D41" s="34"/>
       <c r="E41" s="33">
-        <v>25025.710000000021</v>
+        <v>24831.160000000003</v>
       </c>
       <c r="F41" s="123">
-        <v>0.45501290909090947</v>
+        <v>0.45147563636363641</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="35">
         <v>55000</v>
       </c>
       <c r="I41" s="35">
-        <v>21153.846153846152</v>
+        <v>23269.230769230766</v>
       </c>
       <c r="J41" s="35">
-        <v>38077.270000000026</v>
+        <v>40543.58</v>
       </c>
       <c r="K41" s="70">
-        <v>1.8000164000000014</v>
+        <v>1.7423687272727275</v>
       </c>
       <c r="L41" s="36"/>
       <c r="M41" s="35">
         <v>8921.0164607613788</v>
       </c>
       <c r="N41" s="35">
-        <v>3431.1601772159152</v>
+        <v>3774.2761949375067</v>
       </c>
       <c r="O41" s="37">
         <v>1255.83</v>
       </c>
       <c r="P41" s="35">
-        <v>6099.8899999999958</v>
+        <v>6685.0499999999947</v>
       </c>
       <c r="Q41" s="115">
-        <v>1.7777922582878425</v>
+        <v>1.7712137784104811</v>
       </c>
       <c r="R41" s="36"/>
       <c r="S41" s="127">
         <v>0.16220029928657051</v>
       </c>
       <c r="T41" s="127">
-        <v>0.16019767173434418</v>
+        <v>0.16488553798159891</v>
       </c>
       <c r="U41" s="36"/>
       <c r="V41" s="35"/>
       <c r="W41" s="38">
-        <v>-3.6531505541230893</v>
+        <v>-2.7193701197574622</v>
       </c>
       <c r="X41" s="69" t="s">
         <v>69</v>
@@ -8477,38 +8477,38 @@
         <v>2115.3846153846152</v>
       </c>
       <c r="AB41" s="33">
-        <v>16117.37</v>
+        <v>2466.31</v>
       </c>
       <c r="AC41" s="36"/>
       <c r="AD41" s="35">
         <v>343.1160177215915</v>
       </c>
       <c r="AE41" s="35">
-        <v>1836.1699999999989</v>
+        <v>585.15999999999985</v>
       </c>
       <c r="AF41" s="115">
-        <v>5.3514552080453717</v>
+        <v>1.7054289796368696</v>
       </c>
       <c r="AG41" s="36"/>
       <c r="AH41" s="35">
-        <v>609.98899999999958</v>
+        <v>607.73181818181774</v>
       </c>
       <c r="AI41" s="35">
-        <v>15859.713999999989</v>
+        <v>15801.02727272726</v>
       </c>
       <c r="AJ41" s="115">
-        <v>1.7777922582878427</v>
+        <v>1.7712137784104813</v>
       </c>
       <c r="AK41" s="36"/>
       <c r="AL41" s="108">
         <v>0.16220029928657051</v>
       </c>
       <c r="AM41" s="108">
-        <v>0.11392491454871352</v>
+        <v>0.23726133373339112</v>
       </c>
       <c r="AN41" s="36"/>
       <c r="AO41" s="38">
-        <v>-9.3755991207002154</v>
+        <v>11.697231897044583</v>
       </c>
       <c r="AP41" s="70">
         <v>0</v>
@@ -8522,51 +8522,51 @@
       </c>
       <c r="D42" s="28"/>
       <c r="E42" s="27">
-        <v>693024.85000000009</v>
+        <v>722691.14999999967</v>
       </c>
       <c r="F42" s="124">
-        <v>0.38933980337078655</v>
+        <v>0.40600626404494361</v>
       </c>
       <c r="G42" s="26"/>
       <c r="H42" s="29">
         <v>1780000</v>
       </c>
       <c r="I42" s="29">
-        <v>688349.87593052106</v>
+        <v>747475.18610421824</v>
       </c>
       <c r="J42" s="29">
-        <v>709738.75999997533</v>
+        <v>766754.57999996946</v>
       </c>
       <c r="K42" s="31">
-        <v>1.0310726925613816</v>
+        <v>1.0257926875087773</v>
       </c>
       <c r="L42" s="39"/>
       <c r="M42" s="29">
         <v>283802.51646076137</v>
       </c>
       <c r="N42" s="29">
-        <v>109779.5820134442</v>
+        <v>119133.14344059509</v>
       </c>
       <c r="O42" s="27">
-        <v>2055.09</v>
+        <v>2318.09</v>
       </c>
       <c r="P42" s="29">
-        <v>116483.56465000012</v>
+        <v>126742.05345000024</v>
       </c>
       <c r="Q42" s="31">
-        <v>1.0610676640737702</v>
+        <v>1.0638689603048985</v>
       </c>
       <c r="R42" s="39"/>
       <c r="S42" s="128">
         <v>0.15943961598919179</v>
       </c>
       <c r="T42" s="128">
-        <v>0.16412174621829045</v>
+        <v>0.16529676738286361</v>
       </c>
       <c r="U42" s="39"/>
       <c r="V42" s="29"/>
       <c r="W42" s="32">
-        <v>5.0295822437509026</v>
+        <v>5.1439527690819551</v>
       </c>
       <c r="X42" s="30" t="s">
         <v>69</v>
@@ -8577,34 +8577,34 @@
         <v>59125.310173697268</v>
       </c>
       <c r="AB42" s="27">
-        <v>68227.27</v>
+        <v>57015.820000000109</v>
       </c>
       <c r="AC42" s="39"/>
       <c r="AD42" s="29">
         <v>9353.561427150873</v>
       </c>
       <c r="AE42" s="29">
-        <v>10999.156399999998</v>
+        <v>9995.4888000000028</v>
       </c>
       <c r="AF42" s="31">
-        <v>1.1759324494381793</v>
+        <v>1.0686291930457406</v>
       </c>
       <c r="AG42" s="39"/>
       <c r="AH42" s="29">
-        <v>9976.9010141666749</v>
+        <v>10002.466858391626</v>
       </c>
       <c r="AI42" s="29">
-        <v>301185.81263916695</v>
+        <v>301851.43333741324</v>
       </c>
       <c r="AJ42" s="31">
-        <v>1.0612513814013662</v>
+        <v>1.0635967471385945</v>
       </c>
       <c r="AK42" s="39"/>
       <c r="AL42" s="80">
         <v>0.15943961598919179</v>
       </c>
       <c r="AM42" s="80">
-        <v>0.16121349132099227</v>
+        <v>0.17531079619656412</v>
       </c>
       <c r="AN42" s="39"/>
       <c r="AO42" s="32">
@@ -8669,51 +8669,51 @@
       </c>
       <c r="D44" s="34"/>
       <c r="E44" s="33">
-        <v>554184.50000000012</v>
+        <v>558361.12000000058</v>
       </c>
       <c r="F44" s="123">
-        <v>3.0118722826086963</v>
+        <v>3.0345713043478293</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="35">
         <v>184000</v>
       </c>
       <c r="I44" s="35">
-        <v>70769.230769230766</v>
+        <v>77846.153846153844</v>
       </c>
       <c r="J44" s="35">
-        <v>62209.240000000209</v>
+        <v>69528.230000000127</v>
       </c>
       <c r="K44" s="70">
-        <v>0.87904360869565512</v>
+        <v>0.8931491996047447</v>
       </c>
       <c r="L44" s="36"/>
       <c r="M44" s="35">
         <v>22080</v>
       </c>
       <c r="N44" s="35">
-        <v>8492.3076923076933</v>
+        <v>9341.5384615384628</v>
       </c>
       <c r="O44" s="37">
         <v>0</v>
       </c>
       <c r="P44" s="35">
-        <v>8774.1226000000079</v>
+        <v>9709.8097999999827</v>
       </c>
       <c r="Q44" s="115">
-        <v>1.0331847264492762</v>
+        <v>1.0394229858366251</v>
       </c>
       <c r="R44" s="36"/>
       <c r="S44" s="127">
         <v>0.12</v>
       </c>
       <c r="T44" s="127">
-        <v>0.14104211207209699</v>
+        <v>0.13965276837911686</v>
       </c>
       <c r="U44" s="36"/>
       <c r="V44" s="35"/>
       <c r="W44" s="38">
-        <v>3.5550387691607774</v>
+        <v>3.286060640404926</v>
       </c>
       <c r="X44" s="69" t="s">
         <v>69</v>
@@ -8724,38 +8724,38 @@
         <v>7076.9230769230771</v>
       </c>
       <c r="AB44" s="33">
-        <v>5474.449999999978</v>
+        <v>7318.9899999999725</v>
       </c>
       <c r="AC44" s="36"/>
       <c r="AD44" s="35">
         <v>849.23076923076928</v>
       </c>
       <c r="AE44" s="35">
-        <v>617.59705000000042</v>
+        <v>935.68720000000064</v>
       </c>
       <c r="AF44" s="115">
-        <v>0.72724290307971062</v>
+        <v>1.1018055797101456</v>
       </c>
       <c r="AG44" s="36"/>
       <c r="AH44" s="35">
-        <v>877.41226000000074</v>
+        <v>882.70998181818027</v>
       </c>
       <c r="AI44" s="35">
-        <v>22812.718760000018</v>
+        <v>22950.459527272687</v>
       </c>
       <c r="AJ44" s="115">
-        <v>1.0331847264492762</v>
+        <v>1.0394229858366253</v>
       </c>
       <c r="AK44" s="36"/>
       <c r="AL44" s="108">
         <v>0.12</v>
       </c>
       <c r="AM44" s="108">
-        <v>0.11281444711340918</v>
+        <v>0.12784375986304178</v>
       </c>
       <c r="AN44" s="36"/>
       <c r="AO44" s="38">
-        <v>-0.16975129921775578</v>
+        <v>0.99982647878972597</v>
       </c>
       <c r="AP44" s="70">
         <v>0</v>
@@ -8771,51 +8771,51 @@
       </c>
       <c r="D45" s="34"/>
       <c r="E45" s="33">
-        <v>934887.19</v>
+        <v>937335.32999999984</v>
       </c>
       <c r="F45" s="123">
-        <v>2.0775270888888886</v>
+        <v>2.0829673999999998</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="35">
         <v>450000</v>
       </c>
       <c r="I45" s="35">
-        <v>174193.54838709679</v>
+        <v>188709.67741935485</v>
       </c>
       <c r="J45" s="35">
-        <v>174628.28999999943</v>
+        <v>188981.9499999976</v>
       </c>
       <c r="K45" s="70">
-        <v>1.0024957388888855</v>
+        <v>1.0014428119657992</v>
       </c>
       <c r="L45" s="36"/>
       <c r="M45" s="35">
         <v>71629.254685760781</v>
       </c>
       <c r="N45" s="35">
-        <v>27727.453426746106</v>
+        <v>30038.074545641615</v>
       </c>
       <c r="O45" s="37">
         <v>0</v>
       </c>
       <c r="P45" s="35">
-        <v>34891.072129999462</v>
+        <v>37889.732979999528</v>
       </c>
       <c r="Q45" s="115">
-        <v>1.25835833507679</v>
+        <v>1.2613902040368015</v>
       </c>
       <c r="R45" s="36"/>
       <c r="S45" s="127">
         <v>0.15917612152391283</v>
       </c>
       <c r="T45" s="127">
-        <v>0.19980194577865693</v>
+        <v>0.20049392537223798</v>
       </c>
       <c r="U45" s="36"/>
       <c r="V45" s="35"/>
       <c r="W45" s="38">
-        <v>9.5169700911575479</v>
+        <v>9.5985002694693069</v>
       </c>
       <c r="X45" s="69" t="s">
         <v>69</v>
@@ -8826,38 +8826,38 @@
         <v>14516.129032258064</v>
       </c>
       <c r="AB45" s="33">
-        <v>11040.659999999922</v>
+        <v>14353.659999999905</v>
       </c>
       <c r="AC45" s="36"/>
       <c r="AD45" s="35">
         <v>2310.621118895509</v>
       </c>
       <c r="AE45" s="35">
-        <v>1959.3248000000003</v>
+        <v>2998.6608499999957</v>
       </c>
       <c r="AF45" s="115">
-        <v>0.8479645511664714</v>
+        <v>1.2977726315569096</v>
       </c>
       <c r="AG45" s="36"/>
       <c r="AH45" s="35">
-        <v>2907.5893441666217</v>
+        <v>2914.5948446153484</v>
       </c>
       <c r="AI45" s="35">
-        <v>90135.269669165267</v>
+        <v>90352.4401830758</v>
       </c>
       <c r="AJ45" s="115">
-        <v>1.2583583350767895</v>
+        <v>1.2613902040368012</v>
       </c>
       <c r="AK45" s="36"/>
       <c r="AL45" s="108">
         <v>0.15917612152391283</v>
       </c>
       <c r="AM45" s="108">
-        <v>0.17746446317521003</v>
+        <v>0.20891262925274914</v>
       </c>
       <c r="AN45" s="36"/>
       <c r="AO45" s="38">
-        <v>7.1920048257979126</v>
+        <v>10.590405861640205</v>
       </c>
       <c r="AP45" s="70">
         <v>0</v>
@@ -8873,51 +8873,51 @@
       </c>
       <c r="D46" s="34"/>
       <c r="E46" s="33">
-        <v>1157511.2900000012</v>
+        <v>1153206.1300000015</v>
       </c>
       <c r="F46" s="123">
-        <v>2.030721561403511</v>
+        <v>2.0231686491228098</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="35">
         <v>570000</v>
       </c>
       <c r="I46" s="35">
-        <v>220645.16129032261</v>
+        <v>239032.25806451615</v>
       </c>
       <c r="J46" s="35">
-        <v>242915.25999998883</v>
+        <v>260496.38999998628</v>
       </c>
       <c r="K46" s="70">
-        <v>1.100931733918078</v>
+        <v>1.0897959635626955</v>
       </c>
       <c r="L46" s="36"/>
       <c r="M46" s="35">
         <v>95190</v>
       </c>
       <c r="N46" s="35">
-        <v>36847.741935483871</v>
+        <v>39918.38709677419</v>
       </c>
       <c r="O46" s="37">
         <v>364.28000000000003</v>
       </c>
       <c r="P46" s="35">
-        <v>43954.640209999918</v>
+        <v>46961.515550000076</v>
       </c>
       <c r="Q46" s="115">
-        <v>1.1928720160643602</v>
+        <v>1.1764382021786408</v>
       </c>
       <c r="R46" s="36"/>
       <c r="S46" s="127">
         <v>0.16700000000000001</v>
       </c>
       <c r="T46" s="127">
-        <v>0.18094639344601873</v>
+        <v>0.18027703013466922</v>
       </c>
       <c r="U46" s="36"/>
       <c r="V46" s="35"/>
       <c r="W46" s="38">
-        <v>7.4192663770858713</v>
+        <v>7.3591021933117338</v>
       </c>
       <c r="X46" s="69" t="s">
         <v>69</v>
@@ -8928,38 +8928,38 @@
         <v>18387.096774193549</v>
       </c>
       <c r="AB46" s="33">
-        <v>15128.969999999901</v>
+        <v>17581.129999999896</v>
       </c>
       <c r="AC46" s="36"/>
       <c r="AD46" s="35">
         <v>3070.6451612903224</v>
       </c>
       <c r="AE46" s="35">
-        <v>2770.2023899999972</v>
+        <v>3006.8753399999978</v>
       </c>
       <c r="AF46" s="115">
-        <v>0.90215646696081431</v>
+        <v>0.9792324355499521</v>
       </c>
       <c r="AG46" s="36"/>
       <c r="AH46" s="35">
-        <v>3662.88668416666</v>
+        <v>3612.4242730769288</v>
       </c>
       <c r="AI46" s="35">
-        <v>113549.48720916646</v>
+        <v>111985.15246538479</v>
       </c>
       <c r="AJ46" s="115">
-        <v>1.1928720160643602</v>
+        <v>1.1764382021786406</v>
       </c>
       <c r="AK46" s="36"/>
       <c r="AL46" s="108">
         <v>0.16700000000000001</v>
       </c>
       <c r="AM46" s="108">
-        <v>0.18310581553139541</v>
+        <v>0.17102855959770594</v>
       </c>
       <c r="AN46" s="36"/>
       <c r="AO46" s="38">
-        <v>7.6565185204273787</v>
+        <v>6.5278246620092366</v>
       </c>
       <c r="AP46" s="70">
         <v>0</v>
@@ -8975,51 +8975,51 @@
       </c>
       <c r="D47" s="34"/>
       <c r="E47" s="33">
-        <v>36880.15</v>
+        <v>41245.730000000018</v>
       </c>
       <c r="F47" s="123">
-        <v>1.6763704545454545</v>
+        <v>1.8748059090909099</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="35">
         <v>22000</v>
       </c>
       <c r="I47" s="35">
-        <v>8461.538461538461</v>
+        <v>9307.6923076923085</v>
       </c>
       <c r="J47" s="35">
-        <v>13912.24999999996</v>
+        <v>14610.389999999959</v>
       </c>
       <c r="K47" s="70">
-        <v>1.6441749999999953</v>
+        <v>1.5697113223140451</v>
       </c>
       <c r="L47" s="36"/>
       <c r="M47" s="35">
         <v>3740.0000000000005</v>
       </c>
       <c r="N47" s="35">
-        <v>1438.4615384615386</v>
+        <v>1582.3076923076926</v>
       </c>
       <c r="O47" s="37">
         <v>2650</v>
       </c>
       <c r="P47" s="35">
-        <v>-4898.2499999999945</v>
+        <v>-4744.6499999999851</v>
       </c>
       <c r="Q47" s="115">
-        <v>-3.4052005347593544</v>
+        <v>-2.9985634419056777</v>
       </c>
       <c r="R47" s="36"/>
       <c r="S47" s="127">
         <v>0.17</v>
       </c>
       <c r="T47" s="127">
-        <v>-0.35208179841506648</v>
+        <v>-0.32474492467346855</v>
       </c>
       <c r="U47" s="36"/>
       <c r="V47" s="35"/>
       <c r="W47" s="38">
-        <v>-67.439702420529073</v>
+        <v>-63.655453413632635</v>
       </c>
       <c r="X47" s="69" t="s">
         <v>69</v>
@@ -9030,38 +9030,38 @@
         <v>846.15384615384619</v>
       </c>
       <c r="AB47" s="33">
-        <v>565.10000000000025</v>
+        <v>698.14000000000055</v>
       </c>
       <c r="AC47" s="36"/>
       <c r="AD47" s="35">
         <v>143.84615384615387</v>
       </c>
       <c r="AE47" s="35">
-        <v>126.62</v>
+        <v>153.6</v>
       </c>
       <c r="AF47" s="115">
-        <v>0.88024598930481268</v>
+        <v>1.0678074866310159</v>
       </c>
       <c r="AG47" s="36"/>
       <c r="AH47" s="35">
-        <v>-489.82499999999948</v>
+        <v>-431.3318181818168</v>
       </c>
       <c r="AI47" s="35">
-        <v>-12735.449999999986</v>
+        <v>-11214.627272727237</v>
       </c>
       <c r="AJ47" s="115">
-        <v>-3.4052005347593544</v>
+        <v>-2.9985634419056781</v>
       </c>
       <c r="AK47" s="36"/>
       <c r="AL47" s="108">
         <v>0.17</v>
       </c>
       <c r="AM47" s="108">
-        <v>0.22406653689612449</v>
+        <v>0.2200131778726328</v>
       </c>
       <c r="AN47" s="36"/>
       <c r="AO47" s="38">
-        <v>12.123517961422809</v>
+        <v>11.755521815108796</v>
       </c>
       <c r="AP47" s="70">
         <v>0</v>
@@ -9075,51 +9075,51 @@
       </c>
       <c r="D48" s="28"/>
       <c r="E48" s="27">
-        <v>2683463.1300000013</v>
+        <v>2690148.3100000019</v>
       </c>
       <c r="F48" s="124">
-        <v>2.1887953752039162</v>
+        <v>2.194248213703101</v>
       </c>
       <c r="G48" s="26"/>
       <c r="H48" s="29">
         <v>1226000</v>
       </c>
       <c r="I48" s="29">
-        <v>474069.47890818858</v>
+        <v>514895.7816377171</v>
       </c>
       <c r="J48" s="29">
-        <v>493665.0399999884</v>
+        <v>533616.95999998401</v>
       </c>
       <c r="K48" s="31">
-        <v>1.0413347873331344</v>
+        <v>1.0363591604940341</v>
       </c>
       <c r="L48" s="39"/>
       <c r="M48" s="29">
         <v>192639.25468576077</v>
       </c>
       <c r="N48" s="29">
-        <v>74505.964592999197</v>
+        <v>80880.307796261957</v>
       </c>
       <c r="O48" s="27">
         <v>3014.28</v>
       </c>
       <c r="P48" s="29">
-        <v>82721.584939999389</v>
+        <v>89816.408329999613</v>
       </c>
       <c r="Q48" s="31">
-        <v>1.1102679549466856</v>
+        <v>1.1104854911809652</v>
       </c>
       <c r="R48" s="39"/>
       <c r="S48" s="128">
         <v>0.15712826646473146</v>
       </c>
       <c r="T48" s="128">
-        <v>0.16756622048829167</v>
+        <v>0.16831625503432707</v>
       </c>
       <c r="U48" s="39"/>
       <c r="V48" s="29"/>
       <c r="W48" s="32">
-        <v>5.5647114367245054</v>
+        <v>5.6771168461336208</v>
       </c>
       <c r="X48" s="30" t="s">
         <v>69</v>
@@ -9130,34 +9130,34 @@
         <v>40826.302729528536</v>
       </c>
       <c r="AB48" s="27">
-        <v>32209.179999999797</v>
+        <v>39951.919999999773</v>
       </c>
       <c r="AC48" s="39"/>
       <c r="AD48" s="29">
         <v>6374.3432032627552</v>
       </c>
       <c r="AE48" s="29">
-        <v>5473.7442399999973</v>
+        <v>7094.8233899999941</v>
       </c>
       <c r="AF48" s="31">
-        <v>0.85871501823093244</v>
+        <v>1.1130281448241532</v>
       </c>
       <c r="AG48" s="39"/>
       <c r="AH48" s="29">
-        <v>6958.0632883332828</v>
+        <v>6978.3972813286409</v>
       </c>
       <c r="AI48" s="29">
-        <v>213762.02563833175</v>
+        <v>214073.42490300603</v>
       </c>
       <c r="AJ48" s="31">
-        <v>1.1096493598203914</v>
+        <v>1.1112658489683702</v>
       </c>
       <c r="AK48" s="39"/>
       <c r="AL48" s="80">
         <v>0.15712826646473146</v>
       </c>
       <c r="AM48" s="80">
-        <v>0.16994360738149905</v>
+        <v>0.17758404076700279</v>
       </c>
       <c r="AN48" s="39"/>
       <c r="AO48" s="32">
@@ -9222,51 +9222,51 @@
       </c>
       <c r="D50" s="34"/>
       <c r="E50" s="33">
-        <v>121431.65</v>
+        <v>138995.09</v>
       </c>
       <c r="F50" s="123">
-        <v>0.20936491379310343</v>
+        <v>0.23964670689655171</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="35">
         <v>580000</v>
       </c>
       <c r="I50" s="35">
-        <v>223076.92307692309</v>
+        <v>245384.6153846154</v>
       </c>
       <c r="J50" s="35">
-        <v>194560.23999999953</v>
+        <v>222540.89999999935</v>
       </c>
       <c r="K50" s="70">
-        <v>0.87216659310344613</v>
+        <v>0.90690648902821047</v>
       </c>
       <c r="L50" s="36"/>
       <c r="M50" s="35">
         <v>98020</v>
       </c>
       <c r="N50" s="35">
-        <v>37700</v>
+        <v>41470</v>
       </c>
       <c r="O50" s="37">
         <v>0</v>
       </c>
       <c r="P50" s="35">
-        <v>33606.823500000071</v>
+        <v>39210.721400000097</v>
       </c>
       <c r="Q50" s="115">
-        <v>0.89142767904509468</v>
+        <v>0.94552016879672285</v>
       </c>
       <c r="R50" s="36"/>
       <c r="S50" s="127">
         <v>0.16900000000000001</v>
       </c>
       <c r="T50" s="127">
-        <v>0.1727322267900171</v>
+        <v>0.1761955730384851</v>
       </c>
       <c r="U50" s="36"/>
       <c r="V50" s="35"/>
       <c r="W50" s="38">
-        <v>-10.515245303973836</v>
+        <v>-10.431052718848687</v>
       </c>
       <c r="X50" s="69" t="s">
         <v>69</v>
@@ -9277,38 +9277,38 @@
         <v>22307.692307692309</v>
       </c>
       <c r="AB50" s="33">
-        <v>26073.289999999997</v>
+        <v>27980.660000000007</v>
       </c>
       <c r="AC50" s="36"/>
       <c r="AD50" s="35">
         <v>3770</v>
       </c>
       <c r="AE50" s="35">
-        <v>4124.2993999999999</v>
+        <v>5603.8979000000008</v>
       </c>
       <c r="AF50" s="115">
-        <v>1.0939786206896551</v>
+        <v>1.4864450663129976</v>
       </c>
       <c r="AG50" s="36"/>
       <c r="AH50" s="35">
-        <v>3360.6823500000073</v>
+        <v>3564.6110363636453</v>
       </c>
       <c r="AI50" s="35">
-        <v>87377.741100000188</v>
+        <v>92679.886945454782</v>
       </c>
       <c r="AJ50" s="115">
-        <v>0.89142767904509479</v>
+        <v>0.94552016879672296</v>
       </c>
       <c r="AK50" s="36"/>
       <c r="AL50" s="108">
         <v>0.16900000000000001</v>
       </c>
       <c r="AM50" s="108">
-        <v>0.15818101206253604</v>
+        <v>0.20027754527591557</v>
       </c>
       <c r="AN50" s="36"/>
       <c r="AO50" s="38">
-        <v>-14.906636638490966</v>
+        <v>-9.845629445481233</v>
       </c>
       <c r="AP50" s="70">
         <v>0</v>
@@ -9324,51 +9324,51 @@
       </c>
       <c r="D51" s="34"/>
       <c r="E51" s="33">
-        <v>101535.80999999997</v>
+        <v>104561.74999999997</v>
       </c>
       <c r="F51" s="123">
-        <v>0.39817964705882342</v>
+        <v>0.41004607843137242</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="35">
         <v>255000</v>
       </c>
       <c r="I51" s="35">
-        <v>98709.677419354848</v>
+        <v>106935.48387096774</v>
       </c>
       <c r="J51" s="35">
-        <v>90247.480000000214</v>
+        <v>95969.90000000014</v>
       </c>
       <c r="K51" s="70">
-        <v>0.91427185620915241</v>
+        <v>0.89745607843137387</v>
       </c>
       <c r="L51" s="36"/>
       <c r="M51" s="35">
         <v>50745</v>
       </c>
       <c r="N51" s="35">
-        <v>19643.225806451614</v>
+        <v>21280.161290322583</v>
       </c>
       <c r="O51" s="37">
         <v>0</v>
       </c>
       <c r="P51" s="35">
-        <v>19803.0609</v>
+        <v>21044.400200000004</v>
       </c>
       <c r="Q51" s="115">
-        <v>1.0081369065917825</v>
+        <v>0.9889210853665007</v>
       </c>
       <c r="R51" s="36"/>
       <c r="S51" s="127">
         <v>0.19900000000000001</v>
       </c>
       <c r="T51" s="127">
-        <v>0.21943062454486212</v>
+        <v>0.21928125589377476</v>
       </c>
       <c r="U51" s="36"/>
       <c r="V51" s="35"/>
       <c r="W51" s="38">
-        <v>3.5425708285704003</v>
+        <v>3.682363115935078</v>
       </c>
       <c r="X51" s="69" t="s">
         <v>69</v>
@@ -9379,38 +9379,38 @@
         <v>8225.8064516129034</v>
       </c>
       <c r="AB51" s="33">
-        <v>5089.5499999999984</v>
+        <v>5722.4199999999973</v>
       </c>
       <c r="AC51" s="36"/>
       <c r="AD51" s="35">
         <v>1636.9354838709678</v>
       </c>
       <c r="AE51" s="35">
-        <v>1148.5110500000003</v>
+        <v>1241.3393000000005</v>
       </c>
       <c r="AF51" s="115">
-        <v>0.70162267316977056</v>
+        <v>0.7583312306631198</v>
       </c>
       <c r="AG51" s="36"/>
       <c r="AH51" s="35">
-        <v>1650.255075</v>
+        <v>1618.8000153846156</v>
       </c>
       <c r="AI51" s="35">
-        <v>51157.907325</v>
+        <v>50182.800476923083</v>
       </c>
       <c r="AJ51" s="115">
-        <v>1.0081369065917825</v>
+        <v>0.98892108536650081</v>
       </c>
       <c r="AK51" s="36"/>
       <c r="AL51" s="108">
         <v>0.19900000000000001</v>
       </c>
       <c r="AM51" s="108">
-        <v>0.22566062814983656</v>
+        <v>0.21692558393127404</v>
       </c>
       <c r="AN51" s="36"/>
       <c r="AO51" s="38">
-        <v>4.3597380907938685</v>
+        <v>5.8870075946889724</v>
       </c>
       <c r="AP51" s="70">
         <v>0</v>
@@ -9426,51 +9426,51 @@
       </c>
       <c r="D52" s="34"/>
       <c r="E52" s="33">
-        <v>176649.38999999993</v>
+        <v>168520.79</v>
       </c>
       <c r="F52" s="123">
-        <v>0.38402041304347811</v>
+        <v>0.36634954347826088</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="35">
         <v>460000</v>
       </c>
       <c r="I52" s="35">
-        <v>178064.51612903224</v>
+        <v>192903.22580645161</v>
       </c>
       <c r="J52" s="35">
-        <v>147884.68999999983</v>
+        <v>166432.54999999967</v>
       </c>
       <c r="K52" s="70">
-        <v>0.83051184601449191</v>
+        <v>0.86277743311036625</v>
       </c>
       <c r="L52" s="36"/>
       <c r="M52" s="35">
         <v>95534.936056770661</v>
       </c>
       <c r="N52" s="35">
-        <v>36981.265570362833</v>
+        <v>40063.037701226407</v>
       </c>
       <c r="O52" s="37">
         <v>0</v>
       </c>
       <c r="P52" s="35">
-        <v>33585.474200000004</v>
+        <v>36916.069149999996</v>
       </c>
       <c r="Q52" s="115">
-        <v>0.90817536074037841</v>
+        <v>0.92144957717147657</v>
       </c>
       <c r="R52" s="36"/>
       <c r="S52" s="127">
         <v>0.20768464360167535</v>
       </c>
       <c r="T52" s="127">
-        <v>0.22710582278665928</v>
+        <v>0.22180798858156092</v>
       </c>
       <c r="U52" s="36"/>
       <c r="V52" s="35"/>
       <c r="W52" s="38">
-        <v>2.822803496426642</v>
+        <v>1.6212508610843046</v>
       </c>
       <c r="X52" s="69" t="s">
         <v>69</v>
@@ -9481,38 +9481,38 @@
         <v>14838.709677419354</v>
       </c>
       <c r="AB52" s="33">
-        <v>6429.5099999999993</v>
+        <v>18547.859999999997</v>
       </c>
       <c r="AC52" s="36"/>
       <c r="AD52" s="35">
         <v>3081.7721308635696</v>
       </c>
       <c r="AE52" s="35">
-        <v>1611.2023000000004</v>
+        <v>3330.5949499999979</v>
       </c>
       <c r="AF52" s="115">
-        <v>0.52281681824039072</v>
+        <v>1.0807401743446565</v>
       </c>
       <c r="AG52" s="36"/>
       <c r="AH52" s="35">
-        <v>2798.7895166666672</v>
+        <v>2839.6976269230768</v>
       </c>
       <c r="AI52" s="35">
-        <v>86762.475016666678</v>
+        <v>88030.626434615377</v>
       </c>
       <c r="AJ52" s="115">
-        <v>0.90817536074037841</v>
+        <v>0.92144957717147657</v>
       </c>
       <c r="AK52" s="36"/>
       <c r="AL52" s="108">
         <v>0.20768464360167535</v>
       </c>
       <c r="AM52" s="108">
-        <v>0.25059488203611169</v>
+        <v>0.17956761319095563</v>
       </c>
       <c r="AN52" s="36"/>
       <c r="AO52" s="38">
-        <v>6.6232465615575737</v>
+        <v>-7.9588968754347693</v>
       </c>
       <c r="AP52" s="70">
         <v>0</v>
@@ -9528,51 +9528,51 @@
       </c>
       <c r="D53" s="34"/>
       <c r="E53" s="33">
-        <v>32576.359999999997</v>
+        <v>32744.410000000003</v>
       </c>
       <c r="F53" s="123">
-        <v>8.5727263157894723E-2</v>
+        <v>8.616950000000001E-2</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="35">
         <v>380000</v>
       </c>
       <c r="I53" s="35">
-        <v>146153.84615384616</v>
+        <v>160769.23076923078</v>
       </c>
       <c r="J53" s="35">
-        <v>70257.750000000015</v>
+        <v>79233.88</v>
       </c>
       <c r="K53" s="70">
-        <v>0.48071092105263169</v>
+        <v>0.49284231578947368</v>
       </c>
       <c r="L53" s="36"/>
       <c r="M53" s="35">
         <v>77231.730048526413</v>
       </c>
       <c r="N53" s="35">
-        <v>29704.511557125545</v>
+        <v>32674.962712838096</v>
       </c>
       <c r="O53" s="37">
         <v>463.78</v>
       </c>
       <c r="P53" s="35">
-        <v>9856.1299999999992</v>
+        <v>12086.500000000002</v>
       </c>
       <c r="Q53" s="115">
-        <v>0.33180582623098887</v>
+        <v>0.36990095769110631</v>
       </c>
       <c r="R53" s="36"/>
       <c r="S53" s="127">
         <v>0.20324139486454318</v>
       </c>
       <c r="T53" s="127">
-        <v>0.14028530660318608</v>
+        <v>0.15254206912497534</v>
       </c>
       <c r="U53" s="36"/>
       <c r="V53" s="35"/>
       <c r="W53" s="38">
-        <v>-1.5323576402603143</v>
+        <v>-0.98182747077383214</v>
       </c>
       <c r="X53" s="69" t="s">
         <v>69</v>
@@ -9583,38 +9583,38 @@
         <v>14615.384615384615</v>
       </c>
       <c r="AB53" s="33">
-        <v>1243.28</v>
+        <v>8976.130000000001</v>
       </c>
       <c r="AC53" s="36"/>
       <c r="AD53" s="35">
         <v>2970.4511557125543</v>
       </c>
       <c r="AE53" s="35">
-        <v>192.37000000000003</v>
+        <v>2230.3700000000008</v>
       </c>
       <c r="AF53" s="115">
-        <v>6.4761206266613108E-2</v>
+        <v>0.75085227229228002</v>
       </c>
       <c r="AG53" s="36"/>
       <c r="AH53" s="35">
-        <v>985.61299999999994</v>
+        <v>1098.7727272727275</v>
       </c>
       <c r="AI53" s="35">
-        <v>25625.937999999998</v>
+        <v>28568.090909090915</v>
       </c>
       <c r="AJ53" s="115">
-        <v>0.33180582623098887</v>
+        <v>0.36990095769110637</v>
       </c>
       <c r="AK53" s="36"/>
       <c r="AL53" s="108">
         <v>0.20324139486454318</v>
       </c>
       <c r="AM53" s="108">
-        <v>0.15472781674280936</v>
+        <v>0.24847790751693666</v>
       </c>
       <c r="AN53" s="36"/>
       <c r="AO53" s="38">
-        <v>3.0572356991184604</v>
+        <v>3.3272691014947604</v>
       </c>
       <c r="AP53" s="70">
         <v>0</v>
@@ -9628,51 +9628,51 @@
       </c>
       <c r="D54" s="28"/>
       <c r="E54" s="27">
-        <v>432193.20999999985</v>
+        <v>444822.04000000004</v>
       </c>
       <c r="F54" s="124">
-        <v>0.25802579701492528</v>
+        <v>0.26556539701492538</v>
       </c>
       <c r="G54" s="26"/>
       <c r="H54" s="29">
         <v>1675000</v>
       </c>
       <c r="I54" s="29">
-        <v>646004.96277915628</v>
+        <v>705992.55583126552</v>
       </c>
       <c r="J54" s="29">
-        <v>502950.15999999957</v>
+        <v>564177.22999999917</v>
       </c>
       <c r="K54" s="31">
-        <v>0.77855463808865266</v>
+        <v>0.79912631562483405</v>
       </c>
       <c r="L54" s="39"/>
       <c r="M54" s="29">
         <v>321531.6661052971</v>
       </c>
       <c r="N54" s="29">
-        <v>124029.00293393999</v>
+        <v>135488.16170438711</v>
       </c>
       <c r="O54" s="27">
         <v>463.78</v>
       </c>
       <c r="P54" s="29">
-        <v>96851.48860000007</v>
+        <v>109257.6907500001</v>
       </c>
       <c r="Q54" s="31">
-        <v>0.78087774882448147</v>
+        <v>0.80640027420537608</v>
       </c>
       <c r="R54" s="39"/>
       <c r="S54" s="128">
         <v>0.1919592036449535</v>
       </c>
       <c r="T54" s="128">
-        <v>0.19256677162603975</v>
+        <v>0.19365845507448121</v>
       </c>
       <c r="U54" s="39"/>
       <c r="V54" s="29"/>
       <c r="W54" s="32">
-        <v>-2.8160864686871889</v>
+        <v>-3.1477784472090309</v>
       </c>
       <c r="X54" s="30" t="s">
         <v>69</v>
@@ -9683,34 +9683,34 @@
         <v>59987.593052109187</v>
       </c>
       <c r="AB54" s="27">
-        <v>38835.629999999997</v>
+        <v>61227.070000000007</v>
       </c>
       <c r="AC54" s="39"/>
       <c r="AD54" s="29">
         <v>11459.158770447091</v>
       </c>
       <c r="AE54" s="29">
-        <v>7076.3827499999998</v>
+        <v>12406.202149999999</v>
       </c>
       <c r="AF54" s="31">
-        <v>0.61753073604755604</v>
+        <v>1.0826451049788499</v>
       </c>
       <c r="AG54" s="39"/>
       <c r="AH54" s="29">
-        <v>8795.3399416666743</v>
+        <v>9121.8814059440647</v>
       </c>
       <c r="AI54" s="29">
-        <v>250924.06144166688</v>
+        <v>259461.40476608416</v>
       </c>
       <c r="AJ54" s="31">
-        <v>0.78040233013781224</v>
+        <v>0.80695443751756069</v>
       </c>
       <c r="AK54" s="39"/>
       <c r="AL54" s="80">
         <v>0.1919592036449535</v>
       </c>
       <c r="AM54" s="80">
-        <v>0.18221367208411451</v>
+        <v>0.20262609577757024</v>
       </c>
       <c r="AN54" s="39"/>
       <c r="AO54" s="32">
@@ -9775,51 +9775,51 @@
       </c>
       <c r="D56" s="34"/>
       <c r="E56" s="33">
-        <v>347851.48999999982</v>
+        <v>353921.8199999996</v>
       </c>
       <c r="F56" s="123">
-        <v>4.5769932894736822</v>
+        <v>4.6568660526315737</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="35">
         <v>76000</v>
       </c>
       <c r="I56" s="35">
-        <v>29230.769230769227</v>
+        <v>32153.846153846152</v>
       </c>
       <c r="J56" s="35">
-        <v>25836.000000000557</v>
+        <v>28192.080000000777</v>
       </c>
       <c r="K56" s="70">
-        <v>0.883863157894756</v>
+        <v>0.87678717703351705</v>
       </c>
       <c r="L56" s="36"/>
       <c r="M56" s="35">
         <v>16644</v>
       </c>
       <c r="N56" s="35">
-        <v>6401.5384615384619</v>
+        <v>7041.6923076923085</v>
       </c>
       <c r="O56" s="37">
         <v>0</v>
       </c>
       <c r="P56" s="35">
-        <v>5862.8399999999911</v>
+        <v>6440.509999999992</v>
       </c>
       <c r="Q56" s="115">
-        <v>0.91584859408795816</v>
+        <v>0.91462530860151503</v>
       </c>
       <c r="R56" s="36"/>
       <c r="S56" s="127">
         <v>0.219</v>
       </c>
       <c r="T56" s="127">
-        <v>0.22692522062238213</v>
+        <v>0.22845104015027676</v>
       </c>
       <c r="U56" s="36"/>
       <c r="V56" s="35"/>
       <c r="W56" s="38">
-        <v>10.9866078340317</v>
+        <v>11.176046605999399</v>
       </c>
       <c r="X56" s="69" t="s">
         <v>69</v>
@@ -9830,38 +9830,38 @@
         <v>2923.0769230769229</v>
       </c>
       <c r="AB56" s="33">
-        <v>1793.9000000000008</v>
+        <v>2356.079999999999</v>
       </c>
       <c r="AC56" s="36"/>
       <c r="AD56" s="35">
         <v>640.15384615384619</v>
       </c>
       <c r="AE56" s="35">
-        <v>396.7399999999999</v>
+        <v>577.66999999999996</v>
       </c>
       <c r="AF56" s="115">
-        <v>0.61975726988704616</v>
+        <v>0.90239245373708232</v>
       </c>
       <c r="AG56" s="36"/>
       <c r="AH56" s="35">
-        <v>586.28399999999908</v>
+        <v>585.50090909090841</v>
       </c>
       <c r="AI56" s="35">
-        <v>15243.383999999976</v>
+        <v>15223.023636363618</v>
       </c>
       <c r="AJ56" s="115">
-        <v>0.91584859408795816</v>
+        <v>0.91462530860151514</v>
       </c>
       <c r="AK56" s="36"/>
       <c r="AL56" s="108">
         <v>0.219</v>
       </c>
       <c r="AM56" s="108">
-        <v>0.22116059981046865</v>
+        <v>0.24518267630980281</v>
       </c>
       <c r="AN56" s="36"/>
       <c r="AO56" s="38">
-        <v>10.42477284129556</v>
+        <v>13.25337000441405</v>
       </c>
       <c r="AP56" s="70">
         <v>0</v>
@@ -9877,51 +9877,51 @@
       </c>
       <c r="D57" s="34"/>
       <c r="E57" s="33">
-        <v>501999.19999999978</v>
+        <v>499365.24999999942</v>
       </c>
       <c r="F57" s="123">
-        <v>2.5099959999999988</v>
+        <v>2.4968262499999971</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="35">
         <v>200000</v>
       </c>
       <c r="I57" s="35">
-        <v>77419.354838709682</v>
+        <v>83870.967741935485</v>
       </c>
       <c r="J57" s="35">
-        <v>73689.830000000758</v>
+        <v>78359.100000000879</v>
       </c>
       <c r="K57" s="70">
-        <v>0.95182697083334311</v>
+        <v>0.93428157692308744</v>
       </c>
       <c r="L57" s="36"/>
       <c r="M57" s="35">
         <v>45000</v>
       </c>
       <c r="N57" s="35">
-        <v>17419.354838709674</v>
+        <v>18870.967741935481</v>
       </c>
       <c r="O57" s="37">
         <v>0</v>
       </c>
       <c r="P57" s="35">
-        <v>16355.16000000002</v>
+        <v>17322.320000000011</v>
       </c>
       <c r="Q57" s="115">
-        <v>0.93890733333333465</v>
+        <v>0.91793490598290672</v>
       </c>
       <c r="R57" s="36"/>
       <c r="S57" s="127">
         <v>0.22500000000000001</v>
       </c>
       <c r="T57" s="127">
-        <v>0.22194595916424087</v>
+        <v>0.2210632842898887</v>
       </c>
       <c r="U57" s="36"/>
       <c r="V57" s="35"/>
       <c r="W57" s="38">
-        <v>10.243923754473027</v>
+        <v>10.177477791348739</v>
       </c>
       <c r="X57" s="69" t="s">
         <v>69</v>
@@ -9932,38 +9932,38 @@
         <v>6451.6129032258068</v>
       </c>
       <c r="AB57" s="33">
-        <v>3793.4699999999934</v>
+        <v>4669.2699999999904</v>
       </c>
       <c r="AC57" s="36"/>
       <c r="AD57" s="35">
         <v>1451.6129032258063</v>
       </c>
       <c r="AE57" s="35">
-        <v>839.1499999999993</v>
+        <v>967.15999999999985</v>
       </c>
       <c r="AF57" s="115">
-        <v>0.57808111111111071</v>
+        <v>0.66626577777777773</v>
       </c>
       <c r="AG57" s="36"/>
       <c r="AH57" s="35">
-        <v>1362.9300000000017</v>
+        <v>1332.4861538461546</v>
       </c>
       <c r="AI57" s="35">
-        <v>42250.830000000053</v>
+        <v>41307.070769230791</v>
       </c>
       <c r="AJ57" s="115">
-        <v>0.93890733333333454</v>
+        <v>0.9179349059829065</v>
       </c>
       <c r="AK57" s="36"/>
       <c r="AL57" s="108">
         <v>0.22500000000000001</v>
       </c>
       <c r="AM57" s="108">
-        <v>0.22120907770458201</v>
+        <v>0.20713302079340065</v>
       </c>
       <c r="AN57" s="36"/>
       <c r="AO57" s="38">
-        <v>10.311930765235861</v>
+        <v>9.1288359850681537</v>
       </c>
       <c r="AP57" s="70">
         <v>0</v>
@@ -9979,51 +9979,51 @@
       </c>
       <c r="D58" s="34"/>
       <c r="E58" s="33">
-        <v>583453.87999999861</v>
+        <v>580176.9399999989</v>
       </c>
       <c r="F58" s="123">
-        <v>2.7783518095238029</v>
+        <v>2.7627473333333281</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="35">
         <v>210000</v>
       </c>
       <c r="I58" s="35">
-        <v>81290.322580645152</v>
+        <v>88064.516129032258</v>
       </c>
       <c r="J58" s="35">
-        <v>88623.250000000902</v>
+        <v>94413.300000001167</v>
       </c>
       <c r="K58" s="70">
-        <v>1.0902066468254081</v>
+        <v>1.0720924175824309</v>
       </c>
       <c r="L58" s="36"/>
       <c r="M58" s="35">
         <v>49770</v>
       </c>
       <c r="N58" s="35">
-        <v>19265.806451612902</v>
+        <v>20871.290322580644</v>
       </c>
       <c r="O58" s="37">
         <v>0</v>
       </c>
       <c r="P58" s="35">
-        <v>18056.390000000025</v>
+        <v>19204.760000000009</v>
       </c>
       <c r="Q58" s="115">
-        <v>0.93722471703168042</v>
+        <v>0.92015202237987093</v>
       </c>
       <c r="R58" s="36"/>
       <c r="S58" s="127">
         <v>0.23699999999999999</v>
       </c>
       <c r="T58" s="127">
-        <v>0.20374326150304622</v>
+        <v>0.20341159561205649</v>
       </c>
       <c r="U58" s="36"/>
       <c r="V58" s="35"/>
       <c r="W58" s="38">
-        <v>8.5319822958427931</v>
+        <v>8.5165755248472994</v>
       </c>
       <c r="X58" s="69" t="s">
         <v>69</v>
@@ -10034,38 +10034,38 @@
         <v>6774.1935483870966</v>
       </c>
       <c r="AB58" s="33">
-        <v>4453.2699999999877</v>
+        <v>5790.0499999999829</v>
       </c>
       <c r="AC58" s="36"/>
       <c r="AD58" s="35">
         <v>1605.483870967742</v>
       </c>
       <c r="AE58" s="35">
-        <v>867.16999999999939</v>
+        <v>1148.3700000000013</v>
       </c>
       <c r="AF58" s="115">
-        <v>0.54012999799075712</v>
+        <v>0.71527968655816832</v>
       </c>
       <c r="AG58" s="36"/>
       <c r="AH58" s="35">
-        <v>1504.6991666666688</v>
+        <v>1477.2892307692314</v>
       </c>
       <c r="AI58" s="35">
-        <v>46645.674166666737</v>
+        <v>45795.966153846173</v>
       </c>
       <c r="AJ58" s="115">
-        <v>0.93722471703168042</v>
+        <v>0.92015202237987093</v>
       </c>
       <c r="AK58" s="36"/>
       <c r="AL58" s="108">
         <v>0.23699999999999999</v>
       </c>
       <c r="AM58" s="108">
-        <v>0.19472657171022681</v>
+        <v>0.19833507482664306</v>
       </c>
       <c r="AN58" s="36"/>
       <c r="AO58" s="38">
-        <v>7.9029567037253656</v>
+        <v>8.2807575064115255</v>
       </c>
       <c r="AP58" s="70">
         <v>0</v>
@@ -10081,51 +10081,51 @@
       </c>
       <c r="D59" s="34"/>
       <c r="E59" s="33">
-        <v>36379.249999999985</v>
+        <v>36684.409999999989</v>
       </c>
       <c r="F59" s="123">
-        <v>4.4364939024390226</v>
+        <v>4.4737085365853648</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="35">
         <v>8200</v>
       </c>
       <c r="I59" s="35">
-        <v>3153.8461538461534</v>
+        <v>3469.2307692307691</v>
       </c>
       <c r="J59" s="35">
-        <v>2825.7199999999962</v>
+        <v>3038.8899999999921</v>
       </c>
       <c r="K59" s="70">
-        <v>0.89595999999999887</v>
+        <v>0.8759549889135233</v>
       </c>
       <c r="L59" s="36"/>
       <c r="M59" s="35">
         <v>656</v>
       </c>
       <c r="N59" s="35">
-        <v>252.30769230769229</v>
+        <v>277.53846153846155</v>
       </c>
       <c r="O59" s="37">
         <v>0</v>
       </c>
       <c r="P59" s="35">
-        <v>482.93999999999977</v>
+        <v>530.49999999999966</v>
       </c>
       <c r="Q59" s="115">
-        <v>1.9140914634146333</v>
+        <v>1.9114467849223933</v>
       </c>
       <c r="R59" s="36"/>
       <c r="S59" s="127">
         <v>0.08</v>
       </c>
       <c r="T59" s="127">
-        <v>0.17090865336976077</v>
+        <v>0.17457032008397838</v>
       </c>
       <c r="U59" s="36"/>
       <c r="V59" s="35"/>
       <c r="W59" s="38">
-        <v>5.6587347649447297</v>
+        <v>5.9462501110600137</v>
       </c>
       <c r="X59" s="69" t="s">
         <v>69</v>
@@ -10136,38 +10136,38 @@
         <v>315.38461538461536</v>
       </c>
       <c r="AB59" s="33">
-        <v>294.90000000000009</v>
+        <v>213.17000000000004</v>
       </c>
       <c r="AC59" s="36"/>
       <c r="AD59" s="35">
         <v>25.23076923076923</v>
       </c>
       <c r="AE59" s="35">
-        <v>56.99</v>
+        <v>47.559999999999995</v>
       </c>
       <c r="AF59" s="115">
-        <v>2.25875</v>
+        <v>1.8849999999999998</v>
       </c>
       <c r="AG59" s="36"/>
       <c r="AH59" s="35">
-        <v>48.293999999999976</v>
+        <v>48.227272727272698</v>
       </c>
       <c r="AI59" s="35">
-        <v>1255.6439999999993</v>
+        <v>1253.9090909090901</v>
       </c>
       <c r="AJ59" s="115">
-        <v>1.9140914634146331</v>
+        <v>1.9114467849223935</v>
       </c>
       <c r="AK59" s="36"/>
       <c r="AL59" s="108">
         <v>0.08</v>
       </c>
       <c r="AM59" s="108">
-        <v>0.19325194981349605</v>
+        <v>0.2231083173054369</v>
       </c>
       <c r="AN59" s="36"/>
       <c r="AO59" s="38">
-        <v>7.5144116649712016</v>
+        <v>9.7574705634001191</v>
       </c>
       <c r="AP59" s="70">
         <v>0</v>
@@ -10181,51 +10181,51 @@
       </c>
       <c r="D60" s="28"/>
       <c r="E60" s="27">
-        <v>1469683.8199999982</v>
+        <v>1470148.4199999978</v>
       </c>
       <c r="F60" s="124">
-        <v>2.9738644678267869</v>
+        <v>2.9748045730473449</v>
       </c>
       <c r="G60" s="26"/>
       <c r="H60" s="29">
         <v>494200</v>
       </c>
       <c r="I60" s="29">
-        <v>191094.29280397022</v>
+        <v>207558.56079404466</v>
       </c>
       <c r="J60" s="29">
-        <v>190974.80000000223</v>
+        <v>204003.37000000282</v>
       </c>
       <c r="K60" s="31">
-        <v>0.9993746919271389</v>
+        <v>0.98287138443993372</v>
       </c>
       <c r="L60" s="39"/>
       <c r="M60" s="29">
         <v>112070</v>
       </c>
       <c r="N60" s="29">
-        <v>43339.007444168732</v>
+        <v>47061.488833746895</v>
       </c>
       <c r="O60" s="27">
         <v>0</v>
       </c>
       <c r="P60" s="29">
-        <v>40757.330000000038</v>
+        <v>43498.090000000011</v>
       </c>
       <c r="Q60" s="31">
-        <v>0.94043062828574175</v>
+        <v>0.92428206327396001</v>
       </c>
       <c r="R60" s="39"/>
       <c r="S60" s="128">
         <v>0.22677053824362606</v>
       </c>
       <c r="T60" s="128">
-        <v>0.21341731998148217</v>
+        <v>0.21322240902196571</v>
       </c>
       <c r="U60" s="39"/>
       <c r="V60" s="29"/>
       <c r="W60" s="32">
-        <v>9.4821149177806276</v>
+        <v>9.4837747043110312</v>
       </c>
       <c r="X60" s="30" t="s">
         <v>69</v>
@@ -10236,34 +10236,34 @@
         <v>16464.267990074441</v>
       </c>
       <c r="AB60" s="27">
-        <v>10335.539999999981</v>
+        <v>13028.569999999972</v>
       </c>
       <c r="AC60" s="39"/>
       <c r="AD60" s="29">
         <v>3722.4813895781635</v>
       </c>
       <c r="AE60" s="29">
-        <v>2160.0499999999984</v>
+        <v>2740.7600000000011</v>
       </c>
       <c r="AF60" s="31">
-        <v>0.58027153770264461</v>
+        <v>0.73627231761945422</v>
       </c>
       <c r="AG60" s="39"/>
       <c r="AH60" s="29">
-        <v>3502.2071666666698</v>
+        <v>3443.5035664335669</v>
       </c>
       <c r="AI60" s="29">
-        <v>105395.53216666676</v>
+        <v>103579.96965034967</v>
       </c>
       <c r="AJ60" s="31">
-        <v>0.94044375985247397</v>
+        <v>0.92424350540153177</v>
       </c>
       <c r="AK60" s="39"/>
       <c r="AL60" s="80">
         <v>0.22677053824362606</v>
       </c>
       <c r="AM60" s="80">
-        <v>0.20899246676999966</v>
+        <v>0.21036537394357224</v>
       </c>
       <c r="AN60" s="39"/>
       <c r="AO60" s="32">
@@ -10328,51 +10328,51 @@
       </c>
       <c r="D62" s="34"/>
       <c r="E62" s="33">
-        <v>231363.23000000007</v>
+        <v>215468.4800000001</v>
       </c>
       <c r="F62" s="123">
-        <v>0.21422521296296301</v>
+        <v>0.19950785185185194</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="35">
         <v>1080000</v>
       </c>
       <c r="I62" s="35">
-        <v>415384.61538461538</v>
+        <v>456923.07692307694</v>
       </c>
       <c r="J62" s="35">
-        <v>450540.40999999945</v>
+        <v>486673.43999999919</v>
       </c>
       <c r="K62" s="70">
-        <v>1.084634320370369</v>
+        <v>1.0651102222222204</v>
       </c>
       <c r="L62" s="36"/>
       <c r="M62" s="35">
         <v>43200</v>
       </c>
       <c r="N62" s="35">
-        <v>16615.384615384613</v>
+        <v>18276.923076923074</v>
       </c>
       <c r="O62" s="37">
         <v>0</v>
       </c>
       <c r="P62" s="35">
-        <v>8649.6502999999866</v>
+        <v>9170.5458999999792</v>
       </c>
       <c r="Q62" s="115">
-        <v>0.52058080509259186</v>
+        <v>0.50175545749158146</v>
       </c>
       <c r="R62" s="36"/>
       <c r="S62" s="127">
         <v>0.04</v>
       </c>
       <c r="T62" s="127">
-        <v>1.9198389551782928E-2</v>
+        <v>1.8843325207966957E-2</v>
       </c>
       <c r="U62" s="36"/>
       <c r="V62" s="35"/>
       <c r="W62" s="38">
-        <v>-11.579303108460644</v>
+        <v>-11.578025318168482</v>
       </c>
       <c r="X62" s="69" t="s">
         <v>69</v>
@@ -10383,38 +10383,38 @@
         <v>41538.461538461539</v>
       </c>
       <c r="AB62" s="33">
-        <v>35725.699999999983</v>
+        <v>36133.030000000006</v>
       </c>
       <c r="AC62" s="36"/>
       <c r="AD62" s="35">
         <v>1661.5384615384614</v>
       </c>
       <c r="AE62" s="35">
-        <v>236.14999999999958</v>
+        <v>520.89559999999881</v>
       </c>
       <c r="AF62" s="115">
-        <v>0.14212731481481458</v>
+        <v>0.31350198148148078</v>
       </c>
       <c r="AG62" s="36"/>
       <c r="AH62" s="35">
-        <v>864.96502999999871</v>
+        <v>833.68599090908901</v>
       </c>
       <c r="AI62" s="35">
-        <v>22489.090779999966</v>
+        <v>21675.835763636314</v>
       </c>
       <c r="AJ62" s="115">
-        <v>0.52058080509259186</v>
+        <v>0.50175545749158135</v>
       </c>
       <c r="AK62" s="36"/>
       <c r="AL62" s="108">
         <v>0.04</v>
       </c>
       <c r="AM62" s="108">
-        <v>6.6100874160618184E-3</v>
+        <v>1.4416050909652435E-2</v>
       </c>
       <c r="AN62" s="36"/>
       <c r="AO62" s="38">
-        <v>-12.837509132081475</v>
+        <v>-11.562092633803458</v>
       </c>
       <c r="AP62" s="70">
         <v>0</v>
@@ -10430,51 +10430,51 @@
       </c>
       <c r="D63" s="34"/>
       <c r="E63" s="33">
-        <v>253557.49999999997</v>
+        <v>248767.09</v>
       </c>
       <c r="F63" s="123">
-        <v>0.31694687499999996</v>
+        <v>0.31095886249999999</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="35">
         <v>800000</v>
       </c>
       <c r="I63" s="35">
-        <v>309677.41935483873</v>
+        <v>335483.87096774194</v>
       </c>
       <c r="J63" s="35">
-        <v>261230.57999999513</v>
+        <v>297004.06999999454</v>
       </c>
       <c r="K63" s="70">
-        <v>0.84355708124998419</v>
+        <v>0.88530059326921451</v>
       </c>
       <c r="L63" s="36"/>
       <c r="M63" s="35">
         <v>72000</v>
       </c>
       <c r="N63" s="35">
-        <v>27870.967741935485</v>
+        <v>30193.548387096773</v>
       </c>
       <c r="O63" s="37">
         <v>0</v>
       </c>
       <c r="P63" s="35">
-        <v>29481.144400000067</v>
+        <v>32735.197550000066</v>
       </c>
       <c r="Q63" s="115">
-        <v>1.057772542129632</v>
+        <v>1.0841785513354723</v>
       </c>
       <c r="R63" s="36"/>
       <c r="S63" s="127">
         <v>0.09</v>
       </c>
       <c r="T63" s="127">
-        <v>0.11285487480064783</v>
+        <v>0.11021800997542111</v>
       </c>
       <c r="U63" s="36"/>
       <c r="V63" s="35"/>
       <c r="W63" s="38">
-        <v>-0.33272735527527536</v>
+        <v>-0.63193829296857462</v>
       </c>
       <c r="X63" s="69" t="s">
         <v>69</v>
@@ -10485,38 +10485,38 @@
         <v>25806.451612903227</v>
       </c>
       <c r="AB63" s="33">
-        <v>20870.229999999992</v>
+        <v>35773.490000000013</v>
       </c>
       <c r="AC63" s="36"/>
       <c r="AD63" s="35">
         <v>2322.5806451612902</v>
       </c>
       <c r="AE63" s="35">
-        <v>2885.0862000000002</v>
+        <v>3254.0531499999993</v>
       </c>
       <c r="AF63" s="115">
-        <v>1.2421898916666667</v>
+        <v>1.4010506618055554</v>
       </c>
       <c r="AG63" s="36"/>
       <c r="AH63" s="35">
-        <v>2456.7620333333389</v>
+        <v>2518.0921192307742</v>
       </c>
       <c r="AI63" s="35">
-        <v>76159.623033333512</v>
+        <v>78060.855696154002</v>
       </c>
       <c r="AJ63" s="115">
-        <v>1.057772542129632</v>
+        <v>1.0841785513354723</v>
       </c>
       <c r="AK63" s="36"/>
       <c r="AL63" s="108">
         <v>0.09</v>
       </c>
       <c r="AM63" s="108">
-        <v>0.13823931025197142</v>
+        <v>9.096269751707195E-2</v>
       </c>
       <c r="AN63" s="36"/>
       <c r="AO63" s="38">
-        <v>1.1371997337835054</v>
+        <v>-2.8168815790686645</v>
       </c>
       <c r="AP63" s="70">
         <v>0</v>
@@ -10532,51 +10532,51 @@
       </c>
       <c r="D64" s="34"/>
       <c r="E64" s="33">
-        <v>379829.0499999997</v>
+        <v>386726.68</v>
       </c>
       <c r="F64" s="123">
-        <v>0.46604791411042906</v>
+        <v>0.47451126380368097</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="35">
         <v>815000</v>
       </c>
       <c r="I64" s="35">
-        <v>315483.87096774194</v>
+        <v>341774.19354838709</v>
       </c>
       <c r="J64" s="35">
-        <v>297602.0099999943</v>
+        <v>319711.78999999294</v>
       </c>
       <c r="K64" s="70">
-        <v>0.94331925460120891</v>
+        <v>0.93544742708822848</v>
       </c>
       <c r="L64" s="36"/>
       <c r="M64" s="35">
         <v>80685</v>
       </c>
       <c r="N64" s="35">
-        <v>31232.903225806447</v>
+        <v>33835.645161290318</v>
       </c>
       <c r="O64" s="37">
         <v>0</v>
       </c>
       <c r="P64" s="35">
-        <v>39398.119799999949</v>
+        <v>41943.402449999994</v>
       </c>
       <c r="Q64" s="115">
-        <v>1.2614299578608152</v>
+        <v>1.2396217731348407</v>
       </c>
       <c r="R64" s="36"/>
       <c r="S64" s="127">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="T64" s="127">
-        <v>0.13238526110761384</v>
+        <v>0.13119129091235865</v>
       </c>
       <c r="U64" s="36"/>
       <c r="V64" s="35"/>
       <c r="W64" s="38">
-        <v>1.3468423146720996</v>
+        <v>1.2203905429928348</v>
       </c>
       <c r="X64" s="69" t="s">
         <v>69</v>
@@ -10587,38 +10587,38 @@
         <v>26290.322580645163</v>
       </c>
       <c r="AB64" s="33">
-        <v>31436.209999999981</v>
+        <v>22109.779999999962</v>
       </c>
       <c r="AC64" s="36"/>
       <c r="AD64" s="35">
         <v>2602.7419354838707</v>
       </c>
       <c r="AE64" s="35">
-        <v>3491.3030499999982</v>
+        <v>2545.2826500000006</v>
       </c>
       <c r="AF64" s="115">
-        <v>1.3413942436636295</v>
+        <v>0.97792355642312723</v>
       </c>
       <c r="AG64" s="36"/>
       <c r="AH64" s="35">
-        <v>3283.1766499999958</v>
+        <v>3226.4155730769226</v>
       </c>
       <c r="AI64" s="35">
-        <v>101778.47614999987</v>
+        <v>100018.88276538459</v>
       </c>
       <c r="AJ64" s="115">
-        <v>1.2614299578608152</v>
+        <v>1.2396217731348405</v>
       </c>
       <c r="AK64" s="36"/>
       <c r="AL64" s="108">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="AM64" s="108">
-        <v>0.11105992261789828</v>
+        <v>0.11512021603109596</v>
       </c>
       <c r="AN64" s="36"/>
       <c r="AO64" s="38">
-        <v>-1.9200690859363063</v>
+        <v>-0.48167530387017465</v>
       </c>
       <c r="AP64" s="70">
         <v>0</v>
@@ -10634,51 +10634,51 @@
       </c>
       <c r="D65" s="34"/>
       <c r="E65" s="33">
-        <v>67474.41</v>
+        <v>59437.560000000005</v>
       </c>
       <c r="F65" s="123">
-        <v>8.5001776266061979E-2</v>
+        <v>7.4877248677248681E-2</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="35">
         <v>793800</v>
       </c>
       <c r="I65" s="35">
-        <v>305307.69230769231</v>
+        <v>335838.46153846156</v>
       </c>
       <c r="J65" s="35">
-        <v>279492.85999999975</v>
+        <v>289574.68999999965</v>
       </c>
       <c r="K65" s="70">
-        <v>0.9154465054169808</v>
+        <v>0.86224397489635474</v>
       </c>
       <c r="L65" s="36"/>
       <c r="M65" s="35">
         <v>75457.228812394649</v>
       </c>
       <c r="N65" s="35">
-        <v>29022.011081690249</v>
+        <v>31924.212189859274</v>
       </c>
       <c r="O65" s="37">
         <v>4996.79</v>
       </c>
       <c r="P65" s="35">
-        <v>-22086.980000000018</v>
+        <v>-22283.340000000018</v>
       </c>
       <c r="Q65" s="115">
-        <v>-0.76104236669989123</v>
+        <v>-0.69800751440558084</v>
       </c>
       <c r="R65" s="36"/>
       <c r="S65" s="127">
         <v>9.5058237354994524E-2</v>
       </c>
       <c r="T65" s="127">
-        <v>-7.902520300518602E-2</v>
+        <v>-7.6951960131598676E-2</v>
       </c>
       <c r="U65" s="36"/>
       <c r="V65" s="35"/>
       <c r="W65" s="38">
-        <v>-23.721886848916359</v>
+        <v>-23.436478512676768</v>
       </c>
       <c r="X65" s="69" t="s">
         <v>69</v>
@@ -10689,38 +10689,38 @@
         <v>30530.76923076923</v>
       </c>
       <c r="AB65" s="33">
-        <v>21503.75</v>
+        <v>10081.83</v>
       </c>
       <c r="AC65" s="36"/>
       <c r="AD65" s="35">
         <v>2902.2011081690248</v>
       </c>
       <c r="AE65" s="35">
-        <v>4332.4399999999996</v>
+        <v>-196.36000000000092</v>
       </c>
       <c r="AF65" s="115">
-        <v>1.4928117792406539</v>
+        <v>-6.7658991462477544E-2</v>
       </c>
       <c r="AG65" s="36"/>
       <c r="AH65" s="35">
-        <v>-2208.6980000000017</v>
+        <v>-2025.7581818181834</v>
       </c>
       <c r="AI65" s="35">
-        <v>-57426.148000000045</v>
+        <v>-52669.712727272767</v>
       </c>
       <c r="AJ65" s="115">
-        <v>-0.76104236669989123</v>
+        <v>-0.69800751440558084</v>
       </c>
       <c r="AK65" s="36"/>
       <c r="AL65" s="108">
         <v>9.5058237354994524E-2</v>
       </c>
       <c r="AM65" s="108">
-        <v>0.20147369644829388</v>
+        <v>-1.947662279566318E-2</v>
       </c>
       <c r="AN65" s="36"/>
       <c r="AO65" s="38">
-        <v>2.2598849037958457</v>
+        <v>-15.524264939996025</v>
       </c>
       <c r="AP65" s="70">
         <v>0</v>
@@ -10734,51 +10734,51 @@
       </c>
       <c r="D66" s="28"/>
       <c r="E66" s="27">
-        <v>932224.18999999983</v>
+        <v>910399.81</v>
       </c>
       <c r="F66" s="124">
-        <v>0.26720482400825496</v>
+        <v>0.26094926908965838</v>
       </c>
       <c r="G66" s="26"/>
       <c r="H66" s="29">
         <v>3488800</v>
       </c>
       <c r="I66" s="29">
-        <v>1345853.5980148884</v>
+        <v>1470019.6029776675</v>
       </c>
       <c r="J66" s="29">
-        <v>1288865.8599999887</v>
+        <v>1392963.9899999865</v>
       </c>
       <c r="K66" s="31">
-        <v>0.95765680747225734</v>
+        <v>0.94758191467542519</v>
       </c>
       <c r="L66" s="39"/>
       <c r="M66" s="29">
         <v>271342.22881239466</v>
       </c>
       <c r="N66" s="29">
-        <v>104741.26666481678</v>
+        <v>114230.32881516944</v>
       </c>
       <c r="O66" s="27">
         <v>4996.79</v>
       </c>
       <c r="P66" s="29">
-        <v>55441.934499999996</v>
+        <v>61565.805900000014</v>
       </c>
       <c r="Q66" s="31">
-        <v>0.52932274227139242</v>
+        <v>0.53896199493233232</v>
       </c>
       <c r="R66" s="39"/>
       <c r="S66" s="128">
         <v>7.7775231831115191E-2</v>
       </c>
       <c r="T66" s="128">
-        <v>4.3016062586994495E-2</v>
+        <v>4.419770097574497E-2</v>
       </c>
       <c r="U66" s="39"/>
       <c r="V66" s="29"/>
       <c r="W66" s="32">
-        <v>-8.9482838423551723</v>
+        <v>-8.7718300671947009</v>
       </c>
       <c r="X66" s="30" t="s">
         <v>69</v>
@@ -10789,34 +10789,34 @@
         <v>124166.00496277917</v>
       </c>
       <c r="AB66" s="27">
-        <v>109535.88999999996</v>
+        <v>104098.12999999999</v>
       </c>
       <c r="AC66" s="39"/>
       <c r="AD66" s="29">
         <v>9489.0621503526472</v>
       </c>
       <c r="AE66" s="29">
-        <v>10944.979249999997</v>
+        <v>6123.8713999999982</v>
       </c>
       <c r="AF66" s="31">
-        <v>1.1534310848194036</v>
+        <v>0.64536108025938199</v>
       </c>
       <c r="AG66" s="39"/>
       <c r="AH66" s="29">
-        <v>4396.205713333331</v>
+        <v>4552.4355013986024</v>
       </c>
       <c r="AI66" s="29">
-        <v>143001.04196333332</v>
+        <v>147085.86149790214</v>
       </c>
       <c r="AJ66" s="31">
-        <v>0.52701358940411702</v>
+        <v>0.54206771331415915</v>
       </c>
       <c r="AK66" s="39"/>
       <c r="AL66" s="80">
         <v>7.7775231831115191E-2</v>
       </c>
       <c r="AM66" s="80">
-        <v>9.9921397908941084E-2</v>
+        <v>5.882787135561416E-2</v>
       </c>
       <c r="AN66" s="39"/>
       <c r="AO66" s="32">
@@ -10881,51 +10881,51 @@
       </c>
       <c r="D68" s="34"/>
       <c r="E68" s="33">
-        <v>252328.21999999991</v>
+        <v>255631.55999999988</v>
       </c>
       <c r="F68" s="123">
-        <v>4.0698099999999986</v>
+        <v>4.1230896774193528</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="35">
         <v>62000</v>
       </c>
       <c r="I68" s="35">
-        <v>23846.153846153848</v>
+        <v>26230.769230769234</v>
       </c>
       <c r="J68" s="35">
-        <v>24518.31000000034</v>
+        <v>27185.480000000458</v>
       </c>
       <c r="K68" s="70">
-        <v>1.0281871935484013</v>
+        <v>1.0363965982404866</v>
       </c>
       <c r="L68" s="36"/>
       <c r="M68" s="35">
         <v>12524</v>
       </c>
       <c r="N68" s="35">
-        <v>4816.9230769230771</v>
+        <v>5298.6153846153848</v>
       </c>
       <c r="O68" s="37">
         <v>0</v>
       </c>
       <c r="P68" s="35">
-        <v>5312.37</v>
+        <v>5790.4999999999945</v>
       </c>
       <c r="Q68" s="115">
-        <v>1.1028554774832322</v>
+        <v>1.0928326703638096</v>
       </c>
       <c r="R68" s="36"/>
       <c r="S68" s="127">
         <v>0.20200000000000001</v>
       </c>
       <c r="T68" s="127">
-        <v>0.21666950128291576</v>
+        <v>0.21299973368135847</v>
       </c>
       <c r="U68" s="36"/>
       <c r="V68" s="35"/>
       <c r="W68" s="38">
-        <v>9.7797523565053126</v>
+        <v>9.4040642284056641</v>
       </c>
       <c r="X68" s="69" t="s">
         <v>69</v>
@@ -10936,38 +10936,38 @@
         <v>2384.6153846153848</v>
       </c>
       <c r="AB68" s="33">
-        <v>2408.7399999999989</v>
+        <v>2667.17</v>
       </c>
       <c r="AC68" s="36"/>
       <c r="AD68" s="35">
         <v>481.69230769230768</v>
       </c>
       <c r="AE68" s="35">
-        <v>538.04000000000008</v>
+        <v>478.13000000000039</v>
       </c>
       <c r="AF68" s="115">
-        <v>1.1169786010859153</v>
+        <v>0.9926045991695952</v>
       </c>
       <c r="AG68" s="36"/>
       <c r="AH68" s="35">
-        <v>531.23699999999997</v>
+        <v>526.40909090909042</v>
       </c>
       <c r="AI68" s="35">
-        <v>13812.161999999998</v>
+        <v>13686.636363636351</v>
       </c>
       <c r="AJ68" s="115">
-        <v>1.102855477483232</v>
+        <v>1.0928326703638096</v>
       </c>
       <c r="AK68" s="36"/>
       <c r="AL68" s="108">
         <v>0.20200000000000001</v>
       </c>
       <c r="AM68" s="108">
-        <v>0.22336989463370904</v>
+        <v>0.17926491374753029</v>
       </c>
       <c r="AN68" s="36"/>
       <c r="AO68" s="38">
-        <v>10.171708029924316</v>
+        <v>5.9505018427772285</v>
       </c>
       <c r="AP68" s="70">
         <v>0</v>
@@ -10983,51 +10983,51 @@
       </c>
       <c r="D69" s="34"/>
       <c r="E69" s="33">
-        <v>304930.2399999997</v>
+        <v>303050.46999999974</v>
       </c>
       <c r="F69" s="123">
-        <v>2.1029671724137908</v>
+        <v>2.0900032413793084</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="35">
         <v>145000</v>
       </c>
       <c r="I69" s="35">
-        <v>56129.032258064515</v>
+        <v>60806.45161290322</v>
       </c>
       <c r="J69" s="35">
-        <v>54308.080000000082</v>
+        <v>58295.290000000059</v>
       </c>
       <c r="K69" s="70">
-        <v>0.96755774712643827</v>
+        <v>0.95870238196286583</v>
       </c>
       <c r="L69" s="36"/>
       <c r="M69" s="35">
         <v>35179.978006339457</v>
       </c>
       <c r="N69" s="35">
-        <v>13618.056002453985</v>
+        <v>14752.894002658482</v>
       </c>
       <c r="O69" s="37">
         <v>0</v>
       </c>
       <c r="P69" s="35">
-        <v>11731.299999999956</v>
+        <v>12484.05999999993</v>
       </c>
       <c r="Q69" s="115">
-        <v>0.86145188401971373</v>
+        <v>0.84621091954909278</v>
       </c>
       <c r="R69" s="36"/>
       <c r="S69" s="127">
         <v>0.24262053797475489</v>
       </c>
       <c r="T69" s="127">
-        <v>0.21601389701127233</v>
+        <v>0.2141521210375644</v>
       </c>
       <c r="U69" s="36"/>
       <c r="V69" s="35"/>
       <c r="W69" s="38">
-        <v>9.6359510408030857</v>
+        <v>9.4586543784243524</v>
       </c>
       <c r="X69" s="69" t="s">
         <v>69</v>
@@ -11038,38 +11038,38 @@
         <v>4677.4193548387093</v>
       </c>
       <c r="AB69" s="33">
-        <v>3172.7299999999914</v>
+        <v>3987.2099999999891</v>
       </c>
       <c r="AC69" s="36"/>
       <c r="AD69" s="35">
         <v>1134.8380002044987</v>
       </c>
       <c r="AE69" s="35">
-        <v>654.37999999999931</v>
+        <v>752.75999999999931</v>
       </c>
       <c r="AF69" s="115">
-        <v>0.57662855833350624</v>
+        <v>0.66331934590166297</v>
       </c>
       <c r="AG69" s="36"/>
       <c r="AH69" s="35">
-        <v>977.6083333333296</v>
+        <v>960.31230769230228</v>
       </c>
       <c r="AI69" s="35">
-        <v>30305.858333333217</v>
+        <v>29769.681538461369</v>
       </c>
       <c r="AJ69" s="115">
-        <v>0.86145188401971373</v>
+        <v>0.84621091954909267</v>
       </c>
       <c r="AK69" s="36"/>
       <c r="AL69" s="108">
         <v>0.24262053797475489</v>
       </c>
       <c r="AM69" s="108">
-        <v>0.20625139863776656</v>
+        <v>0.18879366775263939</v>
       </c>
       <c r="AN69" s="36"/>
       <c r="AO69" s="38">
-        <v>9.2289605481713135</v>
+        <v>7.0437724624485369</v>
       </c>
       <c r="AP69" s="70">
         <v>0</v>
@@ -11085,51 +11085,51 @@
       </c>
       <c r="D70" s="34"/>
       <c r="E70" s="33">
-        <v>494570.44</v>
+        <v>493303.64</v>
       </c>
       <c r="F70" s="123">
-        <v>2.6030023157894737</v>
+        <v>2.5963349473684212</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="35">
         <v>190000</v>
       </c>
       <c r="I70" s="35">
-        <v>73548.387096774197</v>
+        <v>79677.419354838712</v>
       </c>
       <c r="J70" s="35">
-        <v>82329.990000001359</v>
+        <v>87893.680000001928</v>
       </c>
       <c r="K70" s="70">
-        <v>1.1193989868421237</v>
+        <v>1.1031190607287691</v>
       </c>
       <c r="L70" s="36"/>
       <c r="M70" s="35">
         <v>45410</v>
       </c>
       <c r="N70" s="35">
-        <v>17578.06451612903</v>
+        <v>19042.903225806451</v>
       </c>
       <c r="O70" s="37">
-        <v>930.33</v>
+        <v>1214.25</v>
       </c>
       <c r="P70" s="35">
-        <v>18353.900000000023</v>
+        <v>19673.640000000021</v>
       </c>
       <c r="Q70" s="115">
-        <v>1.0441365705057637</v>
+        <v>1.0331218809818248</v>
       </c>
       <c r="R70" s="36"/>
       <c r="S70" s="127">
         <v>0.23899999999999999</v>
       </c>
       <c r="T70" s="127">
-        <v>0.2229309149679202</v>
+        <v>0.22383452371091517</v>
       </c>
       <c r="U70" s="36"/>
       <c r="V70" s="35"/>
       <c r="W70" s="38">
-        <v>9.2354559984775175</v>
+        <v>9.069605459688761</v>
       </c>
       <c r="X70" s="69" t="s">
         <v>69</v>
@@ -11140,38 +11140,38 @@
         <v>6129.0322580645161</v>
       </c>
       <c r="AB70" s="33">
-        <v>5557.6499999999814</v>
+        <v>5563.689999999975</v>
       </c>
       <c r="AC70" s="36"/>
       <c r="AD70" s="35">
         <v>1464.8387096774193</v>
       </c>
       <c r="AE70" s="35">
-        <v>1088.6000000000004</v>
+        <v>1035.8199999999997</v>
       </c>
       <c r="AF70" s="115">
-        <v>0.74315349042061252</v>
+        <v>0.7071222197753797</v>
       </c>
       <c r="AG70" s="36"/>
       <c r="AH70" s="35">
-        <v>1529.4916666666686</v>
+        <v>1513.3569230769247</v>
       </c>
       <c r="AI70" s="35">
-        <v>47414.241666666727</v>
+        <v>46914.064615384661</v>
       </c>
       <c r="AJ70" s="115">
-        <v>1.0441365705057637</v>
+        <v>1.0331218809818248</v>
       </c>
       <c r="AK70" s="36"/>
       <c r="AL70" s="108">
         <v>0.23899999999999999</v>
       </c>
       <c r="AM70" s="108">
-        <v>0.19587415544339856</v>
+        <v>0.18617500256125061</v>
       </c>
       <c r="AN70" s="36"/>
       <c r="AO70" s="38">
-        <v>7.5060502190671059</v>
+        <v>6.6153937404847776</v>
       </c>
       <c r="AP70" s="70">
         <v>0</v>
@@ -11187,51 +11187,51 @@
       </c>
       <c r="D71" s="34"/>
       <c r="E71" s="33">
-        <v>22183.840000000015</v>
+        <v>21748.780000000013</v>
       </c>
       <c r="F71" s="123">
-        <v>5.5459600000000036</v>
+        <v>5.4371950000000036</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="35">
         <v>4000</v>
       </c>
       <c r="I71" s="35">
-        <v>1538.4615384615383</v>
+        <v>1692.3076923076922</v>
       </c>
       <c r="J71" s="35">
-        <v>831.93000000000052</v>
+        <v>884.09000000000049</v>
       </c>
       <c r="K71" s="70">
-        <v>0.54075450000000036</v>
+        <v>0.52241681818181851</v>
       </c>
       <c r="L71" s="36"/>
       <c r="M71" s="35">
         <v>960</v>
       </c>
       <c r="N71" s="35">
-        <v>369.23076923076917</v>
+        <v>406.15384615384613</v>
       </c>
       <c r="O71" s="37">
         <v>0</v>
       </c>
       <c r="P71" s="35">
-        <v>183.84</v>
+        <v>196.66</v>
       </c>
       <c r="Q71" s="115">
-        <v>0.49790000000000006</v>
+        <v>0.48420075757575759</v>
       </c>
       <c r="R71" s="36"/>
       <c r="S71" s="127">
         <v>0.24</v>
       </c>
       <c r="T71" s="127">
-        <v>0.22098013053982893</v>
+        <v>0.22244341639425838</v>
       </c>
       <c r="U71" s="36"/>
       <c r="V71" s="35"/>
       <c r="W71" s="38">
-        <v>9.8818410202782569</v>
+        <v>9.9865398319176464</v>
       </c>
       <c r="X71" s="69" t="s">
         <v>69</v>
@@ -11242,38 +11242,38 @@
         <v>153.84615384615384</v>
       </c>
       <c r="AB71" s="33">
-        <v>82.51</v>
+        <v>52.160000000000011</v>
       </c>
       <c r="AC71" s="36"/>
       <c r="AD71" s="35">
         <v>36.92307692307692</v>
       </c>
       <c r="AE71" s="35">
-        <v>12.06</v>
+        <v>12.820000000000004</v>
       </c>
       <c r="AF71" s="115">
-        <v>0.32662500000000005</v>
+        <v>0.34720833333333345</v>
       </c>
       <c r="AG71" s="36"/>
       <c r="AH71" s="35">
-        <v>18.384</v>
+        <v>17.878181818181819</v>
       </c>
       <c r="AI71" s="35">
-        <v>477.98400000000004</v>
+        <v>464.83272727272731</v>
       </c>
       <c r="AJ71" s="115">
-        <v>0.49790000000000006</v>
+        <v>0.48420075757575759</v>
       </c>
       <c r="AK71" s="36"/>
       <c r="AL71" s="108">
         <v>0.24</v>
       </c>
       <c r="AM71" s="108">
-        <v>0.14616410132105198</v>
+        <v>0.24578220858895708</v>
       </c>
       <c r="AN71" s="36"/>
       <c r="AO71" s="38">
-        <v>2.3754696400436406</v>
+        <v>11.656441717791433</v>
       </c>
       <c r="AP71" s="70">
         <v>0</v>
@@ -11287,51 +11287,51 @@
       </c>
       <c r="D72" s="28"/>
       <c r="E72" s="27">
-        <v>1074012.7399999998</v>
+        <v>1073734.4499999995</v>
       </c>
       <c r="F72" s="124">
-        <v>2.6783360099750619</v>
+        <v>2.6776420199501234</v>
       </c>
       <c r="G72" s="26"/>
       <c r="H72" s="29">
         <v>401000</v>
       </c>
       <c r="I72" s="29">
-        <v>155062.03473945407</v>
+        <v>168406.94789081888</v>
       </c>
       <c r="J72" s="29">
-        <v>161988.31000000177</v>
+        <v>174258.54000000245</v>
       </c>
       <c r="K72" s="31">
-        <v>1.0446677697231672</v>
+        <v>1.0347467380798163</v>
       </c>
       <c r="L72" s="39"/>
       <c r="M72" s="29">
         <v>94073.978006339457</v>
       </c>
       <c r="N72" s="29">
-        <v>36382.274364736862</v>
+        <v>39500.566459234164</v>
       </c>
       <c r="O72" s="27">
-        <v>930.33</v>
+        <v>1214.25</v>
       </c>
       <c r="P72" s="29">
-        <v>35581.409999999974</v>
+        <v>38144.85999999995</v>
       </c>
       <c r="Q72" s="31">
-        <v>0.97798751236087877</v>
+        <v>0.96567880967901187</v>
       </c>
       <c r="R72" s="39"/>
       <c r="S72" s="128">
         <v>0.23459844889361461</v>
       </c>
       <c r="T72" s="128">
-        <v>0.21965418368769687</v>
+        <v>0.21889808097783564</v>
       </c>
       <c r="U72" s="39"/>
       <c r="V72" s="29"/>
       <c r="W72" s="32">
-        <v>9.4554292220231133</v>
+        <v>9.2565850718145093</v>
       </c>
       <c r="X72" s="30" t="s">
         <v>69</v>
@@ -11342,34 +11342,34 @@
         <v>13344.913151364764</v>
       </c>
       <c r="AB72" s="27">
-        <v>11221.629999999972</v>
+        <v>12270.229999999963</v>
       </c>
       <c r="AC72" s="39"/>
       <c r="AD72" s="29">
         <v>3118.292094497303</v>
       </c>
       <c r="AE72" s="29">
-        <v>2293.0799999999995</v>
+        <v>2279.5299999999993</v>
       </c>
       <c r="AF72" s="31">
-        <v>0.73536408088468852</v>
+        <v>0.73101875351015833</v>
       </c>
       <c r="AG72" s="39"/>
       <c r="AH72" s="29">
-        <v>3056.7209999999982</v>
+        <v>3017.9565034964994</v>
       </c>
       <c r="AI72" s="29">
-        <v>92010.245999999941</v>
+        <v>90835.21524475512</v>
       </c>
       <c r="AJ72" s="31">
-        <v>0.9780626688689571</v>
+        <v>0.96557217170760989</v>
       </c>
       <c r="AK72" s="39"/>
       <c r="AL72" s="80">
         <v>0.23459844889361461</v>
       </c>
       <c r="AM72" s="80">
-        <v>0.20434464511840128</v>
+        <v>0.18577728371839861</v>
       </c>
       <c r="AN72" s="39"/>
       <c r="AO72" s="32">
@@ -11434,51 +11434,51 @@
       </c>
       <c r="D74" s="34"/>
       <c r="E74" s="33">
-        <v>37210.960000000021</v>
+        <v>37577.470000000023</v>
       </c>
       <c r="F74" s="123">
-        <v>0.54722000000000026</v>
+        <v>0.55260985294117682</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="35">
         <v>68000</v>
       </c>
       <c r="I74" s="35">
-        <v>26153.846153846152</v>
+        <v>28769.230769230766</v>
       </c>
       <c r="J74" s="35">
-        <v>23757.310000000194</v>
+        <v>26722.290000000292</v>
       </c>
       <c r="K74" s="70">
-        <v>0.90836773529412507</v>
+        <v>0.92884965240642736</v>
       </c>
       <c r="L74" s="36"/>
       <c r="M74" s="35">
         <v>11900</v>
       </c>
       <c r="N74" s="35">
-        <v>4576.9230769230771</v>
+        <v>5034.6153846153848</v>
       </c>
       <c r="O74" s="37">
-        <v>21.76</v>
+        <v>342.96</v>
       </c>
       <c r="P74" s="35">
-        <v>3057.4299999999971</v>
+        <v>3754.7299999999964</v>
       </c>
       <c r="Q74" s="115">
-        <v>0.66800991596638593</v>
+        <v>0.74578288770053403</v>
       </c>
       <c r="R74" s="36"/>
       <c r="S74" s="127">
         <v>0.17499999999999999</v>
       </c>
       <c r="T74" s="127">
-        <v>0.12869428399090521</v>
+        <v>0.14050929018433508</v>
       </c>
       <c r="U74" s="36"/>
       <c r="V74" s="35"/>
       <c r="W74" s="38">
-        <v>1.8892711338118828</v>
+        <v>1.9052633587926076</v>
       </c>
       <c r="X74" s="69" t="s">
         <v>69</v>
@@ -11489,38 +11489,38 @@
         <v>2615.3846153846152</v>
       </c>
       <c r="AB74" s="33">
-        <v>2384.5999999999995</v>
+        <v>2964.979999999995</v>
       </c>
       <c r="AC74" s="36"/>
       <c r="AD74" s="35">
         <v>457.69230769230768</v>
       </c>
       <c r="AE74" s="35">
-        <v>375.55999999999995</v>
+        <v>376.09999999999985</v>
       </c>
       <c r="AF74" s="115">
-        <v>0.82055126050420157</v>
+        <v>0.82173109243697451</v>
       </c>
       <c r="AG74" s="36"/>
       <c r="AH74" s="35">
-        <v>305.74299999999971</v>
+        <v>341.3390909090906</v>
       </c>
       <c r="AI74" s="35">
-        <v>7949.317999999992</v>
+        <v>8874.8163636363552</v>
       </c>
       <c r="AJ74" s="115">
-        <v>0.66800991596638593</v>
+        <v>0.74578288770053403</v>
       </c>
       <c r="AK74" s="36"/>
       <c r="AL74" s="108">
         <v>0.17499999999999999</v>
       </c>
       <c r="AM74" s="108">
-        <v>0.15749391931560849</v>
+        <v>0.12684739863338049</v>
       </c>
       <c r="AN74" s="36"/>
       <c r="AO74" s="38">
-        <v>5.0280969554641963</v>
+        <v>2.0334032607301067</v>
       </c>
       <c r="AP74" s="70">
         <v>0</v>
@@ -11536,51 +11536,51 @@
       </c>
       <c r="D75" s="34"/>
       <c r="E75" s="33">
-        <v>94581.710000000079</v>
+        <v>92752.010000000038</v>
       </c>
       <c r="F75" s="123">
-        <v>0.61818111111111163</v>
+        <v>0.6062222875816996</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="35">
         <v>153000</v>
       </c>
       <c r="I75" s="35">
-        <v>59225.806451612894</v>
+        <v>64161.290322580637</v>
       </c>
       <c r="J75" s="35">
-        <v>65281.25000000016</v>
+        <v>70550.860000000583</v>
       </c>
       <c r="K75" s="70">
-        <v>1.1022433278867132</v>
+        <v>1.0995860532931214</v>
       </c>
       <c r="L75" s="36"/>
       <c r="M75" s="35">
         <v>30083.290842020251</v>
       </c>
       <c r="N75" s="35">
-        <v>11645.144842072355</v>
+        <v>12615.573578911719</v>
       </c>
       <c r="O75" s="37">
-        <v>68.22</v>
+        <v>936.24</v>
       </c>
       <c r="P75" s="35">
-        <v>12468.320000000043</v>
+        <v>14256.390000000052</v>
       </c>
       <c r="Q75" s="115">
-        <v>1.070688271300299</v>
+        <v>1.1300627681194879</v>
       </c>
       <c r="R75" s="36"/>
       <c r="S75" s="127">
         <v>0.19662281596091669</v>
       </c>
       <c r="T75" s="127">
-        <v>0.1909938918142654</v>
+        <v>0.20207251903095064</v>
       </c>
       <c r="U75" s="36"/>
       <c r="V75" s="35"/>
       <c r="W75" s="38">
-        <v>8.5044633796076816</v>
+        <v>8.3781686006386646</v>
       </c>
       <c r="X75" s="69" t="s">
         <v>69</v>
@@ -11591,38 +11591,38 @@
         <v>4935.4838709677415</v>
       </c>
       <c r="AB75" s="33">
-        <v>4771.4299999999876</v>
+        <v>5269.6099999999824</v>
       </c>
       <c r="AC75" s="36"/>
       <c r="AD75" s="35">
         <v>970.42873683936295</v>
       </c>
       <c r="AE75" s="35">
-        <v>768.22999999999979</v>
+        <v>920.05000000000018</v>
       </c>
       <c r="AF75" s="115">
-        <v>0.79163978851459593</v>
+        <v>0.9480861036705861</v>
       </c>
       <c r="AG75" s="36"/>
       <c r="AH75" s="35">
-        <v>1039.0266666666703</v>
+        <v>1096.6453846153886</v>
       </c>
       <c r="AI75" s="35">
-        <v>32209.826666666777</v>
+        <v>33996.006923077046</v>
       </c>
       <c r="AJ75" s="115">
-        <v>1.070688271300299</v>
+        <v>1.1300627681194879</v>
       </c>
       <c r="AK75" s="36"/>
       <c r="AL75" s="108">
         <v>0.19662281596091669</v>
       </c>
       <c r="AM75" s="108">
-        <v>0.16100623921968923</v>
+        <v>0.17459546342139234</v>
       </c>
       <c r="AN75" s="36"/>
       <c r="AO75" s="38">
-        <v>5.4430223224481162</v>
+        <v>6.8135972111785144</v>
       </c>
       <c r="AP75" s="70">
         <v>0</v>
@@ -11638,51 +11638,51 @@
       </c>
       <c r="D76" s="34"/>
       <c r="E76" s="33">
-        <v>130655.73000000001</v>
+        <v>129643.75999999998</v>
       </c>
       <c r="F76" s="123">
-        <v>0.57305144736842106</v>
+        <v>0.56861298245614023</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="35">
         <v>228000</v>
       </c>
       <c r="I76" s="35">
-        <v>88258.06451612903</v>
+        <v>95612.903225806454</v>
       </c>
       <c r="J76" s="35">
-        <v>97980.540000002817</v>
+        <v>104584.09000000336</v>
       </c>
       <c r="K76" s="70">
-        <v>1.1101596271930143</v>
+        <v>1.093828201754421</v>
       </c>
       <c r="L76" s="36"/>
       <c r="M76" s="35">
         <v>39900</v>
       </c>
       <c r="N76" s="35">
-        <v>15445.16129032258</v>
+        <v>16732.258064516129</v>
       </c>
       <c r="O76" s="37">
-        <v>169.08</v>
+        <v>1442.6100000000001</v>
       </c>
       <c r="P76" s="35">
-        <v>12909.510000000062</v>
+        <v>15159.480000000058</v>
       </c>
       <c r="Q76" s="115">
-        <v>0.83582875939850032</v>
+        <v>0.90600323886640022</v>
       </c>
       <c r="R76" s="36"/>
       <c r="S76" s="127">
         <v>0.17499999999999999</v>
       </c>
       <c r="T76" s="127">
-        <v>0.13175585682626051</v>
+        <v>0.144950154464217</v>
       </c>
       <c r="U76" s="36"/>
       <c r="V76" s="35"/>
       <c r="W76" s="38">
-        <v>2.5940253033944609</v>
+        <v>2.7092839838287666</v>
       </c>
       <c r="X76" s="69" t="s">
         <v>69</v>
@@ -11693,38 +11693,38 @@
         <v>7354.8387096774195</v>
       </c>
       <c r="AB76" s="33">
-        <v>8198.819999999967</v>
+        <v>6603.5499999999711</v>
       </c>
       <c r="AC76" s="36"/>
       <c r="AD76" s="35">
         <v>1287.0967741935483</v>
       </c>
       <c r="AE76" s="35">
-        <v>1299.9299999999998</v>
+        <v>976.43999999999949</v>
       </c>
       <c r="AF76" s="115">
-        <v>1.0099706766917294</v>
+        <v>0.75863759398496211</v>
       </c>
       <c r="AG76" s="36"/>
       <c r="AH76" s="35">
-        <v>1075.7925000000052</v>
+        <v>1166.1138461538505</v>
       </c>
       <c r="AI76" s="35">
-        <v>33349.567500000165</v>
+        <v>36149.529230769367</v>
       </c>
       <c r="AJ76" s="115">
-        <v>0.83582875939850032</v>
+        <v>0.90600323886640022</v>
       </c>
       <c r="AK76" s="36"/>
       <c r="AL76" s="108">
         <v>0.17499999999999999</v>
       </c>
       <c r="AM76" s="108">
-        <v>0.15855086463661905</v>
+        <v>0.14786592060331241</v>
       </c>
       <c r="AN76" s="36"/>
       <c r="AO76" s="38">
-        <v>5.4345625346082134</v>
+        <v>4.4194410582182249</v>
       </c>
       <c r="AP76" s="70">
         <v>0</v>
@@ -11740,51 +11740,51 @@
       </c>
       <c r="D77" s="34"/>
       <c r="E77" s="33">
-        <v>1892.2099999999998</v>
+        <v>2677.7999999999993</v>
       </c>
       <c r="F77" s="123">
-        <v>0.47305249999999993</v>
+        <v>0.66944999999999977</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="35">
         <v>4000</v>
       </c>
       <c r="I77" s="35">
-        <v>1538.4615384615383</v>
+        <v>1692.3076923076922</v>
       </c>
       <c r="J77" s="35">
-        <v>3320.9899999999934</v>
+        <v>3539.5499999999911</v>
       </c>
       <c r="K77" s="70">
-        <v>2.1586434999999957</v>
+        <v>2.0915522727272675</v>
       </c>
       <c r="L77" s="36"/>
       <c r="M77" s="35">
         <v>630.99967958987622</v>
       </c>
       <c r="N77" s="35">
-        <v>242.69218445764469</v>
+        <v>266.96140290340918</v>
       </c>
       <c r="O77" s="37">
         <v>0</v>
       </c>
       <c r="P77" s="35">
-        <v>366.90000000000015</v>
+        <v>419.46000000000015</v>
       </c>
       <c r="Q77" s="115">
-        <v>1.5117915759006757</v>
+        <v>1.5712383716823939</v>
       </c>
       <c r="R77" s="36"/>
       <c r="S77" s="127">
         <v>0.15774991989746906</v>
       </c>
       <c r="T77" s="127">
-        <v>0.11047910412256612</v>
+        <v>0.11850658982074026</v>
       </c>
       <c r="U77" s="36"/>
       <c r="V77" s="35"/>
       <c r="W77" s="38">
-        <v>-0.51942342494276872</v>
+        <v>0.30314588012572335</v>
       </c>
       <c r="X77" s="69" t="s">
         <v>69</v>
@@ -11795,38 +11795,38 @@
         <v>153.84615384615384</v>
       </c>
       <c r="AB77" s="33">
-        <v>95.54</v>
+        <v>218.56</v>
       </c>
       <c r="AC77" s="36"/>
       <c r="AD77" s="35">
         <v>24.269218445764469</v>
       </c>
       <c r="AE77" s="35">
-        <v>28.1</v>
+        <v>52.56</v>
       </c>
       <c r="AF77" s="115">
-        <v>1.1578452788991271</v>
+        <v>2.1657063294995771</v>
       </c>
       <c r="AG77" s="36"/>
       <c r="AH77" s="35">
-        <v>36.690000000000012</v>
+        <v>38.132727272727287</v>
       </c>
       <c r="AI77" s="35">
-        <v>953.94000000000028</v>
+        <v>991.45090909090948</v>
       </c>
       <c r="AJ77" s="115">
-        <v>1.5117915759006755</v>
+        <v>1.5712383716823941</v>
       </c>
       <c r="AK77" s="36"/>
       <c r="AL77" s="108">
         <v>0.15774991989746906</v>
       </c>
       <c r="AM77" s="108">
-        <v>0.29411764705882354</v>
+        <v>0.24048316251830162</v>
       </c>
       <c r="AN77" s="36"/>
       <c r="AO77" s="38">
-        <v>18.065731630730589</v>
+        <v>12.801976573938529</v>
       </c>
       <c r="AP77" s="70">
         <v>0</v>
@@ -11840,51 +11840,51 @@
       </c>
       <c r="D78" s="28"/>
       <c r="E78" s="27">
-        <v>264340.61000000016</v>
+        <v>262651.04000000004</v>
       </c>
       <c r="F78" s="124">
-        <v>0.58353335540838891</v>
+        <v>0.57980362030905086</v>
       </c>
       <c r="G78" s="26"/>
       <c r="H78" s="29">
         <v>453000</v>
       </c>
       <c r="I78" s="29">
-        <v>175176.1786600496</v>
+        <v>190235.73200992553</v>
       </c>
       <c r="J78" s="29">
-        <v>190340.09000000317</v>
+        <v>205396.79000000423</v>
       </c>
       <c r="K78" s="31">
-        <v>1.0865637751430859</v>
+        <v>1.0796961634383579</v>
       </c>
       <c r="L78" s="39"/>
       <c r="M78" s="29">
         <v>82514.290521610121</v>
       </c>
       <c r="N78" s="29">
-        <v>31909.921393775658</v>
+        <v>34649.408430946642</v>
       </c>
       <c r="O78" s="27">
-        <v>259.06</v>
+        <v>2721.8100000000004</v>
       </c>
       <c r="P78" s="29">
-        <v>28802.160000000105</v>
+        <v>33590.060000000107</v>
       </c>
       <c r="Q78" s="31">
-        <v>0.90260830305956974</v>
+        <v>0.96942665174045528</v>
       </c>
       <c r="R78" s="39"/>
       <c r="S78" s="128">
         <v>0.18215075170333361</v>
       </c>
       <c r="T78" s="128">
-        <v>0.1513194619168228</v>
+        <v>0.16353741458179272</v>
       </c>
       <c r="U78" s="39"/>
       <c r="V78" s="29"/>
       <c r="W78" s="32">
-        <v>4.4788515125756305</v>
+        <v>4.5103966814690004</v>
       </c>
       <c r="X78" s="30" t="s">
         <v>69</v>
@@ -11895,34 +11895,34 @@
         <v>15059.553349875931</v>
       </c>
       <c r="AB78" s="27">
-        <v>15450.389999999956</v>
+        <v>15056.699999999948</v>
       </c>
       <c r="AC78" s="39"/>
       <c r="AD78" s="29">
         <v>2739.4870371709835</v>
       </c>
       <c r="AE78" s="29">
-        <v>2471.8199999999993</v>
+        <v>2325.1499999999996</v>
       </c>
       <c r="AF78" s="31">
-        <v>0.90229300831173165</v>
+        <v>0.84875378800884493</v>
       </c>
       <c r="AG78" s="39"/>
       <c r="AH78" s="29">
-        <v>2457.2521666666753</v>
+        <v>2642.2310489510569</v>
       </c>
       <c r="AI78" s="29">
-        <v>74462.652166666929</v>
+        <v>80011.803426573679</v>
       </c>
       <c r="AJ78" s="31">
-        <v>0.90242128600942761</v>
+        <v>0.9696720764461878</v>
       </c>
       <c r="AK78" s="39"/>
       <c r="AL78" s="80">
         <v>0.18215075170333361</v>
       </c>
       <c r="AM78" s="80">
-        <v>0.15998431107564315</v>
+        <v>0.15442626870429826</v>
       </c>
       <c r="AN78" s="39"/>
       <c r="AO78" s="32">
@@ -11987,51 +11987,51 @@
       </c>
       <c r="D80" s="34"/>
       <c r="E80" s="33">
-        <v>656874.28000000014</v>
+        <v>644120.87</v>
       </c>
       <c r="F80" s="123">
-        <v>2.8559751304347833</v>
+        <v>2.8005255217391305</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="35">
         <v>230000</v>
       </c>
       <c r="I80" s="130">
-        <v>88461.538461538454</v>
+        <v>97307.692307692298</v>
       </c>
       <c r="J80" s="35">
-        <v>101509.4100000006</v>
+        <v>109880.11000000092</v>
       </c>
       <c r="K80" s="70">
-        <v>1.1474976782608763</v>
+        <v>1.1292027114624601</v>
       </c>
       <c r="L80" s="36"/>
       <c r="M80" s="35">
         <v>25300</v>
       </c>
       <c r="N80" s="35">
-        <v>9730.7692307692305</v>
+        <v>10703.846153846154</v>
       </c>
       <c r="O80" s="37">
         <v>0</v>
       </c>
       <c r="P80" s="130">
-        <v>6274.7500000000018</v>
+        <v>7023.96</v>
       </c>
       <c r="Q80" s="70">
-        <v>0.6448359683794469</v>
+        <v>0.65620898311174991</v>
       </c>
       <c r="R80" s="36"/>
       <c r="S80" s="127">
         <v>0.11</v>
       </c>
       <c r="T80" s="127">
-        <v>6.1814466264752843E-2</v>
+        <v>6.3923853006699227E-2</v>
       </c>
       <c r="U80" s="36"/>
       <c r="V80" s="35"/>
       <c r="W80" s="38">
-        <v>-2.9002335842554166</v>
+        <v>-2.7460838908872964</v>
       </c>
       <c r="X80" s="69" t="s">
         <v>69</v>
@@ -12042,38 +12042,38 @@
         <v>8846.1538461538457</v>
       </c>
       <c r="AB80" s="33">
-        <v>35711.14</v>
+        <v>8370.6999999999662</v>
       </c>
       <c r="AC80" s="36"/>
       <c r="AD80" s="35">
         <v>973.07692307692309</v>
       </c>
       <c r="AE80" s="35">
-        <v>-1200.9600000000005</v>
+        <v>749.20999999999924</v>
       </c>
       <c r="AF80" s="115">
-        <v>-1.2341881422924905</v>
+        <v>0.76993913043478179</v>
       </c>
       <c r="AG80" s="36"/>
       <c r="AH80" s="35">
-        <v>627.47500000000014</v>
+        <v>638.54181818181814</v>
       </c>
       <c r="AI80" s="35">
-        <v>16314.350000000004</v>
+        <v>16602.087272727273</v>
       </c>
       <c r="AJ80" s="115">
-        <v>0.64483596837944679</v>
+        <v>0.65620898311174991</v>
       </c>
       <c r="AK80" s="36"/>
       <c r="AL80" s="108">
         <v>0.11</v>
       </c>
       <c r="AM80" s="108">
-        <v>-3.3629842116493634E-2</v>
+        <v>8.9503864670816335E-2</v>
       </c>
       <c r="AN80" s="36"/>
       <c r="AO80" s="38">
-        <v>-11.690413691637955</v>
+        <v>-0.87674865901337351</v>
       </c>
       <c r="AP80" s="70">
         <v>0</v>
@@ -12089,51 +12089,51 @@
       </c>
       <c r="D81" s="34"/>
       <c r="E81" s="33">
-        <v>444072.19000000024</v>
+        <v>482438.77000000031</v>
       </c>
       <c r="F81" s="123">
-        <v>1.306094676470589</v>
+        <v>1.4189375588235302</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="35">
         <v>340000</v>
       </c>
       <c r="I81" s="130">
-        <v>131612.90322580645</v>
+        <v>142580.64516129033</v>
       </c>
       <c r="J81" s="35">
-        <v>144263.38000000117</v>
+        <v>152490.76999999935</v>
       </c>
       <c r="K81" s="70">
-        <v>1.0961188186274597</v>
+        <v>1.069505400452484</v>
       </c>
       <c r="L81" s="36"/>
       <c r="M81" s="35">
         <v>50660</v>
       </c>
       <c r="N81" s="35">
-        <v>19610.322580645163</v>
+        <v>21244.516129032258</v>
       </c>
       <c r="O81" s="37">
         <v>0</v>
       </c>
       <c r="P81" s="130">
-        <v>15985.940000000168</v>
+        <v>17317.740000000238</v>
       </c>
       <c r="Q81" s="70">
-        <v>0.81517985919200742</v>
+        <v>0.8151628351908764</v>
       </c>
       <c r="R81" s="36"/>
       <c r="S81" s="127">
         <v>0.14899999999999999</v>
       </c>
       <c r="T81" s="127">
-        <v>0.11081079619789885</v>
+        <v>0.11356582434464926</v>
       </c>
       <c r="U81" s="36"/>
       <c r="V81" s="35"/>
       <c r="W81" s="38">
-        <v>1.3627228198879142</v>
+        <v>1.6213964950138955</v>
       </c>
       <c r="X81" s="69" t="s">
         <v>69</v>
@@ -12144,38 +12144,38 @@
         <v>10967.741935483871</v>
       </c>
       <c r="AB81" s="33">
-        <v>8238.6399999999485</v>
+        <v>8227.3899999999467</v>
       </c>
       <c r="AC81" s="36"/>
       <c r="AD81" s="35">
         <v>1634.1935483870968</v>
       </c>
       <c r="AE81" s="35">
-        <v>1286.0599999999986</v>
+        <v>1331.799999999999</v>
       </c>
       <c r="AF81" s="115">
-        <v>0.78696920647453528</v>
+        <v>0.81495854717725957</v>
       </c>
       <c r="AG81" s="36"/>
       <c r="AH81" s="35">
-        <v>1332.1616666666807</v>
+        <v>1332.1338461538644</v>
       </c>
       <c r="AI81" s="35">
-        <v>41297.011666667102</v>
+        <v>41296.149230769799</v>
       </c>
       <c r="AJ81" s="115">
-        <v>0.81517985919200753</v>
+        <v>0.8151628351908764</v>
       </c>
       <c r="AK81" s="36"/>
       <c r="AL81" s="108">
         <v>0.14899999999999999</v>
       </c>
       <c r="AM81" s="108">
-        <v>0.15610100696231496</v>
+        <v>0.16187393571959122</v>
       </c>
       <c r="AN81" s="36"/>
       <c r="AO81" s="38">
-        <v>5.7496140139628498</v>
+        <v>6.1571166554636649</v>
       </c>
       <c r="AP81" s="70">
         <v>0</v>
@@ -12191,51 +12191,51 @@
       </c>
       <c r="D82" s="34"/>
       <c r="E82" s="33">
-        <v>867743.2699999999</v>
+        <v>862603.53000000038</v>
       </c>
       <c r="F82" s="123">
-        <v>2.0180076046511624</v>
+        <v>2.0060547209302335</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="35">
         <v>430000</v>
       </c>
       <c r="I82" s="130">
-        <v>166451.61290322579</v>
+        <v>180322.58064516127</v>
       </c>
       <c r="J82" s="35">
-        <v>171917.63000000012</v>
+        <v>184549.98999999868</v>
       </c>
       <c r="K82" s="70">
-        <v>1.0328384748062023</v>
+        <v>1.0234435939177029</v>
       </c>
       <c r="L82" s="36"/>
       <c r="M82" s="35">
         <v>59770.000000000007</v>
       </c>
       <c r="N82" s="35">
-        <v>23136.77419354839</v>
+        <v>25064.83870967742</v>
       </c>
       <c r="O82" s="37">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="P82" s="130">
-        <v>19426.640000000185</v>
+        <v>20949.720000000227</v>
       </c>
       <c r="Q82" s="70">
-        <v>0.83964341085272109</v>
+        <v>0.83582105764405479</v>
       </c>
       <c r="R82" s="36"/>
       <c r="S82" s="127">
         <v>0.13900000000000001</v>
       </c>
       <c r="T82" s="127">
-        <v>0.11299969642438749</v>
+        <v>0.11351786039110799</v>
       </c>
       <c r="U82" s="36"/>
       <c r="V82" s="35"/>
       <c r="W82" s="38">
-        <v>0.96202466262516662</v>
+        <v>0.79722572729435826</v>
       </c>
       <c r="X82" s="69" t="s">
         <v>69</v>
@@ -12246,38 +12246,38 @@
         <v>13870.967741935483</v>
       </c>
       <c r="AB82" s="33">
-        <v>16709.609999999939</v>
+        <v>12632.359999999951</v>
       </c>
       <c r="AC82" s="36"/>
       <c r="AD82" s="35">
         <v>1928.0645161290324</v>
       </c>
       <c r="AE82" s="35">
-        <v>565.08999999999992</v>
+        <v>1023.0800000000014</v>
       </c>
       <c r="AF82" s="115">
-        <v>0.29308666555127982</v>
+        <v>0.53062539735653402</v>
       </c>
       <c r="AG82" s="36"/>
       <c r="AH82" s="35">
-        <v>1618.886666666682</v>
+        <v>1611.5169230769404</v>
       </c>
       <c r="AI82" s="35">
-        <v>50185.486666667144</v>
+        <v>49957.024615385155</v>
       </c>
       <c r="AJ82" s="115">
-        <v>0.83964341085272109</v>
+        <v>0.83582105764405468</v>
       </c>
       <c r="AK82" s="36"/>
       <c r="AL82" s="108">
         <v>0.13900000000000001</v>
       </c>
       <c r="AM82" s="108">
-        <v>3.3818263861335005E-2</v>
+        <v>8.0988825524288835E-2</v>
       </c>
       <c r="AN82" s="36"/>
       <c r="AO82" s="38">
-        <v>-5.7040828601030347</v>
+        <v>-1.4455731153960827</v>
       </c>
       <c r="AP82" s="70">
         <v>0</v>
@@ -12293,51 +12293,51 @@
       </c>
       <c r="D83" s="34"/>
       <c r="E83" s="33">
-        <v>18894.23</v>
+        <v>18581.070000000007</v>
       </c>
       <c r="F83" s="123">
-        <v>1.5745191666666667</v>
+        <v>1.5484225000000005</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="35">
         <v>12000</v>
       </c>
       <c r="I83" s="130">
-        <v>4615.3846153846152</v>
+        <v>5076.9230769230771</v>
       </c>
       <c r="J83" s="35">
-        <v>1368.7700000000007</v>
+        <v>1643.4900000000009</v>
       </c>
       <c r="K83" s="70">
-        <v>0.2965668333333335</v>
+        <v>0.32371772727272746</v>
       </c>
       <c r="L83" s="36"/>
       <c r="M83" s="35">
         <v>1872</v>
       </c>
       <c r="N83" s="35">
-        <v>720</v>
+        <v>792</v>
       </c>
       <c r="O83" s="37">
         <v>0</v>
       </c>
       <c r="P83" s="130">
-        <v>266.02</v>
+        <v>326.28999999999996</v>
       </c>
       <c r="Q83" s="70">
-        <v>0.3694722222222222</v>
+        <v>0.4119823232323232</v>
       </c>
       <c r="R83" s="36"/>
       <c r="S83" s="127">
         <v>0.156</v>
       </c>
       <c r="T83" s="127">
-        <v>0.1943496716029719</v>
+        <v>0.19853482528034838</v>
       </c>
       <c r="U83" s="36"/>
       <c r="V83" s="35"/>
       <c r="W83" s="38">
-        <v>9.4858887906661131</v>
+        <v>10.060298511095295</v>
       </c>
       <c r="X83" s="69" t="s">
         <v>69</v>
@@ -12348,38 +12348,38 @@
         <v>461.53846153846155</v>
       </c>
       <c r="AB83" s="33">
-        <v>176.09</v>
+        <v>274.72000000000003</v>
       </c>
       <c r="AC83" s="36"/>
       <c r="AD83" s="35">
         <v>72</v>
       </c>
       <c r="AE83" s="35">
-        <v>23.949999999999996</v>
+        <v>60.269999999999996</v>
       </c>
       <c r="AF83" s="115">
-        <v>0.33263888888888882</v>
+        <v>0.83708333333333329</v>
       </c>
       <c r="AG83" s="36"/>
       <c r="AH83" s="35">
-        <v>26.601999999999997</v>
+        <v>29.66272727272727</v>
       </c>
       <c r="AI83" s="35">
-        <v>691.65199999999993</v>
+        <v>771.23090909090899</v>
       </c>
       <c r="AJ83" s="115">
-        <v>0.3694722222222222</v>
+        <v>0.4119823232323232</v>
       </c>
       <c r="AK83" s="36"/>
       <c r="AL83" s="108">
         <v>0.156</v>
       </c>
       <c r="AM83" s="108">
-        <v>0.13600999488897719</v>
+        <v>0.21938701223063478</v>
       </c>
       <c r="AN83" s="36"/>
       <c r="AO83" s="38">
-        <v>4.4522687262195486</v>
+        <v>12.922248107163655</v>
       </c>
       <c r="AP83" s="70">
         <v>0</v>
@@ -12393,51 +12393,51 @@
       </c>
       <c r="D84" s="28"/>
       <c r="E84" s="27">
-        <v>1987583.9700000002</v>
+        <v>2007744.2400000009</v>
       </c>
       <c r="F84" s="124">
-        <v>1.9640157806324112</v>
+        <v>1.9839369960474318</v>
       </c>
       <c r="G84" s="26"/>
       <c r="H84" s="29">
         <v>1012000</v>
       </c>
       <c r="I84" s="29">
-        <v>391141.43920595536</v>
+        <v>425287.84119106695</v>
       </c>
       <c r="J84" s="29">
-        <v>419059.19000000192</v>
+        <v>448564.35999999894</v>
       </c>
       <c r="K84" s="31">
-        <v>1.0713750781577158</v>
+        <v>1.0547312115571972</v>
       </c>
       <c r="L84" s="39"/>
       <c r="M84" s="29">
         <v>137602</v>
       </c>
       <c r="N84" s="29">
-        <v>53197.86600496278</v>
+        <v>57805.200992555838</v>
       </c>
       <c r="O84" s="27">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="P84" s="29">
-        <v>41953.350000000348</v>
+        <v>45617.710000000465</v>
       </c>
       <c r="Q84" s="31">
-        <v>0.78862843851831499</v>
+        <v>0.78916272613384941</v>
       </c>
       <c r="R84" s="39"/>
       <c r="S84" s="128">
         <v>0.13597035573122529</v>
       </c>
       <c r="T84" s="128">
-        <v>0.10011318448833005</v>
+        <v>0.10169713438669219</v>
       </c>
       <c r="U84" s="39"/>
       <c r="V84" s="29"/>
       <c r="W84" s="32">
-        <v>0.19224730520830957</v>
+        <v>0.24337644658161903</v>
       </c>
       <c r="X84" s="30" t="s">
         <v>69</v>
@@ -12448,34 +12448,34 @@
         <v>34146.401985111661</v>
       </c>
       <c r="AB84" s="27">
-        <v>60835.47999999988</v>
+        <v>29505.169999999867</v>
       </c>
       <c r="AC84" s="39"/>
       <c r="AD84" s="29">
         <v>4607.3349875930526</v>
       </c>
       <c r="AE84" s="29">
-        <v>674.13999999999805</v>
+        <v>3164.3599999999997</v>
       </c>
       <c r="AF84" s="31">
-        <v>0.1463188593439306</v>
+        <v>0.68680918763693222</v>
       </c>
       <c r="AG84" s="39"/>
       <c r="AH84" s="29">
-        <v>3605.1253333333625</v>
+        <v>3611.8553146853501</v>
       </c>
       <c r="AI84" s="29">
-        <v>108488.50033333426</v>
+        <v>108626.49202797313</v>
       </c>
       <c r="AJ84" s="31">
-        <v>0.78842240907351824</v>
+        <v>0.78942524111548618</v>
       </c>
       <c r="AK84" s="39"/>
       <c r="AL84" s="80">
         <v>0.13597035573122529</v>
       </c>
       <c r="AM84" s="80">
-        <v>1.1081362389184722E-2</v>
+        <v>0.10724764507372823</v>
       </c>
       <c r="AN84" s="39"/>
       <c r="AO84" s="32">
@@ -12540,51 +12540,51 @@
       </c>
       <c r="D86" s="34"/>
       <c r="E86" s="33">
-        <v>534006.31000000006</v>
+        <v>566247.14999999967</v>
       </c>
       <c r="F86" s="123">
-        <v>2.4273014090909095</v>
+        <v>2.5738506818181803</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="35">
         <v>220000</v>
       </c>
       <c r="I86" s="35">
-        <v>84615.38461538461</v>
+        <v>93076.923076923063</v>
       </c>
       <c r="J86" s="35">
-        <v>85490.960000000574</v>
+        <v>92672.720000000729</v>
       </c>
       <c r="K86" s="70">
-        <v>1.0103477090909159</v>
+        <v>0.99565732231405757</v>
       </c>
       <c r="L86" s="36"/>
       <c r="M86" s="35">
         <v>28600</v>
       </c>
       <c r="N86" s="35">
-        <v>11000</v>
+        <v>12100</v>
       </c>
       <c r="O86" s="37">
         <v>353.7</v>
       </c>
       <c r="P86" s="35">
-        <v>10777.507900000033</v>
+        <v>11648.817900000033</v>
       </c>
       <c r="Q86" s="115">
-        <v>0.97977344545454848</v>
+        <v>0.96271222314049854</v>
       </c>
       <c r="R86" s="36"/>
       <c r="S86" s="127">
         <v>0.13</v>
       </c>
       <c r="T86" s="127">
-        <v>0.12606605306572718</v>
+        <v>0.12569845689216785</v>
       </c>
       <c r="U86" s="36"/>
       <c r="V86" s="35"/>
       <c r="W86" s="38">
-        <v>3.6126134271981662</v>
+        <v>3.6274190506124375</v>
       </c>
       <c r="X86" s="69" t="s">
         <v>69</v>
@@ -12595,38 +12595,38 @@
         <v>8461.538461538461</v>
       </c>
       <c r="AB86" s="33">
-        <v>8892.4499999999789</v>
+        <v>7181.7599999999802</v>
       </c>
       <c r="AC86" s="36"/>
       <c r="AD86" s="35">
         <v>1100</v>
       </c>
       <c r="AE86" s="35">
-        <v>628.04894999999988</v>
+        <v>871.31000000000017</v>
       </c>
       <c r="AF86" s="115">
-        <v>0.57095359090909081</v>
+        <v>0.79210000000000014</v>
       </c>
       <c r="AG86" s="36"/>
       <c r="AH86" s="35">
-        <v>1077.7507900000032</v>
+        <v>1058.9834454545485</v>
       </c>
       <c r="AI86" s="35">
-        <v>28021.520540000085</v>
+        <v>27533.569581818261</v>
       </c>
       <c r="AJ86" s="115">
-        <v>0.97977344545454848</v>
+        <v>0.96271222314049865</v>
       </c>
       <c r="AK86" s="36"/>
       <c r="AL86" s="108">
         <v>0.13</v>
       </c>
       <c r="AM86" s="108">
-        <v>7.0627211848253449E-2</v>
+        <v>0.12132262843648389</v>
       </c>
       <c r="AN86" s="36"/>
       <c r="AO86" s="38">
-        <v>-0.73288070216890933</v>
+        <v>3.8036637258830948</v>
       </c>
       <c r="AP86" s="70">
         <v>0</v>
@@ -12642,51 +12642,51 @@
       </c>
       <c r="D87" s="34"/>
       <c r="E87" s="33">
-        <v>582779.79000000015</v>
+        <v>581262.78000000014</v>
       </c>
       <c r="F87" s="123">
-        <v>1.6892167826086961</v>
+        <v>1.6848196521739134</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="35">
         <v>345000</v>
       </c>
       <c r="I87" s="35">
-        <v>133548.38709677421</v>
+        <v>144677.41935483873</v>
       </c>
       <c r="J87" s="35">
-        <v>164398.6100000013</v>
+        <v>174683.58000000042</v>
       </c>
       <c r="K87" s="70">
-        <v>1.2310040845410724</v>
+        <v>1.2074004414715747</v>
       </c>
       <c r="L87" s="36"/>
       <c r="M87" s="35">
         <v>55890</v>
       </c>
       <c r="N87" s="35">
-        <v>21634.83870967742</v>
+        <v>23437.741935483871</v>
       </c>
       <c r="O87" s="37">
-        <v>200.06</v>
+        <v>1053.21</v>
       </c>
       <c r="P87" s="35">
-        <v>24345.339999999902</v>
+        <v>26823.159999999891</v>
       </c>
       <c r="Q87" s="115">
-        <v>1.1252840997196829</v>
+        <v>1.1444430130613659</v>
       </c>
       <c r="R87" s="36"/>
       <c r="S87" s="127">
         <v>0.16200000000000001</v>
       </c>
       <c r="T87" s="127">
-        <v>0.14808726180835538</v>
+        <v>0.15355284108557785</v>
       </c>
       <c r="U87" s="36"/>
       <c r="V87" s="35"/>
       <c r="W87" s="38">
-        <v>6.1253741743931158</v>
+        <v>6.1575335243302147</v>
       </c>
       <c r="X87" s="69" t="s">
         <v>69</v>
@@ -12697,38 +12697,38 @@
         <v>11129.032258064517</v>
       </c>
       <c r="AB87" s="33">
-        <v>13291.869999999954</v>
+        <v>10284.969999999963</v>
       </c>
       <c r="AC87" s="36"/>
       <c r="AD87" s="35">
         <v>1802.9032258064517</v>
       </c>
       <c r="AE87" s="35">
-        <v>1831.3899999999992</v>
+        <v>1624.6699999999987</v>
       </c>
       <c r="AF87" s="115">
-        <v>1.0158005009840754</v>
+        <v>0.90114099123277791</v>
       </c>
       <c r="AG87" s="36"/>
       <c r="AH87" s="35">
-        <v>2028.7783333333252</v>
+        <v>2063.3199999999915</v>
       </c>
       <c r="AI87" s="35">
-        <v>62892.128333333079</v>
+        <v>63962.919999999736</v>
       </c>
       <c r="AJ87" s="115">
-        <v>1.1252840997196829</v>
+        <v>1.1444430130613659</v>
       </c>
       <c r="AK87" s="36"/>
       <c r="AL87" s="108">
         <v>0.16200000000000001</v>
       </c>
       <c r="AM87" s="108">
-        <v>0.13778271981293871</v>
+        <v>0.15796545833386044</v>
       </c>
       <c r="AN87" s="36"/>
       <c r="AO87" s="38">
-        <v>5.0746057552469894</v>
+        <v>6.6715799851623441</v>
       </c>
       <c r="AP87" s="70">
         <v>0</v>
@@ -12744,51 +12744,51 @@
       </c>
       <c r="D88" s="34"/>
       <c r="E88" s="33">
-        <v>921372.87999999977</v>
+        <v>916524.90000000061</v>
       </c>
       <c r="F88" s="123">
-        <v>1.7384393962264146</v>
+        <v>1.7292922641509445</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="35">
         <v>530000</v>
       </c>
       <c r="I88" s="35">
-        <v>205161.29032258064</v>
+        <v>222258.06451612903</v>
       </c>
       <c r="J88" s="35">
-        <v>210658.02999999994</v>
+        <v>225013.52999999927</v>
       </c>
       <c r="K88" s="70">
-        <v>1.0267922845911948</v>
+        <v>1.0123975950653088</v>
       </c>
       <c r="L88" s="36"/>
       <c r="M88" s="35">
         <v>80560</v>
       </c>
       <c r="N88" s="35">
-        <v>31184.516129032258</v>
+        <v>33783.225806451614</v>
       </c>
       <c r="O88" s="37">
-        <v>926.82</v>
+        <v>2655.66</v>
       </c>
       <c r="P88" s="35">
-        <v>30704.274750000219</v>
+        <v>34554.384750000245</v>
       </c>
       <c r="Q88" s="115">
-        <v>0.98460000543074189</v>
+        <v>1.0228266817374605</v>
       </c>
       <c r="R88" s="36"/>
       <c r="S88" s="127">
         <v>0.152</v>
       </c>
       <c r="T88" s="127">
-        <v>0.14575411509354866</v>
+        <v>0.15356580890935917</v>
       </c>
       <c r="U88" s="36"/>
       <c r="V88" s="35"/>
       <c r="W88" s="38">
-        <v>5.5376121907148779</v>
+        <v>5.5463174814420109</v>
       </c>
       <c r="X88" s="69" t="s">
         <v>69</v>
@@ -12799,38 +12799,38 @@
         <v>17096.774193548386</v>
       </c>
       <c r="AB88" s="33">
-        <v>17873.509999999951</v>
+        <v>14355.499999999951</v>
       </c>
       <c r="AC88" s="36"/>
       <c r="AD88" s="35">
         <v>2598.7096774193546</v>
       </c>
       <c r="AE88" s="35">
-        <v>1665.0296499999999</v>
+        <v>2121.2700000000009</v>
       </c>
       <c r="AF88" s="115">
-        <v>0.64071399143495533</v>
+        <v>0.81627817775571043</v>
       </c>
       <c r="AG88" s="36"/>
       <c r="AH88" s="35">
-        <v>2558.6895625000184</v>
+        <v>2658.029596153865</v>
       </c>
       <c r="AI88" s="35">
-        <v>79319.37643750057</v>
+        <v>82398.917480769815</v>
       </c>
       <c r="AJ88" s="115">
-        <v>0.98460000543074189</v>
+        <v>1.0228266817374605</v>
       </c>
       <c r="AK88" s="36"/>
       <c r="AL88" s="108">
         <v>0.152</v>
       </c>
       <c r="AM88" s="108">
-        <v>9.3156277082677347E-2</v>
+        <v>0.14776705792205136</v>
       </c>
       <c r="AN88" s="36"/>
       <c r="AO88" s="38">
-        <v>0.10120927562607716</v>
+        <v>5.674062206122886</v>
       </c>
       <c r="AP88" s="70">
         <v>0</v>
@@ -12846,51 +12846,51 @@
       </c>
       <c r="D89" s="34"/>
       <c r="E89" s="33">
-        <v>13634.519999999999</v>
+        <v>14065.629999999997</v>
       </c>
       <c r="F89" s="123">
-        <v>1.9477885714285712</v>
+        <v>2.009375714285714</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="35">
         <v>7000</v>
       </c>
       <c r="I89" s="35">
-        <v>2692.3076923076924</v>
+        <v>2961.5384615384614</v>
       </c>
       <c r="J89" s="35">
-        <v>2815.9599999999959</v>
+        <v>3003.0099999999943</v>
       </c>
       <c r="K89" s="70">
-        <v>1.0459279999999984</v>
+        <v>1.0140033766233747</v>
       </c>
       <c r="L89" s="36"/>
       <c r="M89" s="35">
         <v>1680</v>
       </c>
       <c r="N89" s="35">
-        <v>646.15384615384619</v>
+        <v>710.76923076923072</v>
       </c>
       <c r="O89" s="37">
         <v>0</v>
       </c>
       <c r="P89" s="35">
-        <v>465.87000000000006</v>
+        <v>499.17</v>
       </c>
       <c r="Q89" s="115">
-        <v>0.72098928571428578</v>
+        <v>0.70229545454545461</v>
       </c>
       <c r="R89" s="36"/>
       <c r="S89" s="127">
         <v>0.24</v>
       </c>
       <c r="T89" s="127">
-        <v>0.16543913976050822</v>
+        <v>0.16622322269989143</v>
       </c>
       <c r="U89" s="36"/>
       <c r="V89" s="35"/>
       <c r="W89" s="38">
-        <v>8.99977272404427</v>
+        <v>9.027941964895092</v>
       </c>
       <c r="X89" s="69" t="s">
         <v>69</v>
@@ -12901,38 +12901,38 @@
         <v>269.23076923076923</v>
       </c>
       <c r="AB89" s="33">
-        <v>339.5</v>
+        <v>187.04999999999998</v>
       </c>
       <c r="AC89" s="36"/>
       <c r="AD89" s="35">
         <v>64.615384615384613</v>
       </c>
       <c r="AE89" s="35">
-        <v>75.600000000000009</v>
+        <v>33.300000000000004</v>
       </c>
       <c r="AF89" s="115">
-        <v>1.1700000000000002</v>
+        <v>0.51535714285714296</v>
       </c>
       <c r="AG89" s="36"/>
       <c r="AH89" s="35">
-        <v>46.587000000000003</v>
+        <v>45.379090909090912</v>
       </c>
       <c r="AI89" s="35">
-        <v>1211.2620000000002</v>
+        <v>1179.8563636363638</v>
       </c>
       <c r="AJ89" s="115">
-        <v>0.72098928571428578</v>
+        <v>0.70229545454545461</v>
       </c>
       <c r="AK89" s="36"/>
       <c r="AL89" s="108">
         <v>0.24</v>
       </c>
       <c r="AM89" s="108">
-        <v>0.22268041237113403</v>
+        <v>0.17802726543704894</v>
       </c>
       <c r="AN89" s="36"/>
       <c r="AO89" s="38">
-        <v>13.617083946980859</v>
+        <v>9.4520181769580365</v>
       </c>
       <c r="AP89" s="70">
         <v>0</v>
@@ -12946,51 +12946,51 @@
       </c>
       <c r="D90" s="28"/>
       <c r="E90" s="27">
-        <v>2051793.5</v>
+        <v>2078100.4600000002</v>
       </c>
       <c r="F90" s="124">
-        <v>1.8618815789473684</v>
+        <v>1.8857535934664249</v>
       </c>
       <c r="G90" s="26"/>
       <c r="H90" s="29">
         <v>1102000</v>
       </c>
       <c r="I90" s="29">
-        <v>426017.3697270471</v>
+        <v>462973.94540942926</v>
       </c>
       <c r="J90" s="29">
-        <v>463363.56000000186</v>
+        <v>495372.84000000043</v>
       </c>
       <c r="K90" s="31">
-        <v>1.087663538923032</v>
+        <v>1.0699799522453026</v>
       </c>
       <c r="L90" s="39"/>
       <c r="M90" s="29">
         <v>166730</v>
       </c>
       <c r="N90" s="29">
-        <v>64465.508684863526</v>
+        <v>70031.736972704719</v>
       </c>
       <c r="O90" s="27">
-        <v>1480.58</v>
+        <v>4062.5699999999997</v>
       </c>
       <c r="P90" s="29">
-        <v>66292.992650000146</v>
+        <v>73525.532650000168</v>
       </c>
       <c r="Q90" s="31">
-        <v>1.0283482439279303</v>
+        <v>1.0498887479923165</v>
       </c>
       <c r="R90" s="39"/>
       <c r="S90" s="128">
         <v>0.15129764065335752</v>
       </c>
       <c r="T90" s="128">
-        <v>0.14306906794742313</v>
+        <v>0.14842463436227166</v>
       </c>
       <c r="U90" s="39"/>
       <c r="V90" s="29"/>
       <c r="W90" s="32">
-        <v>5.4120230451444371</v>
+        <v>5.4239757371438975</v>
       </c>
       <c r="X90" s="30" t="s">
         <v>69</v>
@@ -13001,34 +13001,34 @@
         <v>36956.575682382128</v>
       </c>
       <c r="AB90" s="27">
-        <v>40397.329999999885</v>
+        <v>32009.279999999893</v>
       </c>
       <c r="AC90" s="39"/>
       <c r="AD90" s="29">
         <v>5566.2282878411916</v>
       </c>
       <c r="AE90" s="29">
-        <v>4200.0685999999987</v>
+        <v>4650.55</v>
       </c>
       <c r="AF90" s="31">
-        <v>0.75456276365354669</v>
+        <v>0.83549393943446604</v>
       </c>
       <c r="AG90" s="39"/>
       <c r="AH90" s="29">
-        <v>5711.8056858333466</v>
+        <v>5825.7121325174958</v>
       </c>
       <c r="AI90" s="29">
-        <v>171444.28731083372</v>
+        <v>175075.26342622415</v>
       </c>
       <c r="AJ90" s="31">
-        <v>1.0282749793728407</v>
+        <v>1.0500525605843229</v>
       </c>
       <c r="AK90" s="39"/>
       <c r="AL90" s="80">
         <v>0.15129764065335752</v>
       </c>
       <c r="AM90" s="80">
-        <v>0.10396896527567566</v>
+        <v>0.1452875541093088</v>
       </c>
       <c r="AN90" s="39"/>
       <c r="AO90" s="32">
@@ -13090,53 +13090,53 @@
       </c>
       <c r="D92" s="34"/>
       <c r="E92" s="93">
-        <v>4345860.4100000011</v>
+        <v>4395594.5300000012</v>
       </c>
       <c r="F92" s="126">
-        <v>0.81920083129123489</v>
+        <v>0.82857578322337444</v>
       </c>
       <c r="G92" s="34"/>
       <c r="H92" s="93">
         <v>5305000</v>
       </c>
       <c r="I92" s="93">
-        <v>2040384.615384615</v>
+        <v>2244423.076923077</v>
       </c>
       <c r="J92" s="93">
-        <v>2427036.8600000017</v>
+        <v>2645051.2900000024</v>
       </c>
       <c r="K92" s="112">
-        <v>1.1894996863336487</v>
+        <v>1.1784994180447272</v>
       </c>
       <c r="L92" s="36"/>
       <c r="M92" s="93">
         <v>530312.894377677</v>
       </c>
       <c r="N92" s="93">
-        <v>203966.49783756805</v>
+        <v>224363.14762132484</v>
       </c>
       <c r="O92" s="93">
-        <v>375.46</v>
+        <v>696.66</v>
       </c>
       <c r="P92" s="93">
-        <v>226168.33297000013</v>
+        <v>251850.67259000018</v>
       </c>
       <c r="Q92" s="112">
-        <v>1.1088504012561555</v>
+        <v>1.1225135467214435</v>
       </c>
       <c r="R92" s="96"/>
       <c r="S92" s="129">
         <v>9.9964730325669562E-2</v>
       </c>
       <c r="T92" s="129">
-        <v>9.3187020229268364E-2</v>
+        <v>9.5215799233140747E-2</v>
       </c>
       <c r="U92" s="98"/>
       <c r="V92" s="99">
         <v>0</v>
       </c>
       <c r="W92" s="103">
-        <v>-4.3324445855345886</v>
+        <v>-4.1561673236967183</v>
       </c>
       <c r="X92" s="100" t="s">
         <v>69</v>
@@ -13147,38 +13147,38 @@
         <v>204038.46153846156</v>
       </c>
       <c r="AB92" s="93">
-        <v>274734.39999999985</v>
+        <v>218014.42999999988</v>
       </c>
       <c r="AC92" s="98"/>
       <c r="AD92" s="93">
         <v>20396.649783756809</v>
       </c>
       <c r="AE92" s="93">
-        <v>24702.239879999997</v>
+        <v>25361.139619999998</v>
       </c>
       <c r="AF92" s="112">
-        <v>1.211093005071451</v>
+        <v>1.2433973171514048</v>
       </c>
       <c r="AG92" s="98"/>
       <c r="AH92" s="93">
-        <v>22616.833297000016</v>
+        <v>22895.515690000018</v>
       </c>
       <c r="AI92" s="93">
-        <v>588037.6657220003</v>
+        <v>595283.40794000064</v>
       </c>
       <c r="AJ92" s="112">
-        <v>1.1088504012561553</v>
+        <v>1.1225135467214438</v>
       </c>
       <c r="AK92" s="98"/>
       <c r="AL92" s="102">
         <v>9.9964730325669562E-2</v>
       </c>
       <c r="AM92" s="97">
-        <v>8.9913166607458003E-2</v>
+        <v>0.11632780279727362</v>
       </c>
       <c r="AN92" s="98"/>
       <c r="AO92" s="103">
-        <v>-3.3095164347821542</v>
+        <v>-2.1661136742187552</v>
       </c>
       <c r="AP92" s="95">
         <v>0</v>
@@ -13191,53 +13191,53 @@
       </c>
       <c r="D93" s="34"/>
       <c r="E93" s="93">
-        <v>5257091.5599999987</v>
+        <v>5327965.5799999991</v>
       </c>
       <c r="F93" s="126">
-        <v>0.98576627789236804</v>
+        <v>0.99905598724920286</v>
       </c>
       <c r="G93" s="34"/>
       <c r="H93" s="93">
         <v>5333000</v>
       </c>
       <c r="I93" s="93">
-        <v>2064387.0967741937</v>
+        <v>2236419.3548387098</v>
       </c>
       <c r="J93" s="93">
-        <v>2084742.889999985</v>
+        <v>2266856.739999976</v>
       </c>
       <c r="K93" s="112">
-        <v>1.0098604536220941</v>
+        <v>1.013609873790178</v>
       </c>
       <c r="L93" s="36"/>
       <c r="M93" s="93">
         <v>817629.02353412041</v>
       </c>
       <c r="N93" s="93">
-        <v>316501.55749707879</v>
+        <v>342876.68728850211</v>
       </c>
       <c r="O93" s="93">
-        <v>635.6400000000001</v>
+        <v>2356.8100000000004</v>
       </c>
       <c r="P93" s="93">
-        <v>331856.42279999959</v>
+        <v>360920.83665999991</v>
       </c>
       <c r="Q93" s="112">
-        <v>1.0485143435765321</v>
+        <v>1.0526257690897345</v>
       </c>
       <c r="R93" s="96"/>
       <c r="S93" s="129">
         <v>0.15331502410165393</v>
       </c>
       <c r="T93" s="129">
-        <v>0.15918338150562153</v>
+        <v>0.15921642964522043</v>
       </c>
       <c r="U93" s="98"/>
       <c r="V93" s="99">
         <v>0</v>
       </c>
       <c r="W93" s="103">
-        <v>4.0098245784153699</v>
+        <v>3.9330450436835869</v>
       </c>
       <c r="X93" s="100" t="s">
         <v>69</v>
@@ -13248,38 +13248,38 @@
         <v>172032.25806451609</v>
       </c>
       <c r="AB93" s="93">
-        <v>142678.88999999969</v>
+        <v>182113.84999999974</v>
       </c>
       <c r="AC93" s="98"/>
       <c r="AD93" s="93">
         <v>26375.129791423242</v>
       </c>
       <c r="AE93" s="93">
-        <v>22762.999249999997</v>
+        <v>27343.243859999988</v>
       </c>
       <c r="AF93" s="112">
-        <v>0.86304785720531885</v>
+        <v>1.036705566047738</v>
       </c>
       <c r="AG93" s="98"/>
       <c r="AH93" s="93">
-        <v>27654.701899999971</v>
+        <v>27763.141281538454</v>
       </c>
       <c r="AI93" s="93">
-        <v>857295.75889999873</v>
+        <v>860657.37972769188</v>
       </c>
       <c r="AJ93" s="112">
-        <v>1.0485143435765316</v>
+        <v>1.0526257690897343</v>
       </c>
       <c r="AK93" s="98"/>
       <c r="AL93" s="102">
         <v>0.15331502410165393</v>
       </c>
       <c r="AM93" s="97">
-        <v>0.15954006405572713</v>
+        <v>0.15014368132901493</v>
       </c>
       <c r="AN93" s="98"/>
       <c r="AO93" s="103">
-        <v>4.6751620018908771</v>
+        <v>3.2512704882136716</v>
       </c>
       <c r="AP93" s="95">
         <v>0</v>
@@ -13292,53 +13292,53 @@
       </c>
       <c r="D94" s="34"/>
       <c r="E94" s="93">
-        <v>8445855.8100000005</v>
+        <v>8477034.1699999999</v>
       </c>
       <c r="F94" s="126">
-        <v>1.0264773711716093</v>
+        <v>1.0302666711229946</v>
       </c>
       <c r="G94" s="34"/>
       <c r="H94" s="93">
         <v>8228000</v>
       </c>
       <c r="I94" s="93">
-        <v>3185032.2580645168</v>
+        <v>3450451.6129032257</v>
       </c>
       <c r="J94" s="93">
-        <v>3257774.4699999434</v>
+        <v>3542137.3099999302</v>
       </c>
       <c r="K94" s="112">
-        <v>1.0228387677240138</v>
+        <v>1.026572086028924</v>
       </c>
       <c r="L94" s="36"/>
       <c r="M94" s="93">
         <v>1301569.1825819584</v>
       </c>
       <c r="N94" s="93">
-        <v>503833.23196720966</v>
+        <v>545819.33463114372</v>
       </c>
       <c r="O94" s="93">
-        <v>10180.269999999999</v>
+        <v>14229.56</v>
       </c>
       <c r="P94" s="93">
-        <v>514901.58757000027</v>
+        <v>559854.50543000048</v>
       </c>
       <c r="Q94" s="112">
-        <v>1.0219682920865985</v>
+        <v>1.0257139494853944</v>
       </c>
       <c r="R94" s="96"/>
       <c r="S94" s="129">
         <v>0.15818779564681068</v>
       </c>
       <c r="T94" s="129">
-        <v>0.15805317167029342</v>
+        <v>0.15805556262583495</v>
       </c>
       <c r="U94" s="98"/>
       <c r="V94" s="99">
         <v>0</v>
       </c>
       <c r="W94" s="103">
-        <v>3.176982891941766</v>
+        <v>2.986708480534114</v>
       </c>
       <c r="X94" s="100" t="s">
         <v>69</v>
@@ -13349,38 +13349,38 @@
         <v>265419.35483870964</v>
       </c>
       <c r="AB94" s="93">
-        <v>251455.58999999982</v>
+        <v>284362.83999999997</v>
       </c>
       <c r="AC94" s="98"/>
       <c r="AD94" s="93">
         <v>41986.102663934129</v>
       </c>
       <c r="AE94" s="93">
-        <v>35007.675579999996</v>
+        <v>40903.627860000008</v>
       </c>
       <c r="AF94" s="112">
-        <v>0.8337919777934385</v>
+        <v>0.97421825948937235</v>
       </c>
       <c r="AG94" s="98"/>
       <c r="AH94" s="93">
-        <v>42908.465630833358</v>
+        <v>43065.731186923113</v>
       </c>
       <c r="AI94" s="93">
-        <v>1330162.4345558339</v>
+        <v>1335037.6667946163</v>
       </c>
       <c r="AJ94" s="112">
-        <v>1.0219682920865985</v>
+        <v>1.025713949485394</v>
       </c>
       <c r="AK94" s="98"/>
       <c r="AL94" s="102">
         <v>0.15818779564681068</v>
       </c>
       <c r="AM94" s="97">
-        <v>0.13922011270459336</v>
+        <v>0.14384308392756245</v>
       </c>
       <c r="AN94" s="98"/>
       <c r="AO94" s="103">
-        <v>2.2657581722481397</v>
+        <v>0.90947813715741044</v>
       </c>
       <c r="AP94" s="95">
         <v>0</v>
@@ -13393,53 +13393,53 @@
       </c>
       <c r="D95" s="34"/>
       <c r="E95" s="93">
-        <v>500705.78000000014</v>
+        <v>411747.18</v>
       </c>
       <c r="F95" s="126">
-        <v>0.15172902424242429</v>
+        <v>0.12477187272727272</v>
       </c>
       <c r="G95" s="34"/>
       <c r="H95" s="93">
         <v>3300000</v>
       </c>
       <c r="I95" s="93">
-        <v>1269230.7692307692</v>
+        <v>1396153.8461538462</v>
       </c>
       <c r="J95" s="93">
-        <v>1460156.0099999993</v>
+        <v>1602245.1799999992</v>
       </c>
       <c r="K95" s="112">
-        <v>1.1504259472727267</v>
+        <v>1.1476136275482087</v>
       </c>
       <c r="L95" s="36"/>
       <c r="M95" s="93">
         <v>555198.5430327655</v>
       </c>
       <c r="N95" s="93">
-        <v>213537.90116644828</v>
+        <v>234891.6912830931</v>
       </c>
       <c r="O95" s="93">
         <v>19500.95</v>
       </c>
       <c r="P95" s="93">
-        <v>105910.7</v>
+        <v>126065.04000000002</v>
       </c>
       <c r="Q95" s="112">
-        <v>0.49598080444485049</v>
+        <v>0.53669433478626349</v>
       </c>
       <c r="R95" s="96"/>
       <c r="S95" s="129">
         <v>0.16824198273720167</v>
       </c>
       <c r="T95" s="129">
-        <v>7.2533824656174958E-2</v>
+        <v>7.8680242932607905E-2</v>
       </c>
       <c r="U95" s="98"/>
       <c r="V95" s="99">
         <v>0</v>
       </c>
       <c r="W95" s="103">
-        <v>-8.464668100773757</v>
+        <v>-7.8023545684812969</v>
       </c>
       <c r="X95" s="100" t="s">
         <v>69</v>
@@ -13450,38 +13450,38 @@
         <v>126923.07692307692</v>
       </c>
       <c r="AB95" s="93">
-        <v>57701.51</v>
+        <v>142089.16999999998</v>
       </c>
       <c r="AC95" s="98"/>
       <c r="AD95" s="93">
         <v>21353.790116644828</v>
       </c>
       <c r="AE95" s="93">
-        <v>7357.8599999999988</v>
+        <v>20154.340000000004</v>
       </c>
       <c r="AF95" s="112">
-        <v>0.34456927598369069</v>
+        <v>0.94382963820039245</v>
       </c>
       <c r="AG95" s="98"/>
       <c r="AH95" s="93">
-        <v>10591.070000000003</v>
+        <v>11460.458181818183</v>
       </c>
       <c r="AI95" s="93">
-        <v>275367.82</v>
+        <v>297971.91272727289</v>
       </c>
       <c r="AJ95" s="112">
-        <v>0.49598080444485054</v>
+        <v>0.53669433478626372</v>
       </c>
       <c r="AK95" s="98"/>
       <c r="AL95" s="102">
         <v>0.16824198273720167</v>
       </c>
       <c r="AM95" s="97">
-        <v>0.12751590036378596</v>
+        <v>0.14184290048284473</v>
       </c>
       <c r="AN95" s="98"/>
       <c r="AO95" s="103">
-        <v>-4.701402095023167</v>
+        <v>-0.97650651348023509</v>
       </c>
       <c r="AP95" s="95">
         <v>0</v>
@@ -13537,53 +13537,53 @@
       </c>
       <c r="D97" s="28"/>
       <c r="E97" s="93">
-        <v>18549513.560000002</v>
+        <v>18612341.460000001</v>
       </c>
       <c r="F97" s="126">
-        <v>0.83684532888207175</v>
+        <v>0.83967975548136786</v>
       </c>
       <c r="G97" s="28"/>
       <c r="H97" s="93">
         <v>22166000</v>
       </c>
       <c r="I97" s="93">
-        <v>8559034.7394540943</v>
+        <v>9327447.8908188585</v>
       </c>
       <c r="J97" s="93">
-        <v>9229710.2299999297</v>
+        <v>10056290.519999908</v>
       </c>
       <c r="K97" s="44">
-        <v>1.0783587765398661</v>
+        <v>1.0781395551829842</v>
       </c>
       <c r="L97" s="39"/>
       <c r="M97" s="93">
         <v>3204709.643526521</v>
       </c>
       <c r="N97" s="93">
-        <v>1237839.1884683049</v>
+        <v>1347950.8608240637</v>
       </c>
       <c r="O97" s="93">
-        <v>30692.32</v>
+        <v>36783.979999999996</v>
       </c>
       <c r="P97" s="93">
-        <v>1178837.0433399999</v>
+        <v>1298691.0546800005</v>
       </c>
       <c r="Q97" s="44">
-        <v>0.95233456358631363</v>
+        <v>0.96345578494311845</v>
       </c>
       <c r="R97" s="39"/>
       <c r="S97" s="129">
         <v>0.14457771557910859</v>
       </c>
       <c r="T97" s="129">
-        <v>0.12772199927884506</v>
+        <v>0.12914215754777264</v>
       </c>
       <c r="U97" s="45"/>
       <c r="V97" s="43">
         <v>0</v>
       </c>
       <c r="W97" s="46">
-        <v>-0.45130253953886906</v>
+        <v>-0.3977191713042621</v>
       </c>
       <c r="X97" s="81" t="s">
         <v>69</v>
@@ -13594,38 +13594,38 @@
         <v>768413.15136476408</v>
       </c>
       <c r="AB97" s="93">
-        <v>726570.38999999943</v>
+        <v>826580.28999999957</v>
       </c>
       <c r="AC97" s="98"/>
       <c r="AD97" s="93">
         <v>110111.672355759</v>
       </c>
       <c r="AE97" s="93">
-        <v>89830.774709999983</v>
+        <v>113762.35133999999</v>
       </c>
       <c r="AF97" s="112">
-        <v>0.81581518823695987</v>
+        <v>1.0331543323803678</v>
       </c>
       <c r="AG97" s="98"/>
       <c r="AH97" s="93">
-        <v>103771.07082783335</v>
+        <v>105184.84634027976</v>
       </c>
       <c r="AI97" s="93">
-        <v>3050863.6791778328</v>
+        <v>3088950.367189582</v>
       </c>
       <c r="AJ97" s="112">
-        <v>0.95199378993368233</v>
+        <v>0.96387838861758612</v>
       </c>
       <c r="AK97" s="98"/>
       <c r="AL97" s="102">
         <v>0.14457771557910859</v>
       </c>
       <c r="AM97" s="97">
-        <v>0.12363671289990232</v>
+        <v>0.13763012827223362</v>
       </c>
       <c r="AN97" s="98"/>
       <c r="AO97" s="103">
-        <v>7.7443936299041838E-2</v>
+        <v>0.2900240144849735</v>
       </c>
       <c r="AP97" s="42">
         <v>0</v>
